--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAV" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fills" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,6 +564,67 @@
         <v>0.3074378487744298</v>
       </c>
       <c r="Q2" t="n">
+        <v>0.0338626887492592</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-25T09:08:26.098645+00:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Crisis</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.255229225018728</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.0654602418928413</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.1897689831258868</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6586994624763109</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3074378487744298</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0338626887492592</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6586994624763109</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3074378487744298</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.0338626887492592</v>
       </c>
     </row>
@@ -577,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,6 +718,37 @@
       </c>
       <c r="I2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3003385.859672599</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2400122.1596726</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1324475836892178</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0616352705410217</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0067783498195663</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.799138795950194</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +1005,600 @@
         <v>103.8</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-25-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2484</v>
+      </c>
+      <c r="F10" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-25-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2104</v>
+      </c>
+      <c r="F11" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-25-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2925</v>
+      </c>
+      <c r="F12" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-25-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3947</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-25-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>451</v>
+      </c>
+      <c r="F14" t="n">
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-25-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>533</v>
+      </c>
+      <c r="F15" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>600</v>
+      </c>
+      <c r="F16" t="n">
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-25-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>195</v>
+      </c>
+      <c r="F17" t="n">
+        <v>104.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fill_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>signal_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fill_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fill_price</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fees_tax</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>slippage_bp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-24-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2517</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.169575</v>
+      </c>
+      <c r="H2" t="n">
+        <v>98589.82027500001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>84.29429633512498</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-24-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2108</v>
+      </c>
+      <c r="G3" t="n">
+        <v>46.873425</v>
+      </c>
+      <c r="H3" t="n">
+        <v>98809.1799</v>
+      </c>
+      <c r="I3" t="n">
+        <v>84.48184881449998</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-24-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33.51674999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>98706.82875</v>
+      </c>
+      <c r="I4" t="n">
+        <v>84.39433858124998</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-24-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3952</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25.0125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>98849.39999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>84.51623699999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-24-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>450</v>
+      </c>
+      <c r="G6" t="n">
+        <v>136.56825</v>
+      </c>
+      <c r="H6" t="n">
+        <v>61455.7125</v>
+      </c>
+      <c r="I6" t="n">
+        <v>52.5446341875</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-24-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>534</v>
+      </c>
+      <c r="G7" t="n">
+        <v>115.0575</v>
+      </c>
+      <c r="H7" t="n">
+        <v>61440.705</v>
+      </c>
+      <c r="I7" t="n">
+        <v>52.531802775</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-24-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>605</v>
+      </c>
+      <c r="G8" t="n">
+        <v>101.55075</v>
+      </c>
+      <c r="H8" t="n">
+        <v>61438.20374999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>52.52966420624999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-24-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>195</v>
+      </c>
+      <c r="G9" t="n">
+        <v>102.95145</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20075.53275</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17.16458050125</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +626,67 @@
       </c>
       <c r="Q3" t="n">
         <v>0.0338626887492592</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-26T09:11:55.106026+00:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sideways</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1474205419620445</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.0994252735342825</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.0479952684277619</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7102101104062843</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2530927547424653</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0366971348512503</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7102101104062843</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2530927547424653</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0366971348512503</v>
       </c>
     </row>
   </sheetData>
@@ -639,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,6 +809,37 @@
         <v>8</v>
       </c>
       <c r="I3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2997580.922685131</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1800948.622685131</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2628292013862529</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1225920198580742</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0137781101045318</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.600800668651141</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -762,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,6 +1303,214 @@
       </c>
       <c r="F17" t="n">
         <v>104.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-26-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F18" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-26-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2394</v>
+      </c>
+      <c r="F19" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-26-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3341</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-26-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4464</v>
+      </c>
+      <c r="F21" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-26-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>319</v>
+      </c>
+      <c r="F22" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-26-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>375</v>
+      </c>
+      <c r="F23" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-26-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>429</v>
+      </c>
+      <c r="F24" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-26-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>215</v>
+      </c>
+      <c r="F25" t="n">
+        <v>105.9</v>
       </c>
     </row>
   </sheetData>
@@ -1224,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1599,6 +1899,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-25-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2484</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.6198</v>
+      </c>
+      <c r="H10" t="n">
+        <v>98415.58319999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>84.14532363599999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-25-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2104</v>
+      </c>
+      <c r="G11" t="n">
+        <v>46.92345</v>
+      </c>
+      <c r="H11" t="n">
+        <v>98726.9388</v>
+      </c>
+      <c r="I11" t="n">
+        <v>84.41153267399999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-25-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2925</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33.51674999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>98036.49374999998</v>
+      </c>
+      <c r="I12" t="n">
+        <v>83.82120215624998</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-25-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3947</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25.0125</v>
+      </c>
+      <c r="H13" t="n">
+        <v>98724.33749999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>84.40930856249999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-25-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>451</v>
+      </c>
+      <c r="G14" t="n">
+        <v>136.56825</v>
+      </c>
+      <c r="H14" t="n">
+        <v>61592.28075000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>52.66140004125</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-25-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>533</v>
+      </c>
+      <c r="G15" t="n">
+        <v>115.0575</v>
+      </c>
+      <c r="H15" t="n">
+        <v>61325.64749999999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>52.43342861249999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>600</v>
+      </c>
+      <c r="G16" t="n">
+        <v>102.55125</v>
+      </c>
+      <c r="H16" t="n">
+        <v>61530.75</v>
+      </c>
+      <c r="I16" t="n">
+        <v>52.60879125</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-25-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>195</v>
+      </c>
+      <c r="G17" t="n">
+        <v>104.15205</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20309.64975</v>
+      </c>
+      <c r="I17" t="n">
+        <v>17.36475053625</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,6 +687,67 @@
       </c>
       <c r="Q4" t="n">
         <v>0.0366971348512503</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-27T19:13:28.536995+00:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sideways</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1089805136466243</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.081923805706775</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.0270567079398493</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7478820956458789</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2127714709141795</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0393464334399415</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.7478820956458789</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2127714709141795</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0393464334399415</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,6 +901,37 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2990921.174510478</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1199624.374510478</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4110521402160386</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1664075951722332</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0214516686520503</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4010885959596778</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -854,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,6 +1603,214 @@
       </c>
       <c r="F25" t="n">
         <v>105.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-27-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3191</v>
+      </c>
+      <c r="F26" t="n">
+        <v>39.35</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-27-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2721</v>
+      </c>
+      <c r="F27" t="n">
+        <v>46.15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-27-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3765</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33.35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-27-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5013</v>
+      </c>
+      <c r="F29" t="n">
+        <v>25.05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-27-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>170</v>
+      </c>
+      <c r="F30" t="n">
+        <v>135.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-27-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>199</v>
+      </c>
+      <c r="F31" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-27-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>227</v>
+      </c>
+      <c r="F32" t="n">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-27-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>50</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>251</v>
+      </c>
+      <c r="F33" t="n">
+        <v>106.05</v>
       </c>
     </row>
   </sheetData>
@@ -1524,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,6 +2519,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-26-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2818</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39.8199</v>
+      </c>
+      <c r="H18" t="n">
+        <v>112212.4782</v>
+      </c>
+      <c r="I18" t="n">
+        <v>95.941668861</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-26-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2394</v>
+      </c>
+      <c r="G19" t="n">
+        <v>46.6233</v>
+      </c>
+      <c r="H19" t="n">
+        <v>111616.1802</v>
+      </c>
+      <c r="I19" t="n">
+        <v>95.431834071</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-26-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3341</v>
+      </c>
+      <c r="G20" t="n">
+        <v>33.51674999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>111979.46175</v>
+      </c>
+      <c r="I20" t="n">
+        <v>95.74243979624998</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-26-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4464</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25.0125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>111655.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>95.465709</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-26-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>319</v>
+      </c>
+      <c r="G22" t="n">
+        <v>136.56825</v>
+      </c>
+      <c r="H22" t="n">
+        <v>43565.27175</v>
+      </c>
+      <c r="I22" t="n">
+        <v>37.24830734625</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-26-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>375</v>
+      </c>
+      <c r="G23" t="n">
+        <v>116.058</v>
+      </c>
+      <c r="H23" t="n">
+        <v>43521.75</v>
+      </c>
+      <c r="I23" t="n">
+        <v>37.21109625</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-26-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>429</v>
+      </c>
+      <c r="G24" t="n">
+        <v>101.0505</v>
+      </c>
+      <c r="H24" t="n">
+        <v>43350.6645</v>
+      </c>
+      <c r="I24" t="n">
+        <v>37.0648181475</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-26-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>215</v>
+      </c>
+      <c r="G25" t="n">
+        <v>106.55325</v>
+      </c>
+      <c r="H25" t="n">
+        <v>22908.94875</v>
+      </c>
+      <c r="I25" t="n">
+        <v>19.58715118125</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,6 +748,67 @@
       </c>
       <c r="Q5" t="n">
         <v>0.0393464334399415</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-28T20:19:58.018078+00:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1328263526995829</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.0342580655108901</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1670844182104729</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7700909129169196</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1712221515478624</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0586869355352179</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.7700909129169196</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1712221515478624</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0586869355352179</v>
       </c>
     </row>
   </sheetData>
@@ -761,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +993,37 @@
         <v>8</v>
       </c>
       <c r="I5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3031940.393478123</v>
+      </c>
+      <c r="C6" t="n">
+        <v>597647.8934781225</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5863678269613146</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1863199557666621</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0301949207830495</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.227312904926573</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -946,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,6 +1903,214 @@
       </c>
       <c r="F33" t="n">
         <v>106.05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-28-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2594</v>
+      </c>
+      <c r="F34" t="n">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-28-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F35" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-28-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3036</v>
+      </c>
+      <c r="F36" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-28-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4136</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-28-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>84</v>
+      </c>
+      <c r="F38" t="n">
+        <v>135.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-28-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>99</v>
+      </c>
+      <c r="F39" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-28-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>113</v>
+      </c>
+      <c r="F40" t="n">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-28-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>605</v>
+      </c>
+      <c r="F41" t="n">
+        <v>106.95</v>
       </c>
     </row>
   </sheetData>
@@ -1824,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2839,6 +3139,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-27-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3191</v>
+      </c>
+      <c r="G26" t="n">
+        <v>39.369675</v>
+      </c>
+      <c r="H26" t="n">
+        <v>125628.632925</v>
+      </c>
+      <c r="I26" t="n">
+        <v>107.412481150875</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-27-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2721</v>
+      </c>
+      <c r="G27" t="n">
+        <v>46.92345</v>
+      </c>
+      <c r="H27" t="n">
+        <v>127678.70745</v>
+      </c>
+      <c r="I27" t="n">
+        <v>109.16529486975</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-27-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3765</v>
+      </c>
+      <c r="G28" t="n">
+        <v>33.51674999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>126190.56375</v>
+      </c>
+      <c r="I28" t="n">
+        <v>107.89293200625</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-27-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5013</v>
+      </c>
+      <c r="G29" t="n">
+        <v>25.11255</v>
+      </c>
+      <c r="H29" t="n">
+        <v>125889.21315</v>
+      </c>
+      <c r="I29" t="n">
+        <v>107.63527724325</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-27-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>170</v>
+      </c>
+      <c r="G30" t="n">
+        <v>136.068</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23131.56</v>
+      </c>
+      <c r="I30" t="n">
+        <v>19.7774838</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-27-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>199</v>
+      </c>
+      <c r="G31" t="n">
+        <v>115.55775</v>
+      </c>
+      <c r="H31" t="n">
+        <v>22995.99225</v>
+      </c>
+      <c r="I31" t="n">
+        <v>19.66157337375</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-27-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>227</v>
+      </c>
+      <c r="G32" t="n">
+        <v>101.55075</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23052.02025</v>
+      </c>
+      <c r="I32" t="n">
+        <v>19.70947731375</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-27-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>251</v>
+      </c>
+      <c r="G33" t="n">
+        <v>107.15355</v>
+      </c>
+      <c r="H33" t="n">
+        <v>26895.54105</v>
+      </c>
+      <c r="I33" t="n">
+        <v>22.99568759775</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,67 @@
       </c>
       <c r="Q6" t="n">
         <v>0.0586869355352179</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-31T16:18:59.744314+00:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1999055418320601</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.1939901650674131</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.0059153767646472</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7950658232334912</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1360668595342115</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0688673172322973</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7950658232334912</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1360668595342115</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0688673172322973</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1085,37 @@
         <v>8</v>
       </c>
       <c r="I6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3073950.77181552</v>
+      </c>
+      <c r="C7" t="n">
+        <v>150317.7718155193</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7271963398033733</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1734042083195695</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0504989381818623</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1235752112659109</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1038,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2111,6 +2203,214 @@
       </c>
       <c r="F41" t="n">
         <v>106.95</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>946</v>
+      </c>
+      <c r="F42" t="n">
+        <v>41.35</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>805</v>
+      </c>
+      <c r="F43" t="n">
+        <v>48.55</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F44" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1531</v>
+      </c>
+      <c r="F45" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>210</v>
+      </c>
+      <c r="F46" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>247</v>
+      </c>
+      <c r="F47" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-31-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>284</v>
+      </c>
+      <c r="F48" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-31-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>50</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>398</v>
+      </c>
+      <c r="F49" t="n">
+        <v>106.25</v>
       </c>
     </row>
   </sheetData>
@@ -2124,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3459,6 +3759,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-28-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2594</v>
+      </c>
+      <c r="G34" t="n">
+        <v>40.270125</v>
+      </c>
+      <c r="H34" t="n">
+        <v>104460.70425</v>
+      </c>
+      <c r="I34" t="n">
+        <v>89.31390213374999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-28-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2166</v>
+      </c>
+      <c r="G35" t="n">
+        <v>47.92395</v>
+      </c>
+      <c r="H35" t="n">
+        <v>103803.2757</v>
+      </c>
+      <c r="I35" t="n">
+        <v>88.7518007235</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-28-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3036</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.31715</v>
+      </c>
+      <c r="H36" t="n">
+        <v>104186.8674</v>
+      </c>
+      <c r="I36" t="n">
+        <v>89.07977162699999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-28-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>4136</v>
+      </c>
+      <c r="G37" t="n">
+        <v>25.262625</v>
+      </c>
+      <c r="H37" t="n">
+        <v>104486.217</v>
+      </c>
+      <c r="I37" t="n">
+        <v>89.33571553500001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-28-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>84</v>
+      </c>
+      <c r="G38" t="n">
+        <v>135.932</v>
+      </c>
+      <c r="H38" t="n">
+        <v>11418.288</v>
+      </c>
+      <c r="I38" t="n">
+        <v>44.01750024</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-28-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>99</v>
+      </c>
+      <c r="G39" t="n">
+        <v>114.9425</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11379.3075</v>
+      </c>
+      <c r="I39" t="n">
+        <v>43.8672304125</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-28-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>113</v>
+      </c>
+      <c r="G40" t="n">
+        <v>99.7501</v>
+      </c>
+      <c r="H40" t="n">
+        <v>11271.7613</v>
+      </c>
+      <c r="I40" t="n">
+        <v>43.4526398115</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-28-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>605</v>
+      </c>
+      <c r="G41" t="n">
+        <v>105.6528</v>
+      </c>
+      <c r="H41" t="n">
+        <v>63919.94399999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>54.65155211999999</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,6 +870,67 @@
       </c>
       <c r="Q7" t="n">
         <v>0.0688673172322973</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-01T13:39:07.022522+00:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.192813119991758</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.3592910028920227</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1664778829002648</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8102122555763976</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1094325495821297</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.08035519484147249</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.8102122555763976</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1094325495821297</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.08035519484147249</v>
       </c>
     </row>
   </sheetData>
@@ -883,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,6 +1177,37 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3097147.200387727</v>
+      </c>
+      <c r="C8" t="n">
+        <v>42703.85038772734</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7769544501142062</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1441625053998415</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06509492024620619</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0832480358751697</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1130,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2503,214 @@
       </c>
       <c r="F49" t="n">
         <v>106.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>460</v>
+      </c>
+      <c r="F50" t="n">
+        <v>41.95</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>398</v>
+      </c>
+      <c r="F51" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>537</v>
+      </c>
+      <c r="F52" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>754</v>
+      </c>
+      <c r="F53" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-01-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>197</v>
+      </c>
+      <c r="F54" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-01-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>232</v>
+      </c>
+      <c r="F55" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>266</v>
+      </c>
+      <c r="F56" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>50</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>326</v>
+      </c>
+      <c r="F57" t="n">
+        <v>108.45</v>
       </c>
     </row>
   </sheetData>
@@ -2424,7 +2724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4079,6 +4379,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>946</v>
+      </c>
+      <c r="G42" t="n">
+        <v>40.82039999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>38616.0984</v>
+      </c>
+      <c r="I42" t="n">
+        <v>33.01676413199999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>805</v>
+      </c>
+      <c r="G43" t="n">
+        <v>48.2241</v>
+      </c>
+      <c r="H43" t="n">
+        <v>38820.4005</v>
+      </c>
+      <c r="I43" t="n">
+        <v>33.1914424275</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1108</v>
+      </c>
+      <c r="G44" t="n">
+        <v>35.067525</v>
+      </c>
+      <c r="H44" t="n">
+        <v>38854.81769999999</v>
+      </c>
+      <c r="I44" t="n">
+        <v>33.2208691335</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1336</v>
+      </c>
+      <c r="G45" t="n">
+        <v>25.362675</v>
+      </c>
+      <c r="H45" t="n">
+        <v>33884.5338</v>
+      </c>
+      <c r="I45" t="n">
+        <v>28.971276399</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>210</v>
+      </c>
+      <c r="G46" t="n">
+        <v>135.932</v>
+      </c>
+      <c r="H46" t="n">
+        <v>28545.72</v>
+      </c>
+      <c r="I46" t="n">
+        <v>110.0437506</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>247</v>
+      </c>
+      <c r="G47" t="n">
+        <v>114.9425</v>
+      </c>
+      <c r="H47" t="n">
+        <v>28390.7975</v>
+      </c>
+      <c r="I47" t="n">
+        <v>109.4465243625</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-31-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>284</v>
+      </c>
+      <c r="G48" t="n">
+        <v>100.44975</v>
+      </c>
+      <c r="H48" t="n">
+        <v>28527.729</v>
+      </c>
+      <c r="I48" t="n">
+        <v>109.974395295</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-31-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>50</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>398</v>
+      </c>
+      <c r="G49" t="n">
+        <v>106.55325</v>
+      </c>
+      <c r="H49" t="n">
+        <v>42408.1935</v>
+      </c>
+      <c r="I49" t="n">
+        <v>36.25900544249999</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,6 +931,67 @@
       </c>
       <c r="Q8" t="n">
         <v>0.08035519484147249</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-02T12:53:57.958862+00:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5151382930315769</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.4396423302787564</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.07549596275282</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8277630293518449</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.08939888677085341</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0828380838773016</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8277630293518449</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.08939888677085341</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0828380838773016</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1269,37 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3141313.603368688</v>
+      </c>
+      <c r="C9" t="n">
+        <v>44998.70336868785</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7936938856809116</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1176945528786186</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0742867568999641</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.07091613675603591</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1222,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2711,6 +2803,214 @@
       </c>
       <c r="F57" t="n">
         <v>108.45</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>466</v>
+      </c>
+      <c r="F58" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>409</v>
+      </c>
+      <c r="F59" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>553</v>
+      </c>
+      <c r="F60" t="n">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>762</v>
+      </c>
+      <c r="F61" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-02-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>161</v>
+      </c>
+      <c r="F62" t="n">
+        <v>137.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-02-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>191</v>
+      </c>
+      <c r="F63" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>216</v>
+      </c>
+      <c r="F64" t="n">
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>50</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>188</v>
+      </c>
+      <c r="F65" t="n">
+        <v>106.8</v>
       </c>
     </row>
   </sheetData>
@@ -2724,7 +3024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4699,6 +4999,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>460</v>
+      </c>
+      <c r="G50" t="n">
+        <v>41.970975</v>
+      </c>
+      <c r="H50" t="n">
+        <v>19306.6485</v>
+      </c>
+      <c r="I50" t="n">
+        <v>16.5071844675</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>398</v>
+      </c>
+      <c r="G51" t="n">
+        <v>48.274125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>19213.10175</v>
+      </c>
+      <c r="I51" t="n">
+        <v>16.42720199625</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>116</v>
+      </c>
+      <c r="G52" t="n">
+        <v>35.567775</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4125.8619</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3.5276119245</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>25.6128</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-01-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>197</v>
+      </c>
+      <c r="G54" t="n">
+        <v>136.43175</v>
+      </c>
+      <c r="H54" t="n">
+        <v>26877.05475</v>
+      </c>
+      <c r="I54" t="n">
+        <v>103.61104606125</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-01-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>232</v>
+      </c>
+      <c r="G55" t="n">
+        <v>115.44225</v>
+      </c>
+      <c r="H55" t="n">
+        <v>26782.602</v>
+      </c>
+      <c r="I55" t="n">
+        <v>103.24693071</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>266</v>
+      </c>
+      <c r="G56" t="n">
+        <v>100.44975</v>
+      </c>
+      <c r="H56" t="n">
+        <v>26719.6335</v>
+      </c>
+      <c r="I56" t="n">
+        <v>103.0041871425</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>326</v>
+      </c>
+      <c r="G57" t="n">
+        <v>107.55375</v>
+      </c>
+      <c r="H57" t="n">
+        <v>35062.5225</v>
+      </c>
+      <c r="I57" t="n">
+        <v>29.9784567375</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,6 +992,67 @@
       </c>
       <c r="Q9" t="n">
         <v>0.0828380838773016</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-03T12:58:11.767991+00:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7141563346579127</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.1583385712994003</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.5558177633585124</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8511761803803315</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.075590700795655</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0732331188240134</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8511761803803315</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.075590700795655</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.0732331188240134</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1300,6 +1361,37 @@
         <v>8</v>
       </c>
       <c r="I9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3187508.279090027</v>
+      </c>
+      <c r="C10" t="n">
+        <v>46031.52909002699</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8103781775078001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.09611802485653929</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0790625711165038</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0671547792259061</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1314,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3011,6 +3103,214 @@
       </c>
       <c r="F65" t="n">
         <v>106.8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>561</v>
+      </c>
+      <c r="F66" t="n">
+        <v>43.45</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>483</v>
+      </c>
+      <c r="F67" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-03-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>661</v>
+      </c>
+      <c r="F68" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-03-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>913</v>
+      </c>
+      <c r="F69" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-03-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>118</v>
+      </c>
+      <c r="F70" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-03-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>138</v>
+      </c>
+      <c r="F71" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>158</v>
+      </c>
+      <c r="F72" t="n">
+        <v>103.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-03-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>50</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>131</v>
+      </c>
+      <c r="F73" t="n">
+        <v>106.2</v>
       </c>
     </row>
   </sheetData>
@@ -3024,7 +3324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5319,6 +5619,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>466</v>
+      </c>
+      <c r="G58" t="n">
+        <v>42.92144999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>20001.3957</v>
+      </c>
+      <c r="I58" t="n">
+        <v>17.1011933235</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>409</v>
+      </c>
+      <c r="G59" t="n">
+        <v>49.0245</v>
+      </c>
+      <c r="H59" t="n">
+        <v>20051.0205</v>
+      </c>
+      <c r="I59" t="n">
+        <v>17.1436225275</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>135</v>
+      </c>
+      <c r="G60" t="n">
+        <v>36.268125</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4896.196875</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4.186248328124999</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>26.31315</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-02-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>161</v>
+      </c>
+      <c r="G62" t="n">
+        <v>137.43125</v>
+      </c>
+      <c r="H62" t="n">
+        <v>22126.43125</v>
+      </c>
+      <c r="I62" t="n">
+        <v>85.29739246875</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-02-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>191</v>
+      </c>
+      <c r="G63" t="n">
+        <v>115.942</v>
+      </c>
+      <c r="H63" t="n">
+        <v>22144.922</v>
+      </c>
+      <c r="I63" t="n">
+        <v>85.36867431</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>216</v>
+      </c>
+      <c r="G64" t="n">
+        <v>102.44875</v>
+      </c>
+      <c r="H64" t="n">
+        <v>22128.93</v>
+      </c>
+      <c r="I64" t="n">
+        <v>85.30702515</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>50</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>188</v>
+      </c>
+      <c r="G65" t="n">
+        <v>106.95345</v>
+      </c>
+      <c r="H65" t="n">
+        <v>20107.2486</v>
+      </c>
+      <c r="I65" t="n">
+        <v>17.191697553</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,67 @@
       </c>
       <c r="Q10" t="n">
         <v>0.0732331188240134</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:51:38.333247+00:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5606006159819014</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.4862463305497926</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.0743542854321087</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8585936761335421</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.06398431510992859</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0774220087565291</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8585936761335421</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.06398431510992859</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0774220087565291</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,6 +1453,37 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3194823.798168697</v>
+      </c>
+      <c r="C11" t="n">
+        <v>62637.89816869749</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8240567450101933</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.08061727853274241</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0757199192452072</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0528719840574844</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1406,7 +1498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3311,6 +3403,214 @@
       </c>
       <c r="F73" t="n">
         <v>106.2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>470</v>
+      </c>
+      <c r="F74" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>417</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.55</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>554</v>
+      </c>
+      <c r="F76" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>776</v>
+      </c>
+      <c r="F77" t="n">
+        <v>26.65</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>96</v>
+      </c>
+      <c r="F78" t="n">
+        <v>137.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-04-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>112</v>
+      </c>
+      <c r="F79" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>127</v>
+      </c>
+      <c r="F80" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-04-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>50</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>37</v>
+      </c>
+      <c r="F81" t="n">
+        <v>107.9</v>
       </c>
     </row>
   </sheetData>
@@ -3324,7 +3624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5939,6 +6239,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>561</v>
+      </c>
+      <c r="G66" t="n">
+        <v>43.771875</v>
+      </c>
+      <c r="H66" t="n">
+        <v>24556.021875</v>
+      </c>
+      <c r="I66" t="n">
+        <v>20.995398703125</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>421</v>
+      </c>
+      <c r="G67" t="n">
+        <v>50.8254</v>
+      </c>
+      <c r="H67" t="n">
+        <v>21397.4934</v>
+      </c>
+      <c r="I67" t="n">
+        <v>18.294856857</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-03-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>36.968475</v>
+      </c>
+      <c r="H68" t="n">
+        <v>36.968475</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.031608046125</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-03-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>26.71335</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-03-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>118</v>
+      </c>
+      <c r="G70" t="n">
+        <v>137.931</v>
+      </c>
+      <c r="H70" t="n">
+        <v>16275.858</v>
+      </c>
+      <c r="I70" t="n">
+        <v>62.74343259</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-03-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>138</v>
+      </c>
+      <c r="G71" t="n">
+        <v>117.44125</v>
+      </c>
+      <c r="H71" t="n">
+        <v>16206.8925</v>
+      </c>
+      <c r="I71" t="n">
+        <v>62.4775705875</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>158</v>
+      </c>
+      <c r="G72" t="n">
+        <v>102.9485</v>
+      </c>
+      <c r="H72" t="n">
+        <v>16265.863</v>
+      </c>
+      <c r="I72" t="n">
+        <v>62.704901865</v>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-03-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>50</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>131</v>
+      </c>
+      <c r="G73" t="n">
+        <v>107.64615</v>
+      </c>
+      <c r="H73" t="n">
+        <v>14101.64565</v>
+      </c>
+      <c r="I73" t="n">
+        <v>26.15855268075</v>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,6 +1114,67 @@
       </c>
       <c r="Q11" t="n">
         <v>0.0774220087565291</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:23:35.762729+00:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5647956918720182</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.6193189542229363</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0545232623509175</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8584151489712601</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0643413658172912</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0772434852114485</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8584151489712601</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0643413658172912</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0772434852114485</v>
       </c>
     </row>
   </sheetData>
@@ -1127,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,6 +1237,31 @@
           <t>fills_processed</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>exact_t1_ok</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>same_bar_fills</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>e22_version</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>e22_cash_credit</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>e22_stock_shares_added</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1207,6 +1293,11 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1238,6 +1329,11 @@
       <c r="I3" t="n">
         <v>8</v>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1269,6 +1365,11 @@
       <c r="I4" t="n">
         <v>8</v>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1300,6 +1401,11 @@
       <c r="I5" t="n">
         <v>8</v>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1331,6 +1437,11 @@
       <c r="I6" t="n">
         <v>8</v>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1362,6 +1473,11 @@
       <c r="I7" t="n">
         <v>8</v>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1393,6 +1509,11 @@
       <c r="I8" t="n">
         <v>8</v>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1424,6 +1545,11 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1455,6 +1581,11 @@
       <c r="I10" t="n">
         <v>8</v>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1485,6 +1616,59 @@
       </c>
       <c r="I11" t="n">
         <v>8</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3207833.072464916</v>
+      </c>
+      <c r="C12" t="n">
+        <v>35577.32246491587</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8434396643716229</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.06739128723861119</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0780782834836052</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0188602042931139</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3624,7 +3808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6559,6 +6743,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>470</v>
+      </c>
+      <c r="G74" t="n">
+        <v>44.72235</v>
+      </c>
+      <c r="H74" t="n">
+        <v>21019.5045</v>
+      </c>
+      <c r="I74" t="n">
+        <v>17.9716763475</v>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>417</v>
+      </c>
+      <c r="G75" t="n">
+        <v>50.4252</v>
+      </c>
+      <c r="H75" t="n">
+        <v>21027.3084</v>
+      </c>
+      <c r="I75" t="n">
+        <v>17.978348682</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>540</v>
+      </c>
+      <c r="G76" t="n">
+        <v>38.019</v>
+      </c>
+      <c r="H76" t="n">
+        <v>20530.26</v>
+      </c>
+      <c r="I76" t="n">
+        <v>17.5533723</v>
+      </c>
+      <c r="J76" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>26.763375</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>96</v>
+      </c>
+      <c r="G78" t="n">
+        <v>138.43075</v>
+      </c>
+      <c r="H78" t="n">
+        <v>13289.352</v>
+      </c>
+      <c r="I78" t="n">
+        <v>51.23045196000001</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-04-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>112</v>
+      </c>
+      <c r="G79" t="n">
+        <v>117.941</v>
+      </c>
+      <c r="H79" t="n">
+        <v>13209.392</v>
+      </c>
+      <c r="I79" t="n">
+        <v>50.92220616</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>127</v>
+      </c>
+      <c r="G80" t="n">
+        <v>104.44775</v>
+      </c>
+      <c r="H80" t="n">
+        <v>13264.86425</v>
+      </c>
+      <c r="I80" t="n">
+        <v>51.13605168375</v>
+      </c>
+      <c r="J80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-04-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>50</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>37</v>
+      </c>
+      <c r="G81" t="n">
+        <v>109.104525</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4036.867425</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3.451521648375</v>
+      </c>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,87 +432,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>generated_at_utc</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>data_max_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>score_financial</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>score_telecom</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>score_0050</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>e19_points</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>e19_alert</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>e20_confirmations</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>e20_streak</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>e16_financial</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>e16_telecom</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>e16_0050</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>e20_financial</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>e20_telecom</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>e20_0050</t>
         </is>
@@ -514,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24T23:53:34.871433+00:00</t>
+          <t>2026-09-07T15:10:43.719139+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -549,22 +561,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6586994624763109</v>
+        <v>0.6586994606191088</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3074378487744298</v>
+        <v>0.3074378163576171</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0338626887492592</v>
+        <v>0.033862723023274</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6586994624763109</v>
+        <v>0.6586994606191088</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3074378487744298</v>
+        <v>0.3074378163576171</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0338626887492592</v>
+        <v>0.033862723023274</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +587,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25T09:08:26.098645+00:00</t>
+          <t>2026-09-07T15:10:44.416968+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -610,22 +622,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6586994624763109</v>
+        <v>0.6586994606191088</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3074378487744298</v>
+        <v>0.3074378163576171</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0338626887492592</v>
+        <v>0.033862723023274</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6586994624763109</v>
+        <v>0.6586994606191088</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3074378487744298</v>
+        <v>0.3074378163576171</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0338626887492592</v>
+        <v>0.033862723023274</v>
       </c>
     </row>
     <row r="4">
@@ -636,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26T09:11:55.106026+00:00</t>
+          <t>2026-09-07T15:10:45.137932+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -671,22 +683,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7102101104062843</v>
+        <v>0.7102101090133827</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2530927547424653</v>
+        <v>0.2530927304298557</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0366971348512503</v>
+        <v>0.0366971605567614</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7102101104062843</v>
+        <v>0.7102101090133827</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2530927547424653</v>
+        <v>0.2530927304298557</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0366971348512503</v>
+        <v>0.0366971605567614</v>
       </c>
     </row>
     <row r="5">
@@ -697,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27T19:13:28.536995+00:00</t>
+          <t>2026-09-07T15:10:45.845928+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -732,22 +744,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7478820956458789</v>
+        <v>0.7478820946012026</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2127714709141795</v>
+        <v>0.2127714526797224</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0393464334399415</v>
+        <v>0.0393464527190748</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7478820956458789</v>
+        <v>0.7478820946012026</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2127714709141795</v>
+        <v>0.2127714526797224</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0393464334399415</v>
+        <v>0.0393464527190748</v>
       </c>
     </row>
     <row r="6">
@@ -758,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28T20:19:58.018078+00:00</t>
+          <t>2026-09-07T15:10:46.531553+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -793,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7700909129169196</v>
+        <v>0.7700909121334123</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1712221515478624</v>
+        <v>0.1712221378720195</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0586869355352179</v>
+        <v>0.0586869499945679</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7700909129169196</v>
+        <v>0.7700909121334123</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1712221515478624</v>
+        <v>0.1712221378720195</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0586869355352179</v>
+        <v>0.0586869499945679</v>
       </c>
     </row>
     <row r="7">
@@ -819,7 +831,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31T16:18:59.744314+00:00</t>
+          <t>2026-09-07T15:10:47.223052+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -854,22 +866,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7950658232334912</v>
+        <v>0.7950658226458608</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1360668595342115</v>
+        <v>0.1360668492773293</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0688673172322973</v>
+        <v>0.0688673280768098</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7950658232334912</v>
+        <v>0.7950658226458608</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1360668595342115</v>
+        <v>0.1360668492773293</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0688673172322973</v>
+        <v>0.0688673280768098</v>
       </c>
     </row>
     <row r="8">
@@ -880,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01T13:39:07.022522+00:00</t>
+          <t>2026-09-07T15:10:47.907541+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -915,22 +927,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8102122555763976</v>
+        <v>0.8101534576014104</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1094325495821297</v>
+        <v>0.109550136957997</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08035519484147249</v>
+        <v>0.08029640544059249</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8102122555763976</v>
+        <v>0.8101534576014104</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1094325495821297</v>
+        <v>0.109550136957997</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08035519484147249</v>
+        <v>0.08029640544059249</v>
       </c>
     </row>
     <row r="9">
@@ -941,7 +953,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02T12:53:57.958862+00:00</t>
+          <t>2026-09-07T15:10:48.598052+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -976,22 +988,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8277630293518449</v>
+        <v>0.8276311681627325</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08939888677085341</v>
+        <v>0.0896626027184977</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0828380838773016</v>
+        <v>0.0827062291187696</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8277630293518449</v>
+        <v>0.8276311681627325</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08939888677085341</v>
+        <v>0.0896626027184977</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0828380838773016</v>
+        <v>0.0827062291187696</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03T12:58:11.767991+00:00</t>
+          <t>2026-09-07T15:10:49.285157+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1037,22 +1049,22 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8511761803803315</v>
+        <v>0.8510772844884973</v>
       </c>
       <c r="M10" t="n">
-        <v>0.075590700795655</v>
+        <v>0.0757884877563883</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0732331188240134</v>
+        <v>0.0731342277551144</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8511761803803315</v>
+        <v>0.8510772844884973</v>
       </c>
       <c r="P10" t="n">
-        <v>0.075590700795655</v>
+        <v>0.0757884877563883</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0732331188240134</v>
+        <v>0.0731342277551144</v>
       </c>
     </row>
     <row r="11">
@@ -1063,7 +1075,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-04T12:51:38.333247+00:00</t>
+          <t>2026-09-07T15:10:49.965837+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1098,22 +1110,22 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8585936761335421</v>
+        <v>0.8584151489712601</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06398431510992859</v>
+        <v>0.0643413658172912</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0774220087565291</v>
+        <v>0.0772434852114485</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8585936761335421</v>
+        <v>0.8584151489712601</v>
       </c>
       <c r="P11" t="n">
-        <v>0.06398431510992859</v>
+        <v>0.0643413658172912</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0774220087565291</v>
+        <v>0.0772434852114485</v>
       </c>
     </row>
     <row r="12">
@@ -1124,7 +1136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07T14:23:35.762729+00:00</t>
+          <t>2026-09-07T15:10:50.634519+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1192,72 +1204,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>nav_e16_e18</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pre_financial</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pre_telecom</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pre_0050</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>target_l1_gap</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>orders_created</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fills_processed</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>exact_t1_ok</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>same_bar_fills</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>e22_version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>e22_cash_credit</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>e22_stock_shares_added</t>
         </is>
@@ -1293,11 +1305,23 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1321,7 +1345,7 @@
         <v>0.0067783498195663</v>
       </c>
       <c r="G3" t="n">
-        <v>0.799138795950194</v>
+        <v>0.7991387959501939</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -1329,11 +1353,23 @@
       <c r="I3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1342,7 +1378,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2997580.922685131</v>
+        <v>2997580.92268513</v>
       </c>
       <c r="C4" t="n">
         <v>1800948.622685131</v>
@@ -1357,7 +1393,7 @@
         <v>0.0137781101045318</v>
       </c>
       <c r="G4" t="n">
-        <v>0.600800668651141</v>
+        <v>0.6008006686511409</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -1365,11 +1401,23 @@
       <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1384,7 +1432,7 @@
         <v>1199624.374510478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4110521402160386</v>
+        <v>0.4110521402160387</v>
       </c>
       <c r="E5" t="n">
         <v>0.1664075951722332</v>
@@ -1393,7 +1441,7 @@
         <v>0.0214516686520503</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4010885959596778</v>
+        <v>0.4010885959596775</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -1401,11 +1449,23 @@
       <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1417,7 +1477,7 @@
         <v>3031940.393478123</v>
       </c>
       <c r="C6" t="n">
-        <v>597647.8934781225</v>
+        <v>597647.8934781223</v>
       </c>
       <c r="D6" t="n">
         <v>0.5863678269613146</v>
@@ -1429,7 +1489,7 @@
         <v>0.0301949207830495</v>
       </c>
       <c r="G6" t="n">
-        <v>0.227312904926573</v>
+        <v>0.2273129322782586</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -1437,11 +1497,23 @@
       <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1450,22 +1522,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3073950.77181552</v>
+        <v>3073950.771815519</v>
       </c>
       <c r="C7" t="n">
-        <v>150317.7718155193</v>
+        <v>150317.771815519</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7271963398033733</v>
+        <v>0.7271963398033734</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1734042083195695</v>
+        <v>0.1734042083195696</v>
       </c>
       <c r="F7" t="n">
         <v>0.0504989381818623</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1235752112659109</v>
+        <v>0.123575231779675</v>
       </c>
       <c r="H7" t="n">
         <v>8</v>
@@ -1473,11 +1545,23 @@
       <c r="I7" t="n">
         <v>8</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1486,22 +1570,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3097147.200387727</v>
+        <v>3097189.250170738</v>
       </c>
       <c r="C8" t="n">
-        <v>42703.85038772734</v>
+        <v>37753.90017073768</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7769544501142062</v>
+        <v>0.7785556855678325</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1441625053998415</v>
+        <v>0.1441605481406686</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06509492024620619</v>
+        <v>0.06509403646835139</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0832480358751697</v>
+        <v>0.0814105521884906</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -1509,11 +1593,23 @@
       <c r="I8" t="n">
         <v>8</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1522,22 +1618,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3141313.603368688</v>
+        <v>3142192.724419985</v>
       </c>
       <c r="C9" t="n">
-        <v>44998.70336868785</v>
+        <v>9573.074419985664</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7936938856809116</v>
+        <v>0.8050271488254839</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1176945528786186</v>
+        <v>0.1176942448901712</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0742867568999641</v>
+        <v>0.07423198398597761</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07091613675603591</v>
+        <v>0.059109906641714</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -1545,11 +1641,23 @@
       <c r="I9" t="n">
         <v>8</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1558,22 +1666,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3187508.279090027</v>
+        <v>3189013.648480112</v>
       </c>
       <c r="C10" t="n">
-        <v>46031.52909002699</v>
+        <v>2016.348480111796</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8103781775078001</v>
+        <v>0.8241550804439559</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09611802485653929</v>
+        <v>0.0962872956490311</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0790625711165038</v>
+        <v>0.0789253442423985</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0671547792259061</v>
+        <v>0.0532121284244682</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
@@ -1581,11 +1689,23 @@
       <c r="I10" t="n">
         <v>8</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1594,22 +1714,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3194823.798168697</v>
+        <v>3196751.022288824</v>
       </c>
       <c r="C11" t="n">
-        <v>62637.89816869749</v>
+        <v>19.32228882430718</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8240567450101933</v>
+        <v>0.8435715453589542</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08061727853274241</v>
+        <v>0.0808156463230055</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0757199192452072</v>
+        <v>0.07560676396591851</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0528719840574844</v>
+        <v>0.0329546053635502</v>
       </c>
       <c r="H11" t="n">
         <v>8</v>
@@ -1617,11 +1737,23 @@
       <c r="I11" t="n">
         <v>8</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1630,22 +1762,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3207833.072464916</v>
+        <v>3209456.571991</v>
       </c>
       <c r="C12" t="n">
-        <v>35577.32246491587</v>
+        <v>10.77199099981408</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8434396643716229</v>
+        <v>0.8543491206360181</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06739128723861119</v>
+        <v>0.0677114630235318</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0780782834836052</v>
+        <v>0.0779360600118135</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0188602042931139</v>
+        <v>0.0081287003418476</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1686,32 +1818,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>reference_close</t>
         </is>
@@ -1720,7 +1852,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1729,7 +1861,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1737,16 +1869,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2517</v>
+        <v>195</v>
       </c>
       <c r="F2" t="n">
-        <v>39.25</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1755,7 +1887,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1763,16 +1895,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2108</v>
+        <v>450</v>
       </c>
       <c r="F3" t="n">
-        <v>46.85</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1781,7 +1913,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1789,16 +1921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2945</v>
+        <v>2517</v>
       </c>
       <c r="F4" t="n">
-        <v>33.55</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1807,7 +1939,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1815,16 +1947,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3952</v>
+        <v>2108</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1833,7 +1965,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1841,10 +1973,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>450</v>
+        <v>2945</v>
       </c>
       <c r="F6" t="n">
-        <v>136.5</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="7">
@@ -1902,7 +2034,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24-0050-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1911,7 +2043,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1919,16 +2051,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>195</v>
+        <v>3952</v>
       </c>
       <c r="F9" t="n">
-        <v>103.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1937,7 +2069,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1945,16 +2077,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2484</v>
+        <v>195</v>
       </c>
       <c r="F10" t="n">
-        <v>39.8</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1963,7 +2095,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1971,16 +2103,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2104</v>
+        <v>451</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1989,7 +2121,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1997,16 +2129,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2925</v>
+        <v>2484</v>
       </c>
       <c r="F12" t="n">
-        <v>33.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2015,7 +2147,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,16 +2155,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3947</v>
+        <v>2104</v>
       </c>
       <c r="F13" t="n">
-        <v>25.05</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2041,7 +2173,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,10 +2181,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>451</v>
+        <v>2925</v>
       </c>
       <c r="F14" t="n">
-        <v>136.5</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="15">
@@ -2110,7 +2242,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2119,7 +2251,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2127,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>195</v>
+        <v>3947</v>
       </c>
       <c r="F17" t="n">
-        <v>104.4</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2145,7 +2277,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2153,16 +2285,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>215</v>
       </c>
       <c r="F18" t="n">
-        <v>39.6</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2171,7 +2303,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2179,16 +2311,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2394</v>
+        <v>319</v>
       </c>
       <c r="F19" t="n">
-        <v>46.6</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2197,7 +2329,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2205,16 +2337,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3341</v>
+        <v>2818</v>
       </c>
       <c r="F20" t="n">
-        <v>33.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2223,7 +2355,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2231,16 +2363,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4464</v>
+        <v>2394</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2249,7 +2381,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2257,10 +2389,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>319</v>
+        <v>3341</v>
       </c>
       <c r="F22" t="n">
-        <v>136</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="23">
@@ -2318,7 +2450,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2327,7 +2459,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2335,16 +2467,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>215</v>
+        <v>4464</v>
       </c>
       <c r="F25" t="n">
-        <v>105.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2353,7 +2485,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2361,16 +2493,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3191</v>
+        <v>251</v>
       </c>
       <c r="F26" t="n">
-        <v>39.35</v>
+        <v>106.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2379,7 +2511,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2387,16 +2519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2721</v>
+        <v>170</v>
       </c>
       <c r="F27" t="n">
-        <v>46.15</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2405,7 +2537,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2413,16 +2545,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3765</v>
+        <v>3191</v>
       </c>
       <c r="F28" t="n">
-        <v>33.35</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2431,7 +2563,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2439,16 +2571,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5013</v>
+        <v>2721</v>
       </c>
       <c r="F29" t="n">
-        <v>25.05</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2457,7 +2589,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2465,10 +2597,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>170</v>
+        <v>3765</v>
       </c>
       <c r="F30" t="n">
-        <v>135.5</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="31">
@@ -2526,7 +2658,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2535,7 +2667,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2543,16 +2675,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>251</v>
+        <v>5013</v>
       </c>
       <c r="F33" t="n">
-        <v>106.05</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-28-2412-SELL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2561,24 +2693,24 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2594</v>
+        <v>84</v>
       </c>
       <c r="F34" t="n">
-        <v>40.25</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-28-3045-SELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2587,24 +2719,24 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2166</v>
+        <v>99</v>
       </c>
       <c r="F35" t="n">
-        <v>48.2</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-28-4904-SELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,24 +2745,24 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3036</v>
+        <v>113</v>
       </c>
       <c r="F36" t="n">
-        <v>34.4</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2639,7 +2771,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2647,16 +2779,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4136</v>
+        <v>605</v>
       </c>
       <c r="F37" t="n">
-        <v>25.25</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-28-2412-SELL</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2665,24 +2797,24 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>84</v>
+        <v>2594</v>
       </c>
       <c r="F38" t="n">
-        <v>135.5</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28-3045-SELL</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2691,24 +2823,24 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>99</v>
+        <v>2166</v>
       </c>
       <c r="F39" t="n">
-        <v>115.5</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28-4904-SELL</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2717,24 +2849,24 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>113</v>
+        <v>3036</v>
       </c>
       <c r="F40" t="n">
-        <v>100.5</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2743,7 +2875,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2751,16 +2883,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>605</v>
+        <v>4136</v>
       </c>
       <c r="F41" t="n">
-        <v>106.95</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-31-2412-SELL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2769,24 +2901,24 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>946</v>
+        <v>210</v>
       </c>
       <c r="F42" t="n">
-        <v>41.35</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-31-3045-SELL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2795,24 +2927,24 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>805</v>
+        <v>247</v>
       </c>
       <c r="F43" t="n">
-        <v>48.55</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-31-4904-SELL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2821,24 +2953,24 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>284</v>
       </c>
       <c r="F44" t="n">
-        <v>35.3</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-31-0050-BUY</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2847,7 +2979,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2855,16 +2987,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1531</v>
+        <v>398</v>
       </c>
       <c r="F45" t="n">
-        <v>25.55</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31-2412-SELL</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2873,24 +3005,24 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>946</v>
       </c>
       <c r="F46" t="n">
-        <v>136</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31-3045-SELL</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2899,24 +3031,24 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>247</v>
+        <v>805</v>
       </c>
       <c r="F47" t="n">
-        <v>116</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31-4904-SELL</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2925,24 +3057,24 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>284</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="n">
-        <v>101</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31-0050-BUY</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2951,7 +3083,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2959,16 +3091,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>398</v>
+        <v>1531</v>
       </c>
       <c r="F49" t="n">
-        <v>106.25</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-09-01-2412-SELL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2977,24 +3109,24 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>460</v>
+        <v>197</v>
       </c>
       <c r="F50" t="n">
-        <v>41.95</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-09-01-3045-SELL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3003,24 +3135,24 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>398</v>
+        <v>232</v>
       </c>
       <c r="F51" t="n">
-        <v>48.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-09-01-4904-SELL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3029,24 +3161,24 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>537</v>
+        <v>265</v>
       </c>
       <c r="F52" t="n">
-        <v>35.9</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-09-01-0050-BUY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3055,7 +3187,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3063,16 +3195,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>754</v>
+        <v>325</v>
       </c>
       <c r="F53" t="n">
-        <v>25.6</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01-2412-SELL</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3081,24 +3213,24 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>197</v>
+        <v>437</v>
       </c>
       <c r="F54" t="n">
-        <v>136</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01-3045-SELL</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3107,24 +3239,24 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>232</v>
+        <v>378</v>
       </c>
       <c r="F55" t="n">
-        <v>115.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-01-4904-SELL</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3133,24 +3265,24 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>266</v>
+        <v>511</v>
       </c>
       <c r="F56" t="n">
-        <v>101</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3159,7 +3291,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3167,16 +3299,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>326</v>
+        <v>716</v>
       </c>
       <c r="F57" t="n">
-        <v>108.45</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-09-02-2412-SELL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3185,24 +3317,24 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>466</v>
+        <v>160</v>
       </c>
       <c r="F58" t="n">
-        <v>43</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-09-02-3045-SELL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3211,24 +3343,24 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>409</v>
+        <v>189</v>
       </c>
       <c r="F59" t="n">
-        <v>49</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-09-02-4904-SELL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3237,24 +3369,24 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>553</v>
+        <v>214</v>
       </c>
       <c r="F60" t="n">
-        <v>36.25</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-09-02-0050-BUY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3263,7 +3395,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3271,16 +3403,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>762</v>
+        <v>186</v>
       </c>
       <c r="F61" t="n">
-        <v>26.3</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-02-2412-SELL</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3289,24 +3421,24 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="F62" t="n">
-        <v>137.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-02-3045-SELL</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3315,24 +3447,24 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="F63" t="n">
-        <v>116</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-02-4904-SELL</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3341,24 +3473,24 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>216</v>
+        <v>367</v>
       </c>
       <c r="F64" t="n">
-        <v>102.5</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-02-0050-BUY</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3367,7 +3499,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3375,16 +3507,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>188</v>
+        <v>506</v>
       </c>
       <c r="F65" t="n">
-        <v>106.8</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-09-03-0050-SELL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3393,24 +3525,24 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>561</v>
+        <v>130</v>
       </c>
       <c r="F66" t="n">
-        <v>43.45</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-09-03-2412-SELL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3419,24 +3551,24 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>483</v>
+        <v>118</v>
       </c>
       <c r="F67" t="n">
-        <v>50.4</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-09-03-3045-SELL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3445,24 +3577,24 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2892</v>
+        <v>3045</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>661</v>
+        <v>138</v>
       </c>
       <c r="F68" t="n">
-        <v>36.85</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-03-5880-BUY</t>
+          <t>2026-09-03-4904-SELL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3471,24 +3603,24 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>913</v>
+        <v>157</v>
       </c>
       <c r="F69" t="n">
-        <v>26.7</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-03-2412-SELL</t>
+          <t>2026-09-03-2880-BUY</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3497,24 +3629,24 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>118</v>
+        <v>370</v>
       </c>
       <c r="F70" t="n">
-        <v>138</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-03-3045-SELL</t>
+          <t>2026-09-03-2886-BUY</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3523,24 +3655,24 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>138</v>
+        <v>319</v>
       </c>
       <c r="F71" t="n">
-        <v>118</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-03-4904-SELL</t>
+          <t>2026-09-03-2892-BUY</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3549,24 +3681,24 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>158</v>
+        <v>436</v>
       </c>
       <c r="F72" t="n">
-        <v>103.5</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-03-0050-SELL</t>
+          <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3575,24 +3707,24 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>131</v>
+        <v>602</v>
       </c>
       <c r="F73" t="n">
-        <v>106.2</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-04-2880-BUY</t>
+          <t>2026-09-04-2412-SELL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3601,24 +3733,24 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>470</v>
+        <v>95</v>
       </c>
       <c r="F74" t="n">
-        <v>44</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-04-2886-BUY</t>
+          <t>2026-09-04-3045-SELL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3627,24 +3759,24 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>417</v>
+        <v>111</v>
       </c>
       <c r="F75" t="n">
-        <v>49.55</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-04-2892-BUY</t>
+          <t>2026-09-04-4904-SELL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3653,24 +3785,24 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>554</v>
+        <v>126</v>
       </c>
       <c r="F76" t="n">
-        <v>37.3</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-04-5880-BUY</t>
+          <t>2026-09-04-0050-BUY</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3679,7 +3811,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3687,16 +3819,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>776</v>
+        <v>36</v>
       </c>
       <c r="F77" t="n">
-        <v>26.65</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-04-2412-SELL</t>
+          <t>2026-09-04-2880-BUY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3705,24 +3837,24 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="F78" t="n">
-        <v>137.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-04-3045-SELL</t>
+          <t>2026-09-04-2886-BUY</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3731,24 +3863,24 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="F79" t="n">
-        <v>118</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-04-4904-SELL</t>
+          <t>2026-09-04-2892-BUY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3757,24 +3889,24 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="F80" t="n">
-        <v>104</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-04-0050-BUY</t>
+          <t>2026-09-04-5880-BUY</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3783,7 +3915,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3791,10 +3923,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>37</v>
+        <v>333</v>
       </c>
       <c r="F81" t="n">
-        <v>107.9</v>
+        <v>26.65</v>
       </c>
     </row>
   </sheetData>
@@ -3812,52 +3944,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fill_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>fill_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>fill_price</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gross</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fees_tax</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>slippage_bp</t>
         </is>
@@ -3866,7 +3998,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3880,7 +4012,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3888,16 +4020,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2517</v>
+        <v>195</v>
       </c>
       <c r="G2" t="n">
-        <v>39.169575</v>
+        <v>102.95145</v>
       </c>
       <c r="H2" t="n">
-        <v>98589.82027500001</v>
+        <v>20075.53275</v>
       </c>
       <c r="I2" t="n">
-        <v>84.29429633512498</v>
+        <v>17.16458050125</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -3906,7 +4038,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3920,7 +4052,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3928,16 +4060,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2108</v>
+        <v>450</v>
       </c>
       <c r="G3" t="n">
-        <v>46.873425</v>
+        <v>136.56825</v>
       </c>
       <c r="H3" t="n">
-        <v>98809.1799</v>
+        <v>61455.7125</v>
       </c>
       <c r="I3" t="n">
-        <v>84.48184881449998</v>
+        <v>52.5446341875</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -3946,7 +4078,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3960,7 +4092,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3968,16 +4100,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2945</v>
+        <v>2517</v>
       </c>
       <c r="G4" t="n">
-        <v>33.51674999999999</v>
+        <v>39.169575</v>
       </c>
       <c r="H4" t="n">
-        <v>98706.82875</v>
+        <v>98589.82027500001</v>
       </c>
       <c r="I4" t="n">
-        <v>84.39433858124998</v>
+        <v>84.29429633512498</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -3986,7 +4118,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4000,7 +4132,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4008,16 +4140,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3952</v>
+        <v>2108</v>
       </c>
       <c r="G5" t="n">
-        <v>25.0125</v>
+        <v>46.873425</v>
       </c>
       <c r="H5" t="n">
-        <v>98849.39999999999</v>
+        <v>98809.1799</v>
       </c>
       <c r="I5" t="n">
-        <v>84.51623699999999</v>
+        <v>84.48184881449998</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -4026,7 +4158,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4040,7 +4172,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4048,16 +4180,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>450</v>
+        <v>2945</v>
       </c>
       <c r="G6" t="n">
-        <v>136.56825</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>61455.7125</v>
+        <v>98706.82875</v>
       </c>
       <c r="I6" t="n">
-        <v>52.5446341875</v>
+        <v>84.39433858124998</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -4146,7 +4278,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24-0050-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4160,7 +4292,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4168,16 +4300,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>195</v>
+        <v>3952</v>
       </c>
       <c r="G9" t="n">
-        <v>102.95145</v>
+        <v>25.0125</v>
       </c>
       <c r="H9" t="n">
-        <v>20075.53275</v>
+        <v>98849.39999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>17.16458050125</v>
+        <v>84.51623699999999</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -4186,7 +4318,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4200,7 +4332,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4208,16 +4340,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2484</v>
+        <v>195</v>
       </c>
       <c r="G10" t="n">
-        <v>39.6198</v>
+        <v>104.15205</v>
       </c>
       <c r="H10" t="n">
-        <v>98415.58319999999</v>
+        <v>20309.64975</v>
       </c>
       <c r="I10" t="n">
-        <v>84.14532363599999</v>
+        <v>17.36475053625</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -4226,7 +4358,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4240,7 +4372,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4248,16 +4380,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2104</v>
+        <v>451</v>
       </c>
       <c r="G11" t="n">
-        <v>46.92345</v>
+        <v>136.56825</v>
       </c>
       <c r="H11" t="n">
-        <v>98726.9388</v>
+        <v>61592.28075000001</v>
       </c>
       <c r="I11" t="n">
-        <v>84.41153267399999</v>
+        <v>52.66140004125</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -4266,7 +4398,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4280,7 +4412,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4288,16 +4420,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2925</v>
+        <v>2484</v>
       </c>
       <c r="G12" t="n">
-        <v>33.51674999999999</v>
+        <v>39.6198</v>
       </c>
       <c r="H12" t="n">
-        <v>98036.49374999998</v>
+        <v>98415.58319999999</v>
       </c>
       <c r="I12" t="n">
-        <v>83.82120215624998</v>
+        <v>84.14532363599999</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -4306,7 +4438,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4320,7 +4452,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4328,16 +4460,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3947</v>
+        <v>2104</v>
       </c>
       <c r="G13" t="n">
-        <v>25.0125</v>
+        <v>46.92345</v>
       </c>
       <c r="H13" t="n">
-        <v>98724.33749999999</v>
+        <v>98726.9388</v>
       </c>
       <c r="I13" t="n">
-        <v>84.40930856249999</v>
+        <v>84.41153267399999</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -4346,7 +4478,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4360,7 +4492,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4368,16 +4500,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>451</v>
+        <v>2925</v>
       </c>
       <c r="G14" t="n">
-        <v>136.56825</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>61592.28075000001</v>
+        <v>98036.49374999998</v>
       </c>
       <c r="I14" t="n">
-        <v>52.66140004125</v>
+        <v>83.82120215624998</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -4466,7 +4598,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4480,7 +4612,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4488,16 +4620,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>195</v>
+        <v>3947</v>
       </c>
       <c r="G17" t="n">
-        <v>104.15205</v>
+        <v>25.0125</v>
       </c>
       <c r="H17" t="n">
-        <v>20309.64975</v>
+        <v>98724.33749999999</v>
       </c>
       <c r="I17" t="n">
-        <v>17.36475053625</v>
+        <v>84.40930856249999</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -4506,7 +4638,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4520,7 +4652,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4528,16 +4660,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2818</v>
+        <v>215</v>
       </c>
       <c r="G18" t="n">
-        <v>39.8199</v>
+        <v>106.55325</v>
       </c>
       <c r="H18" t="n">
-        <v>112212.4782</v>
+        <v>22908.94875</v>
       </c>
       <c r="I18" t="n">
-        <v>95.941668861</v>
+        <v>19.58715118125</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -4546,7 +4678,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4560,7 +4692,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4568,16 +4700,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2394</v>
+        <v>319</v>
       </c>
       <c r="G19" t="n">
-        <v>46.6233</v>
+        <v>136.56825</v>
       </c>
       <c r="H19" t="n">
-        <v>111616.1802</v>
+        <v>43565.27175</v>
       </c>
       <c r="I19" t="n">
-        <v>95.431834071</v>
+        <v>37.24830734625</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -4586,7 +4718,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4600,7 +4732,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4608,16 +4740,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3341</v>
+        <v>2818</v>
       </c>
       <c r="G20" t="n">
-        <v>33.51674999999999</v>
+        <v>39.8199</v>
       </c>
       <c r="H20" t="n">
-        <v>111979.46175</v>
+        <v>112212.4782</v>
       </c>
       <c r="I20" t="n">
-        <v>95.74243979624998</v>
+        <v>95.941668861</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -4626,7 +4758,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4640,7 +4772,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4648,16 +4780,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4464</v>
+        <v>2394</v>
       </c>
       <c r="G21" t="n">
-        <v>25.0125</v>
+        <v>46.6233</v>
       </c>
       <c r="H21" t="n">
-        <v>111655.8</v>
+        <v>111616.1802</v>
       </c>
       <c r="I21" t="n">
-        <v>95.465709</v>
+        <v>95.431834071</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -4666,7 +4798,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4680,7 +4812,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4688,16 +4820,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>319</v>
+        <v>3341</v>
       </c>
       <c r="G22" t="n">
-        <v>136.56825</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>43565.27175</v>
+        <v>111979.46175</v>
       </c>
       <c r="I22" t="n">
-        <v>37.24830734625</v>
+        <v>95.74243979624998</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -4786,7 +4918,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4800,7 +4932,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4808,16 +4940,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>215</v>
+        <v>4464</v>
       </c>
       <c r="G25" t="n">
-        <v>106.55325</v>
+        <v>25.0125</v>
       </c>
       <c r="H25" t="n">
-        <v>22908.94875</v>
+        <v>111655.8</v>
       </c>
       <c r="I25" t="n">
-        <v>19.58715118125</v>
+        <v>95.465709</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -4826,7 +4958,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4840,7 +4972,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4848,16 +4980,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3191</v>
+        <v>251</v>
       </c>
       <c r="G26" t="n">
-        <v>39.369675</v>
+        <v>107.15355</v>
       </c>
       <c r="H26" t="n">
-        <v>125628.632925</v>
+        <v>26895.54105</v>
       </c>
       <c r="I26" t="n">
-        <v>107.412481150875</v>
+        <v>22.99568759775</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -4866,7 +4998,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4880,7 +5012,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4888,16 +5020,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2721</v>
+        <v>170</v>
       </c>
       <c r="G27" t="n">
-        <v>46.92345</v>
+        <v>136.068</v>
       </c>
       <c r="H27" t="n">
-        <v>127678.70745</v>
+        <v>23131.56</v>
       </c>
       <c r="I27" t="n">
-        <v>109.16529486975</v>
+        <v>19.7774838</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -4906,7 +5038,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4920,7 +5052,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4928,16 +5060,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3765</v>
+        <v>3191</v>
       </c>
       <c r="G28" t="n">
-        <v>33.51674999999999</v>
+        <v>39.369675</v>
       </c>
       <c r="H28" t="n">
-        <v>126190.56375</v>
+        <v>125628.632925</v>
       </c>
       <c r="I28" t="n">
-        <v>107.89293200625</v>
+        <v>107.412481150875</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -4946,7 +5078,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4960,7 +5092,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4968,16 +5100,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5013</v>
+        <v>2721</v>
       </c>
       <c r="G29" t="n">
-        <v>25.11255</v>
+        <v>46.92345</v>
       </c>
       <c r="H29" t="n">
-        <v>125889.21315</v>
+        <v>127678.70745</v>
       </c>
       <c r="I29" t="n">
-        <v>107.63527724325</v>
+        <v>109.16529486975</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -4986,7 +5118,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5000,7 +5132,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2412</v>
+        <v>2892</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5008,16 +5140,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>170</v>
+        <v>3765</v>
       </c>
       <c r="G30" t="n">
-        <v>136.068</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>23131.56</v>
+        <v>126190.56375</v>
       </c>
       <c r="I30" t="n">
-        <v>19.7774838</v>
+        <v>107.89293200625</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -5106,7 +5238,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5120,7 +5252,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5128,16 +5260,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>251</v>
+        <v>5013</v>
       </c>
       <c r="G33" t="n">
-        <v>107.15355</v>
+        <v>25.11255</v>
       </c>
       <c r="H33" t="n">
-        <v>26895.54105</v>
+        <v>125889.21315</v>
       </c>
       <c r="I33" t="n">
-        <v>22.99568759775</v>
+        <v>107.63527724325</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -5146,7 +5278,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-28-2412-SELL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5160,24 +5292,24 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2594</v>
+        <v>84</v>
       </c>
       <c r="G34" t="n">
-        <v>40.270125</v>
+        <v>135.932</v>
       </c>
       <c r="H34" t="n">
-        <v>104460.70425</v>
+        <v>11418.288</v>
       </c>
       <c r="I34" t="n">
-        <v>89.31390213374999</v>
+        <v>44.01750024</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -5186,7 +5318,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-28-3045-SELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5200,24 +5332,24 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2166</v>
+        <v>99</v>
       </c>
       <c r="G35" t="n">
-        <v>47.92395</v>
+        <v>114.9425</v>
       </c>
       <c r="H35" t="n">
-        <v>103803.2757</v>
+        <v>11379.3075</v>
       </c>
       <c r="I35" t="n">
-        <v>88.7518007235</v>
+        <v>43.8672304125</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -5226,7 +5358,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-28-4904-SELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5240,24 +5372,24 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3036</v>
+        <v>113</v>
       </c>
       <c r="G36" t="n">
-        <v>34.31715</v>
+        <v>99.7501</v>
       </c>
       <c r="H36" t="n">
-        <v>104186.8674</v>
+        <v>11271.7613</v>
       </c>
       <c r="I36" t="n">
-        <v>89.07977162699999</v>
+        <v>43.4526398115</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -5266,7 +5398,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5280,7 +5412,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5288,16 +5420,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4136</v>
+        <v>605</v>
       </c>
       <c r="G37" t="n">
-        <v>25.262625</v>
+        <v>105.6528</v>
       </c>
       <c r="H37" t="n">
-        <v>104486.217</v>
+        <v>63919.94399999999</v>
       </c>
       <c r="I37" t="n">
-        <v>89.33571553500001</v>
+        <v>54.65155211999999</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -5306,7 +5438,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-28-2412-SELL</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5320,24 +5452,24 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>84</v>
+        <v>2594</v>
       </c>
       <c r="G38" t="n">
-        <v>135.932</v>
+        <v>40.270125</v>
       </c>
       <c r="H38" t="n">
-        <v>11418.288</v>
+        <v>104460.70425</v>
       </c>
       <c r="I38" t="n">
-        <v>44.01750024</v>
+        <v>89.31390213374999</v>
       </c>
       <c r="J38" t="n">
         <v>5</v>
@@ -5346,7 +5478,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28-3045-SELL</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5360,24 +5492,24 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>99</v>
+        <v>2166</v>
       </c>
       <c r="G39" t="n">
-        <v>114.9425</v>
+        <v>47.92395</v>
       </c>
       <c r="H39" t="n">
-        <v>11379.3075</v>
+        <v>103803.2757</v>
       </c>
       <c r="I39" t="n">
-        <v>43.8672304125</v>
+        <v>88.7518007235</v>
       </c>
       <c r="J39" t="n">
         <v>5</v>
@@ -5386,7 +5518,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28-4904-SELL</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5400,24 +5532,24 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>113</v>
+        <v>3036</v>
       </c>
       <c r="G40" t="n">
-        <v>99.7501</v>
+        <v>34.31715</v>
       </c>
       <c r="H40" t="n">
-        <v>11271.7613</v>
+        <v>104186.8674</v>
       </c>
       <c r="I40" t="n">
-        <v>43.4526398115</v>
+        <v>89.07977162699999</v>
       </c>
       <c r="J40" t="n">
         <v>5</v>
@@ -5426,7 +5558,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5440,7 +5572,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5448,16 +5580,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>605</v>
+        <v>4136</v>
       </c>
       <c r="G41" t="n">
-        <v>105.6528</v>
+        <v>25.262625</v>
       </c>
       <c r="H41" t="n">
-        <v>63919.94399999999</v>
+        <v>104486.217</v>
       </c>
       <c r="I41" t="n">
-        <v>54.65155211999999</v>
+        <v>89.33571553500001</v>
       </c>
       <c r="J41" t="n">
         <v>5</v>
@@ -5466,7 +5598,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-31-2412-SELL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5480,24 +5612,24 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>946</v>
+        <v>210</v>
       </c>
       <c r="G42" t="n">
-        <v>40.82039999999999</v>
+        <v>135.932</v>
       </c>
       <c r="H42" t="n">
-        <v>38616.0984</v>
+        <v>28545.72</v>
       </c>
       <c r="I42" t="n">
-        <v>33.01676413199999</v>
+        <v>110.0437506</v>
       </c>
       <c r="J42" t="n">
         <v>5</v>
@@ -5506,7 +5638,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-31-3045-SELL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5520,24 +5652,24 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>805</v>
+        <v>247</v>
       </c>
       <c r="G43" t="n">
-        <v>48.2241</v>
+        <v>114.9425</v>
       </c>
       <c r="H43" t="n">
-        <v>38820.4005</v>
+        <v>28390.7975</v>
       </c>
       <c r="I43" t="n">
-        <v>33.1914424275</v>
+        <v>109.4465243625</v>
       </c>
       <c r="J43" t="n">
         <v>5</v>
@@ -5546,7 +5678,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-31-4904-SELL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5560,24 +5692,24 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1108</v>
+        <v>284</v>
       </c>
       <c r="G44" t="n">
-        <v>35.067525</v>
+        <v>100.44975</v>
       </c>
       <c r="H44" t="n">
-        <v>38854.81769999999</v>
+        <v>28527.729</v>
       </c>
       <c r="I44" t="n">
-        <v>33.2208691335</v>
+        <v>109.974395295</v>
       </c>
       <c r="J44" t="n">
         <v>5</v>
@@ -5586,7 +5718,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-31-0050-BUY</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5600,7 +5732,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -5608,16 +5740,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1336</v>
+        <v>398</v>
       </c>
       <c r="G45" t="n">
-        <v>25.362675</v>
+        <v>106.55325</v>
       </c>
       <c r="H45" t="n">
-        <v>33884.5338</v>
+        <v>42408.1935</v>
       </c>
       <c r="I45" t="n">
-        <v>28.971276399</v>
+        <v>36.25900544249999</v>
       </c>
       <c r="J45" t="n">
         <v>5</v>
@@ -5626,7 +5758,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31-2412-SELL</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5640,24 +5772,24 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>210</v>
+        <v>946</v>
       </c>
       <c r="G46" t="n">
-        <v>135.932</v>
+        <v>40.82039999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>28545.72</v>
+        <v>38616.0984</v>
       </c>
       <c r="I46" t="n">
-        <v>110.0437506</v>
+        <v>33.01676413199999</v>
       </c>
       <c r="J46" t="n">
         <v>5</v>
@@ -5666,7 +5798,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31-3045-SELL</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5680,24 +5812,24 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>247</v>
+        <v>805</v>
       </c>
       <c r="G47" t="n">
-        <v>114.9425</v>
+        <v>48.2241</v>
       </c>
       <c r="H47" t="n">
-        <v>28390.7975</v>
+        <v>38820.4005</v>
       </c>
       <c r="I47" t="n">
-        <v>109.4465243625</v>
+        <v>33.1914424275</v>
       </c>
       <c r="J47" t="n">
         <v>5</v>
@@ -5706,7 +5838,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31-4904-SELL</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5720,24 +5852,24 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>284</v>
+        <v>1108</v>
       </c>
       <c r="G48" t="n">
-        <v>100.44975</v>
+        <v>35.067525</v>
       </c>
       <c r="H48" t="n">
-        <v>28527.729</v>
+        <v>38854.81769999999</v>
       </c>
       <c r="I48" t="n">
-        <v>109.974395295</v>
+        <v>33.2208691335</v>
       </c>
       <c r="J48" t="n">
         <v>5</v>
@@ -5746,7 +5878,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31-0050-BUY</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5760,7 +5892,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5768,16 +5900,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>398</v>
+        <v>1531</v>
       </c>
       <c r="G49" t="n">
-        <v>106.55325</v>
+        <v>25.362675</v>
       </c>
       <c r="H49" t="n">
-        <v>42408.1935</v>
+        <v>38830.255425</v>
       </c>
       <c r="I49" t="n">
-        <v>36.25900544249999</v>
+        <v>33.19986838837499</v>
       </c>
       <c r="J49" t="n">
         <v>5</v>
@@ -5786,7 +5918,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-09-01-2412-SELL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5800,24 +5932,24 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>460</v>
+        <v>197</v>
       </c>
       <c r="G50" t="n">
-        <v>41.970975</v>
+        <v>136.43175</v>
       </c>
       <c r="H50" t="n">
-        <v>19306.6485</v>
+        <v>26877.05475</v>
       </c>
       <c r="I50" t="n">
-        <v>16.5071844675</v>
+        <v>103.61104606125</v>
       </c>
       <c r="J50" t="n">
         <v>5</v>
@@ -5826,7 +5958,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-09-01-3045-SELL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5840,24 +5972,24 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>398</v>
+        <v>232</v>
       </c>
       <c r="G51" t="n">
-        <v>48.274125</v>
+        <v>115.44225</v>
       </c>
       <c r="H51" t="n">
-        <v>19213.10175</v>
+        <v>26782.602</v>
       </c>
       <c r="I51" t="n">
-        <v>16.42720199625</v>
+        <v>103.24693071</v>
       </c>
       <c r="J51" t="n">
         <v>5</v>
@@ -5866,7 +5998,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-09-01-4904-SELL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5880,24 +6012,24 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>116</v>
+        <v>265</v>
       </c>
       <c r="G52" t="n">
-        <v>35.567775</v>
+        <v>100.44975</v>
       </c>
       <c r="H52" t="n">
-        <v>4125.8619</v>
+        <v>26619.18375</v>
       </c>
       <c r="I52" t="n">
-        <v>3.5276119245</v>
+        <v>102.61695335625</v>
       </c>
       <c r="J52" t="n">
         <v>5</v>
@@ -5906,7 +6038,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-09-01-0050-BUY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5920,7 +6052,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -5928,16 +6060,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="G53" t="n">
-        <v>25.6128</v>
+        <v>107.55375</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>34954.96875</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>29.88649828125</v>
       </c>
       <c r="J53" t="n">
         <v>5</v>
@@ -5946,7 +6078,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01-2412-SELL</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5960,24 +6092,24 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>197</v>
+        <v>437</v>
       </c>
       <c r="G54" t="n">
-        <v>136.43175</v>
+        <v>41.970975</v>
       </c>
       <c r="H54" t="n">
-        <v>26877.05475</v>
+        <v>18341.316075</v>
       </c>
       <c r="I54" t="n">
-        <v>103.61104606125</v>
+        <v>15.681825244125</v>
       </c>
       <c r="J54" t="n">
         <v>5</v>
@@ -5986,7 +6118,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01-3045-SELL</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6000,24 +6132,24 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>232</v>
+        <v>378</v>
       </c>
       <c r="G55" t="n">
-        <v>115.44225</v>
+        <v>48.274125</v>
       </c>
       <c r="H55" t="n">
-        <v>26782.602</v>
+        <v>18247.61925</v>
       </c>
       <c r="I55" t="n">
-        <v>103.24693071</v>
+        <v>15.60171445875</v>
       </c>
       <c r="J55" t="n">
         <v>5</v>
@@ -6026,7 +6158,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-01-4904-SELL</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6040,24 +6172,24 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>266</v>
+        <v>511</v>
       </c>
       <c r="G56" t="n">
-        <v>100.44975</v>
+        <v>35.567775</v>
       </c>
       <c r="H56" t="n">
-        <v>26719.6335</v>
+        <v>18175.133025</v>
       </c>
       <c r="I56" t="n">
-        <v>103.0041871425</v>
+        <v>15.539738736375</v>
       </c>
       <c r="J56" t="n">
         <v>5</v>
@@ -6066,7 +6198,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6080,7 +6212,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -6088,16 +6220,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>326</v>
+        <v>716</v>
       </c>
       <c r="G57" t="n">
-        <v>107.55375</v>
+        <v>25.6128</v>
       </c>
       <c r="H57" t="n">
-        <v>35062.5225</v>
+        <v>18338.7648</v>
       </c>
       <c r="I57" t="n">
-        <v>29.9784567375</v>
+        <v>15.679643904</v>
       </c>
       <c r="J57" t="n">
         <v>5</v>
@@ -6106,7 +6238,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-09-02-2412-SELL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6120,24 +6252,24 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>466</v>
+        <v>160</v>
       </c>
       <c r="G58" t="n">
-        <v>42.92144999999999</v>
+        <v>137.43125</v>
       </c>
       <c r="H58" t="n">
-        <v>20001.3957</v>
+        <v>21989</v>
       </c>
       <c r="I58" t="n">
-        <v>17.1011933235</v>
+        <v>84.767595</v>
       </c>
       <c r="J58" t="n">
         <v>5</v>
@@ -6146,7 +6278,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-09-02-3045-SELL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6160,24 +6292,24 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>409</v>
+        <v>189</v>
       </c>
       <c r="G59" t="n">
-        <v>49.0245</v>
+        <v>115.942</v>
       </c>
       <c r="H59" t="n">
-        <v>20051.0205</v>
+        <v>21913.038</v>
       </c>
       <c r="I59" t="n">
-        <v>17.1436225275</v>
+        <v>84.47476149000001</v>
       </c>
       <c r="J59" t="n">
         <v>5</v>
@@ -6186,7 +6318,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-09-02-4904-SELL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6200,24 +6332,24 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="G60" t="n">
-        <v>36.268125</v>
+        <v>102.44875</v>
       </c>
       <c r="H60" t="n">
-        <v>4896.196875</v>
+        <v>21924.0325</v>
       </c>
       <c r="I60" t="n">
-        <v>4.186248328124999</v>
+        <v>84.5171452875</v>
       </c>
       <c r="J60" t="n">
         <v>5</v>
@@ -6226,7 +6358,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-09-02-0050-BUY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6240,7 +6372,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -6248,16 +6380,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G61" t="n">
-        <v>26.31315</v>
+        <v>106.95345</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>19893.3417</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>17.0088071535</v>
       </c>
       <c r="J61" t="n">
         <v>5</v>
@@ -6266,7 +6398,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-02-2412-SELL</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6280,24 +6412,24 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="G62" t="n">
-        <v>137.43125</v>
+        <v>42.92144999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>22126.43125</v>
+        <v>13262.72805</v>
       </c>
       <c r="I62" t="n">
-        <v>85.29739246875</v>
+        <v>11.33963248275</v>
       </c>
       <c r="J62" t="n">
         <v>5</v>
@@ -6306,7 +6438,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-02-3045-SELL</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6320,24 +6452,24 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="G63" t="n">
-        <v>115.942</v>
+        <v>49.0245</v>
       </c>
       <c r="H63" t="n">
-        <v>22144.922</v>
+        <v>13285.6395</v>
       </c>
       <c r="I63" t="n">
-        <v>85.36867431</v>
+        <v>11.3592217725</v>
       </c>
       <c r="J63" t="n">
         <v>5</v>
@@ -6346,7 +6478,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-02-4904-SELL</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6360,24 +6492,24 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>216</v>
+        <v>367</v>
       </c>
       <c r="G64" t="n">
-        <v>102.44875</v>
+        <v>36.268125</v>
       </c>
       <c r="H64" t="n">
-        <v>22128.93</v>
+        <v>13310.401875</v>
       </c>
       <c r="I64" t="n">
-        <v>85.30702515</v>
+        <v>11.380393603125</v>
       </c>
       <c r="J64" t="n">
         <v>5</v>
@@ -6386,7 +6518,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-02-0050-BUY</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6400,7 +6532,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -6408,16 +6540,16 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>188</v>
+        <v>506</v>
       </c>
       <c r="G65" t="n">
-        <v>106.95345</v>
+        <v>26.31315</v>
       </c>
       <c r="H65" t="n">
-        <v>20107.2486</v>
+        <v>13314.4539</v>
       </c>
       <c r="I65" t="n">
-        <v>17.191697553</v>
+        <v>11.3838580845</v>
       </c>
       <c r="J65" t="n">
         <v>5</v>
@@ -6426,7 +6558,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-09-03-0050-SELL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6440,24 +6572,24 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>561</v>
+        <v>130</v>
       </c>
       <c r="G66" t="n">
-        <v>43.771875</v>
+        <v>107.64615</v>
       </c>
       <c r="H66" t="n">
-        <v>24556.021875</v>
+        <v>13993.9995</v>
       </c>
       <c r="I66" t="n">
-        <v>20.995398703125</v>
+        <v>25.9588690725</v>
       </c>
       <c r="J66" t="n">
         <v>5</v>
@@ -6466,7 +6598,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-09-03-2412-SELL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6480,24 +6612,24 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>421</v>
+        <v>118</v>
       </c>
       <c r="G67" t="n">
-        <v>50.8254</v>
+        <v>137.931</v>
       </c>
       <c r="H67" t="n">
-        <v>21397.4934</v>
+        <v>16275.858</v>
       </c>
       <c r="I67" t="n">
-        <v>18.294856857</v>
+        <v>62.74343259</v>
       </c>
       <c r="J67" t="n">
         <v>5</v>
@@ -6506,7 +6638,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-09-03-3045-SELL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6520,24 +6652,24 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2892</v>
+        <v>3045</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="G68" t="n">
-        <v>36.968475</v>
+        <v>117.44125</v>
       </c>
       <c r="H68" t="n">
-        <v>36.968475</v>
+        <v>16206.8925</v>
       </c>
       <c r="I68" t="n">
-        <v>0.031608046125</v>
+        <v>62.4775705875</v>
       </c>
       <c r="J68" t="n">
         <v>5</v>
@@ -6546,7 +6678,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-03-5880-BUY</t>
+          <t>2026-09-03-4904-SELL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6560,24 +6692,24 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="G69" t="n">
-        <v>26.71335</v>
+        <v>102.9485</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>16162.9145</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>62.3080353975</v>
       </c>
       <c r="J69" t="n">
         <v>5</v>
@@ -6586,7 +6718,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-03-2412-SELL</t>
+          <t>2026-09-03-2880-BUY</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6600,24 +6732,24 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>118</v>
+        <v>370</v>
       </c>
       <c r="G70" t="n">
-        <v>137.931</v>
+        <v>43.771875</v>
       </c>
       <c r="H70" t="n">
-        <v>16275.858</v>
+        <v>16195.59375</v>
       </c>
       <c r="I70" t="n">
-        <v>62.74343259</v>
+        <v>13.84723265625</v>
       </c>
       <c r="J70" t="n">
         <v>5</v>
@@ -6626,7 +6758,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-03-3045-SELL</t>
+          <t>2026-09-03-2886-BUY</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6640,24 +6772,24 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>138</v>
+        <v>319</v>
       </c>
       <c r="G71" t="n">
-        <v>117.44125</v>
+        <v>50.8254</v>
       </c>
       <c r="H71" t="n">
-        <v>16206.8925</v>
+        <v>16213.3026</v>
       </c>
       <c r="I71" t="n">
-        <v>62.4775705875</v>
+        <v>13.862373723</v>
       </c>
       <c r="J71" t="n">
         <v>5</v>
@@ -6666,7 +6798,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-03-4904-SELL</t>
+          <t>2026-09-03-2892-BUY</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6680,24 +6812,24 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>158</v>
+        <v>436</v>
       </c>
       <c r="G72" t="n">
-        <v>102.9485</v>
+        <v>36.968475</v>
       </c>
       <c r="H72" t="n">
-        <v>16265.863</v>
+        <v>16118.2551</v>
       </c>
       <c r="I72" t="n">
-        <v>62.704901865</v>
+        <v>13.7811081105</v>
       </c>
       <c r="J72" t="n">
         <v>5</v>
@@ -6706,7 +6838,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-03-0050-SELL</t>
+          <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6720,24 +6852,24 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>131</v>
+        <v>593</v>
       </c>
       <c r="G73" t="n">
-        <v>107.64615</v>
+        <v>26.71335</v>
       </c>
       <c r="H73" t="n">
-        <v>14101.64565</v>
+        <v>15841.01655</v>
       </c>
       <c r="I73" t="n">
-        <v>26.15855268075</v>
+        <v>13.54406915025</v>
       </c>
       <c r="J73" t="n">
         <v>5</v>
@@ -6746,7 +6878,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-04-2880-BUY</t>
+          <t>2026-09-04-2412-SELL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6760,24 +6892,24 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>470</v>
+        <v>95</v>
       </c>
       <c r="G74" t="n">
-        <v>44.72235</v>
+        <v>138.43075</v>
       </c>
       <c r="H74" t="n">
-        <v>21019.5045</v>
+        <v>13150.92125</v>
       </c>
       <c r="I74" t="n">
-        <v>17.9716763475</v>
+        <v>50.69680141875001</v>
       </c>
       <c r="J74" t="n">
         <v>5</v>
@@ -6786,7 +6918,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-04-2886-BUY</t>
+          <t>2026-09-04-3045-SELL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6800,24 +6932,24 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>417</v>
+        <v>111</v>
       </c>
       <c r="G75" t="n">
-        <v>50.4252</v>
+        <v>117.941</v>
       </c>
       <c r="H75" t="n">
-        <v>21027.3084</v>
+        <v>13091.451</v>
       </c>
       <c r="I75" t="n">
-        <v>17.978348682</v>
+        <v>50.467543605</v>
       </c>
       <c r="J75" t="n">
         <v>5</v>
@@ -6826,7 +6958,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-04-2892-BUY</t>
+          <t>2026-09-04-4904-SELL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6840,24 +6972,24 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>540</v>
+        <v>126</v>
       </c>
       <c r="G76" t="n">
-        <v>38.019</v>
+        <v>104.44775</v>
       </c>
       <c r="H76" t="n">
-        <v>20530.26</v>
+        <v>13160.4165</v>
       </c>
       <c r="I76" t="n">
-        <v>17.5533723</v>
+        <v>50.7334056075</v>
       </c>
       <c r="J76" t="n">
         <v>5</v>
@@ -6866,7 +6998,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-04-5880-BUY</t>
+          <t>2026-09-04-0050-BUY</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6880,7 +7012,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -6888,16 +7020,16 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G77" t="n">
-        <v>26.763375</v>
+        <v>109.104525</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>3927.7629</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>3.3582372795</v>
       </c>
       <c r="J77" t="n">
         <v>5</v>
@@ -6906,7 +7038,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-04-2412-SELL</t>
+          <t>2026-09-04-2880-BUY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6920,24 +7052,24 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="G78" t="n">
-        <v>138.43075</v>
+        <v>44.72235</v>
       </c>
       <c r="H78" t="n">
-        <v>13289.352</v>
+        <v>9033.914699999999</v>
       </c>
       <c r="I78" t="n">
-        <v>51.23045196000001</v>
+        <v>7.723997068499999</v>
       </c>
       <c r="J78" t="n">
         <v>5</v>
@@ -6946,7 +7078,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-04-3045-SELL</t>
+          <t>2026-09-04-2886-BUY</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6960,24 +7092,24 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="G79" t="n">
-        <v>117.941</v>
+        <v>50.4252</v>
       </c>
       <c r="H79" t="n">
-        <v>13209.392</v>
+        <v>9026.1108</v>
       </c>
       <c r="I79" t="n">
-        <v>50.92220616</v>
+        <v>7.717324733999998</v>
       </c>
       <c r="J79" t="n">
         <v>5</v>
@@ -6986,7 +7118,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-04-4904-SELL</t>
+          <t>2026-09-04-2892-BUY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7000,24 +7132,24 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="G80" t="n">
-        <v>104.44775</v>
+        <v>38.019</v>
       </c>
       <c r="H80" t="n">
-        <v>13264.86425</v>
+        <v>9048.522000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>51.13605168375</v>
+        <v>7.736486309999999</v>
       </c>
       <c r="J80" t="n">
         <v>5</v>
@@ -7026,7 +7158,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-04-0050-BUY</t>
+          <t>2026-09-04-5880-BUY</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7040,7 +7172,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -7048,16 +7180,16 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="G81" t="n">
-        <v>109.104525</v>
+        <v>26.763375</v>
       </c>
       <c r="H81" t="n">
-        <v>4036.867425</v>
+        <v>8189.59275</v>
       </c>
       <c r="I81" t="n">
-        <v>3.451521648375</v>
+        <v>7.002101801249999</v>
       </c>
       <c r="J81" t="n">
         <v>5</v>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:43.719139+00:00</t>
+          <t>2026-09-07T15:21:46.451048+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:44.416968+00:00</t>
+          <t>2026-09-07T15:21:47.125700+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:45.137932+00:00</t>
+          <t>2026-09-07T15:21:47.815010+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:45.845928+00:00</t>
+          <t>2026-09-07T15:21:48.524068+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:46.531553+00:00</t>
+          <t>2026-09-07T15:21:49.213495+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:47.223052+00:00</t>
+          <t>2026-09-07T15:21:49.889988+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:47.907541+00:00</t>
+          <t>2026-09-07T15:21:50.565625+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:48.598052+00:00</t>
+          <t>2026-09-07T15:21:51.248585+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:49.285157+00:00</t>
+          <t>2026-09-07T15:21:51.927420+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:49.965837+00:00</t>
+          <t>2026-09-07T15:21:52.604148+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:50.634519+00:00</t>
+          <t>2026-09-07T15:21:53.277036+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1330,28 +1330,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3003385.859672599</v>
+        <v>3001924.395765</v>
       </c>
       <c r="C3" t="n">
-        <v>2400122.1596726</v>
+        <v>2685574.395765</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1324475836892178</v>
+        <v>0.1053824008513653</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0616352705410217</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0067783498195663</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7991387959501939</v>
+        <v>0.8946175991486346</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1378,28 +1378,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2997580.92268513</v>
+        <v>2998911.005652251</v>
       </c>
       <c r="C4" t="n">
-        <v>1800948.622685131</v>
+        <v>2417111.005652251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2628292013862529</v>
+        <v>0.1940037563313623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1225920198580742</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0137781101045318</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6008006686511409</v>
+        <v>0.8059962436686375</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1426,28 +1426,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2990921.174510478</v>
+        <v>2994284.317075251</v>
       </c>
       <c r="C5" t="n">
-        <v>1199624.374510478</v>
+        <v>2101884.317075251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4110521402160387</v>
+        <v>0.2980344902155704</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1664075951722332</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0214516686520503</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4010885959596775</v>
+        <v>0.7019655097844294</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1474,28 +1474,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3031940.393478123</v>
+        <v>3024257.628498252</v>
       </c>
       <c r="C6" t="n">
-        <v>597647.8934781223</v>
+        <v>1786657.628498251</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5863678269613146</v>
+        <v>0.4092243955468014</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1863199557666621</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0301949207830495</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2273129322782586</v>
+        <v>0.5907756044531984</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1522,28 +1522,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3073950.771815519</v>
+        <v>3051687.935647626</v>
       </c>
       <c r="C7" t="n">
-        <v>150317.771815519</v>
+        <v>1513537.935647627</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7271963398033734</v>
+        <v>0.504032532957396</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1734042083195696</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0504989381818623</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.123575231779675</v>
+        <v>0.4959674670426039</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1570,28 +1570,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3097189.250170738</v>
+        <v>3068713.905429002</v>
       </c>
       <c r="C8" t="n">
-        <v>37753.90017073768</v>
+        <v>1237213.905429002</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7785556855678325</v>
+        <v>0.5968298304901639</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1441605481406686</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06509403646835139</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0814105521884906</v>
+        <v>0.403170169509836</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1618,28 +1618,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3142192.724419985</v>
+        <v>3106745.469685002</v>
       </c>
       <c r="C9" t="n">
-        <v>9573.074419985664</v>
+        <v>891145.4696850018</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8050271488254839</v>
+        <v>0.6787810654516911</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1176942448901712</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07423198398597761</v>
+        <v>0.0343768104088773</v>
       </c>
       <c r="G9" t="n">
-        <v>0.059109906641714</v>
+        <v>0.2868421241394314</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1666,28 +1666,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3189013.648480112</v>
+        <v>3146815.694174252</v>
       </c>
       <c r="C10" t="n">
-        <v>2016.348480111796</v>
+        <v>647515.6941742518</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8241550804439559</v>
+        <v>0.7604830509871878</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0962872956490311</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0789253442423985</v>
+        <v>0.0337484016609583</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0532121284244682</v>
+        <v>0.2057685473518539</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1714,28 +1714,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3196751.022288824</v>
+        <v>3151865.075629502</v>
       </c>
       <c r="C11" t="n">
-        <v>19.32228882430718</v>
+        <v>462365.0756295018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8435715453589542</v>
+        <v>0.8190705940940044</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0808156463230055</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07560676396591851</v>
+        <v>0.0342336989087167</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0329546053635502</v>
+        <v>0.1466957069972788</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1762,28 +1762,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3209456.571991</v>
+        <v>3163015.075629502</v>
       </c>
       <c r="C12" t="n">
-        <v>10.77199099981408</v>
+        <v>462365.0756295018</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8543491206360181</v>
+        <v>0.8190760834373798</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0677114630235318</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0779360600118135</v>
+        <v>0.0347453291787196</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0081287003418476</v>
+        <v>0.1461785873839004</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1814,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,7 +1852,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-0050-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>2880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>195</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="n">
-        <v>103.8</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2412</v>
+        <v>2886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1895,16 +1895,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>450</v>
+        <v>2000</v>
       </c>
       <c r="F3" t="n">
-        <v>136.5</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2517</v>
+        <v>2000</v>
       </c>
       <c r="F4" t="n">
-        <v>39.25</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1947,25 +1947,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2108</v>
+        <v>3000</v>
       </c>
       <c r="F5" t="n">
-        <v>46.85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1973,25 +1973,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2945</v>
+        <v>2000</v>
       </c>
       <c r="F6" t="n">
-        <v>33.55</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24-3045-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1999,25 +1999,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>534</v>
+        <v>1000</v>
       </c>
       <c r="F7" t="n">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24-4904-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>605</v>
+        <v>2000</v>
       </c>
       <c r="F8" t="n">
-        <v>101.5</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3952</v>
+        <v>3000</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>2880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2077,25 +2077,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>2000</v>
       </c>
       <c r="F10" t="n">
-        <v>104.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2412</v>
+        <v>2886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2103,25 +2103,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>451</v>
+        <v>2000</v>
       </c>
       <c r="F11" t="n">
-        <v>136.5</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2129,25 +2129,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2484</v>
+        <v>2000</v>
       </c>
       <c r="F12" t="n">
-        <v>39.8</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2104</v>
+        <v>3000</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2925</v>
+        <v>2000</v>
       </c>
       <c r="F14" t="n">
-        <v>33.8</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25-3045-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>533</v>
+        <v>2000</v>
       </c>
       <c r="F15" t="n">
-        <v>115.5</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25-4904-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="F16" t="n">
-        <v>102.5</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3947</v>
+        <v>3000</v>
       </c>
       <c r="F17" t="n">
         <v>25.05</v>
@@ -2268,16 +2268,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>2880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>215</v>
+        <v>2000</v>
       </c>
       <c r="F18" t="n">
-        <v>105.9</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2412</v>
+        <v>2886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,25 +2311,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>319</v>
+        <v>1000</v>
       </c>
       <c r="F19" t="n">
-        <v>136</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2337,25 +2337,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>2000</v>
       </c>
       <c r="F20" t="n">
-        <v>39.6</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2394</v>
+        <v>3000</v>
       </c>
       <c r="F21" t="n">
-        <v>46.6</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2389,25 +2389,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3341</v>
+        <v>2000</v>
       </c>
       <c r="F22" t="n">
-        <v>33.4</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26-3045-BUY</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>375</v>
+        <v>1000</v>
       </c>
       <c r="F23" t="n">
-        <v>115.5</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26-4904-BUY</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>429</v>
+        <v>2000</v>
       </c>
       <c r="F24" t="n">
-        <v>101</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2467,21 +2467,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4464</v>
+        <v>3000</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-09-01-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2493,25 +2493,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>251</v>
+        <v>1000</v>
       </c>
       <c r="F26" t="n">
-        <v>106.05</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="F27" t="n">
-        <v>135.5</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3191</v>
+        <v>1000</v>
       </c>
       <c r="F28" t="n">
-        <v>39.35</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2571,25 +2571,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2721</v>
+        <v>2000</v>
       </c>
       <c r="F29" t="n">
-        <v>46.15</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2597,25 +2597,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3765</v>
+        <v>3000</v>
       </c>
       <c r="F30" t="n">
-        <v>33.35</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27-3045-BUY</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2623,25 +2623,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>199</v>
+        <v>1000</v>
       </c>
       <c r="F31" t="n">
-        <v>115.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27-4904-BUY</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>227</v>
+        <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>101.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2675,103 +2675,103 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5013</v>
+        <v>2000</v>
       </c>
       <c r="F33" t="n">
-        <v>25.05</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2412-SELL</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2412</v>
+        <v>5880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>84</v>
+        <v>3000</v>
       </c>
       <c r="F34" t="n">
-        <v>135.5</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-3045-SELL</t>
+          <t>2026-09-03-2880-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>99</v>
+        <v>1000</v>
       </c>
       <c r="F35" t="n">
-        <v>115.5</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-4904-SELL</t>
+          <t>2026-09-03-2886-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>113</v>
+        <v>1000</v>
       </c>
       <c r="F36" t="n">
-        <v>100.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-09-03-2892-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>2892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2779,25 +2779,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>605</v>
+        <v>1000</v>
       </c>
       <c r="F37" t="n">
-        <v>106.95</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2880</v>
+        <v>5880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2805,1128 +2805,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2594</v>
+        <v>2000</v>
       </c>
       <c r="F38" t="n">
-        <v>40.25</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-08-28-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>2166</v>
-      </c>
-      <c r="F39" t="n">
-        <v>48.2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-08-28-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>3036</v>
-      </c>
-      <c r="F40" t="n">
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-08-28-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>4136</v>
-      </c>
-      <c r="F41" t="n">
-        <v>25.25</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-31-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2412</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>210</v>
-      </c>
-      <c r="F42" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-08-31-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>247</v>
-      </c>
-      <c r="F43" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-08-31-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>284</v>
-      </c>
-      <c r="F44" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-08-31-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>50</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>398</v>
-      </c>
-      <c r="F45" t="n">
-        <v>106.25</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-08-31-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>946</v>
-      </c>
-      <c r="F46" t="n">
-        <v>41.35</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-08-31-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>805</v>
-      </c>
-      <c r="F47" t="n">
-        <v>48.55</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-08-31-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F48" t="n">
-        <v>35.3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-08-31-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1531</v>
-      </c>
-      <c r="F49" t="n">
-        <v>25.55</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-01-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2412</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>197</v>
-      </c>
-      <c r="F50" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-09-01-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>232</v>
-      </c>
-      <c r="F51" t="n">
-        <v>115.5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-09-01-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>265</v>
-      </c>
-      <c r="F52" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-09-01-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>50</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>325</v>
-      </c>
-      <c r="F53" t="n">
-        <v>108.45</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-09-01-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>437</v>
-      </c>
-      <c r="F54" t="n">
-        <v>41.95</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-09-01-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>378</v>
-      </c>
-      <c r="F55" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-01-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>511</v>
-      </c>
-      <c r="F56" t="n">
-        <v>35.9</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-01-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>716</v>
-      </c>
-      <c r="F57" t="n">
-        <v>25.6</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-02-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>2412</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>160</v>
-      </c>
-      <c r="F58" t="n">
-        <v>137.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-02-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>189</v>
-      </c>
-      <c r="F59" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-09-02-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>214</v>
-      </c>
-      <c r="F60" t="n">
-        <v>102.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-02-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>50</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>186</v>
-      </c>
-      <c r="F61" t="n">
-        <v>106.8</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-02-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>309</v>
-      </c>
-      <c r="F62" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-02-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>271</v>
-      </c>
-      <c r="F63" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-02-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>367</v>
-      </c>
-      <c r="F64" t="n">
-        <v>36.25</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-02-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>506</v>
-      </c>
-      <c r="F65" t="n">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-03-0050-SELL</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>50</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>130</v>
-      </c>
-      <c r="F66" t="n">
-        <v>106.2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-03-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>2412</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>118</v>
-      </c>
-      <c r="F67" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-03-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>138</v>
-      </c>
-      <c r="F68" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-03-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>157</v>
-      </c>
-      <c r="F69" t="n">
-        <v>103.5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-03-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>370</v>
-      </c>
-      <c r="F70" t="n">
-        <v>43.45</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-03-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>319</v>
-      </c>
-      <c r="F71" t="n">
-        <v>50.4</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-03-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>436</v>
-      </c>
-      <c r="F72" t="n">
-        <v>36.85</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-03-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>602</v>
-      </c>
-      <c r="F73" t="n">
         <v>26.7</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-04-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>2412</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>95</v>
-      </c>
-      <c r="F74" t="n">
-        <v>137.5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-04-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>111</v>
-      </c>
-      <c r="F75" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-04-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>126</v>
-      </c>
-      <c r="F76" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-04-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>50</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>36</v>
-      </c>
-      <c r="F77" t="n">
-        <v>107.9</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-04-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>202</v>
-      </c>
-      <c r="F78" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-04-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>179</v>
-      </c>
-      <c r="F79" t="n">
-        <v>49.55</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-04-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>238</v>
-      </c>
-      <c r="F80" t="n">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-04-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>333</v>
-      </c>
-      <c r="F81" t="n">
-        <v>26.65</v>
       </c>
     </row>
   </sheetData>
@@ -3940,7 +2822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3998,7 +2880,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-0050-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4012,7 +2894,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>2880</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4020,16 +2902,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>195</v>
+        <v>2000</v>
       </c>
       <c r="G2" t="n">
-        <v>102.95145</v>
+        <v>39.169575</v>
       </c>
       <c r="H2" t="n">
-        <v>20075.53275</v>
+        <v>78339.14999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>17.16458050125</v>
+        <v>66.97997324999999</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -4038,7 +2920,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4052,7 +2934,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2412</v>
+        <v>2886</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4060,16 +2942,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>450</v>
+        <v>2000</v>
       </c>
       <c r="G3" t="n">
-        <v>136.56825</v>
+        <v>46.873425</v>
       </c>
       <c r="H3" t="n">
-        <v>61455.7125</v>
+        <v>93746.85000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>52.5446341875</v>
+        <v>80.15355674999999</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -4078,7 +2960,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4092,7 +2974,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4100,16 +2982,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2517</v>
+        <v>2000</v>
       </c>
       <c r="G4" t="n">
-        <v>39.169575</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>98589.82027500001</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>84.29429633512498</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -4118,7 +3000,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4132,7 +3014,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4140,16 +3022,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2108</v>
+        <v>3000</v>
       </c>
       <c r="G5" t="n">
-        <v>46.873425</v>
+        <v>25.0125</v>
       </c>
       <c r="H5" t="n">
-        <v>98809.1799</v>
+        <v>75037.5</v>
       </c>
       <c r="I5" t="n">
-        <v>84.48184881449998</v>
+        <v>64.15706249999999</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -4158,21 +3040,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4180,16 +3062,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2945</v>
+        <v>2000</v>
       </c>
       <c r="G6" t="n">
-        <v>33.51674999999999</v>
+        <v>39.6198</v>
       </c>
       <c r="H6" t="n">
-        <v>98706.82875</v>
+        <v>79239.59999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>84.39433858124998</v>
+        <v>67.74985799999999</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -4198,21 +3080,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24-3045-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4220,16 +3102,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>534</v>
+        <v>1000</v>
       </c>
       <c r="G7" t="n">
-        <v>115.0575</v>
+        <v>46.92345</v>
       </c>
       <c r="H7" t="n">
-        <v>61440.705</v>
+        <v>46923.45</v>
       </c>
       <c r="I7" t="n">
-        <v>52.531802775</v>
+        <v>40.11954975</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -4238,21 +3120,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24-4904-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4260,16 +3142,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>605</v>
+        <v>2000</v>
       </c>
       <c r="G8" t="n">
-        <v>101.55075</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>61438.20374999999</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>52.52966420624999</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -4278,17 +3160,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4300,16 +3182,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3952</v>
+        <v>3000</v>
       </c>
       <c r="G9" t="n">
         <v>25.0125</v>
       </c>
       <c r="H9" t="n">
-        <v>98849.39999999999</v>
+        <v>75037.5</v>
       </c>
       <c r="I9" t="n">
-        <v>84.51623699999999</v>
+        <v>64.15706249999999</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -4318,21 +3200,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>2880</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4340,16 +3222,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>195</v>
+        <v>2000</v>
       </c>
       <c r="G10" t="n">
-        <v>104.15205</v>
+        <v>39.8199</v>
       </c>
       <c r="H10" t="n">
-        <v>20309.64975</v>
+        <v>79639.79999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>17.36475053625</v>
+        <v>68.09202899999998</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -4358,21 +3240,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2412</v>
+        <v>2886</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4380,16 +3262,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>451</v>
+        <v>2000</v>
       </c>
       <c r="G11" t="n">
-        <v>136.56825</v>
+        <v>46.6233</v>
       </c>
       <c r="H11" t="n">
-        <v>61592.28075000001</v>
+        <v>93246.60000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>52.66140004125</v>
+        <v>79.725843</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -4398,21 +3280,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4420,16 +3302,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2484</v>
+        <v>2000</v>
       </c>
       <c r="G12" t="n">
-        <v>39.6198</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>98415.58319999999</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>84.14532363599999</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -4438,21 +3320,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4460,16 +3342,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2104</v>
+        <v>3000</v>
       </c>
       <c r="G13" t="n">
-        <v>46.92345</v>
+        <v>25.0125</v>
       </c>
       <c r="H13" t="n">
-        <v>98726.9388</v>
+        <v>75037.5</v>
       </c>
       <c r="I13" t="n">
-        <v>84.41153267399999</v>
+        <v>64.15706249999999</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -4478,21 +3360,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4500,16 +3382,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2925</v>
+        <v>2000</v>
       </c>
       <c r="G14" t="n">
-        <v>33.51674999999999</v>
+        <v>39.369675</v>
       </c>
       <c r="H14" t="n">
-        <v>98036.49374999998</v>
+        <v>78739.35000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>83.82120215624998</v>
+        <v>67.32214425000001</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -4518,21 +3400,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25-3045-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4540,16 +3422,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>533</v>
+        <v>2000</v>
       </c>
       <c r="G15" t="n">
-        <v>115.0575</v>
+        <v>46.92345</v>
       </c>
       <c r="H15" t="n">
-        <v>61325.64749999999</v>
+        <v>93846.89999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>52.43342861249999</v>
+        <v>80.23909949999999</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -4558,21 +3440,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25-4904-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4580,16 +3462,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G16" t="n">
-        <v>102.55125</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>61530.75</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>52.60879125</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -4598,17 +3480,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4620,16 +3502,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3947</v>
+        <v>3000</v>
       </c>
       <c r="G17" t="n">
-        <v>25.0125</v>
+        <v>25.11255</v>
       </c>
       <c r="H17" t="n">
-        <v>98724.33749999999</v>
+        <v>75337.64999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>84.40930856249999</v>
+        <v>64.41369074999999</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -4638,21 +3520,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>2880</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4660,16 +3542,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>215</v>
+        <v>2000</v>
       </c>
       <c r="G18" t="n">
-        <v>106.55325</v>
+        <v>40.270125</v>
       </c>
       <c r="H18" t="n">
-        <v>22908.94875</v>
+        <v>80540.25</v>
       </c>
       <c r="I18" t="n">
-        <v>19.58715118125</v>
+        <v>68.86191375</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -4678,21 +3560,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2412</v>
+        <v>2886</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4700,16 +3582,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>319</v>
+        <v>1000</v>
       </c>
       <c r="G19" t="n">
-        <v>136.56825</v>
+        <v>47.92395</v>
       </c>
       <c r="H19" t="n">
-        <v>43565.27175</v>
+        <v>47923.95</v>
       </c>
       <c r="I19" t="n">
-        <v>37.24830734625</v>
+        <v>40.97497725</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -4718,21 +3600,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4740,16 +3622,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2818</v>
+        <v>2000</v>
       </c>
       <c r="G20" t="n">
-        <v>39.8199</v>
+        <v>34.31715</v>
       </c>
       <c r="H20" t="n">
-        <v>112212.4782</v>
+        <v>68634.3</v>
       </c>
       <c r="I20" t="n">
-        <v>95.941668861</v>
+        <v>58.6823265</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -4758,21 +3640,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4780,16 +3662,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2394</v>
+        <v>3000</v>
       </c>
       <c r="G21" t="n">
-        <v>46.6233</v>
+        <v>25.262625</v>
       </c>
       <c r="H21" t="n">
-        <v>111616.1802</v>
+        <v>75787.875</v>
       </c>
       <c r="I21" t="n">
-        <v>95.431834071</v>
+        <v>64.79863312499999</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -4798,21 +3680,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4820,16 +3702,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3341</v>
+        <v>2000</v>
       </c>
       <c r="G22" t="n">
-        <v>33.51674999999999</v>
+        <v>40.82039999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>111979.46175</v>
+        <v>81640.79999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>95.74243979624998</v>
+        <v>69.80288399999999</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -4838,21 +3720,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26-3045-BUY</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3045</v>
+        <v>2886</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4860,16 +3742,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>375</v>
+        <v>1000</v>
       </c>
       <c r="G23" t="n">
-        <v>116.058</v>
+        <v>48.2241</v>
       </c>
       <c r="H23" t="n">
-        <v>43521.75</v>
+        <v>48224.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.21109625</v>
+        <v>41.2316055</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -4878,21 +3760,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26-4904-BUY</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4904</v>
+        <v>2892</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4900,16 +3782,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>429</v>
+        <v>2000</v>
       </c>
       <c r="G24" t="n">
-        <v>101.0505</v>
+        <v>35.067525</v>
       </c>
       <c r="H24" t="n">
-        <v>43350.6645</v>
+        <v>70135.04999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>37.0648181475</v>
+        <v>59.96546774999999</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -4918,17 +3800,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4940,16 +3822,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4464</v>
+        <v>3000</v>
       </c>
       <c r="G25" t="n">
-        <v>25.0125</v>
+        <v>25.362675</v>
       </c>
       <c r="H25" t="n">
-        <v>111655.8</v>
+        <v>76088.02499999999</v>
       </c>
       <c r="I25" t="n">
-        <v>95.465709</v>
+        <v>65.05526137499999</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -4958,17 +3840,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-09-01-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -4980,16 +3862,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>251</v>
+        <v>1000</v>
       </c>
       <c r="G26" t="n">
-        <v>107.15355</v>
+        <v>107.55375</v>
       </c>
       <c r="H26" t="n">
-        <v>26895.54105</v>
+        <v>107553.75</v>
       </c>
       <c r="I26" t="n">
-        <v>22.99568759775</v>
+        <v>91.95845625</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -4998,21 +3880,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5020,16 +3902,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="G27" t="n">
-        <v>136.068</v>
+        <v>41.970975</v>
       </c>
       <c r="H27" t="n">
-        <v>23131.56</v>
+        <v>41970.97500000001</v>
       </c>
       <c r="I27" t="n">
-        <v>19.7774838</v>
+        <v>35.885183625</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -5038,21 +3920,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5060,16 +3942,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3191</v>
+        <v>1000</v>
       </c>
       <c r="G28" t="n">
-        <v>39.369675</v>
+        <v>48.274125</v>
       </c>
       <c r="H28" t="n">
-        <v>125628.632925</v>
+        <v>48274.125</v>
       </c>
       <c r="I28" t="n">
-        <v>107.412481150875</v>
+        <v>41.274376875</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -5078,21 +3960,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5100,16 +3982,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2721</v>
+        <v>2000</v>
       </c>
       <c r="G29" t="n">
-        <v>46.92345</v>
+        <v>35.567775</v>
       </c>
       <c r="H29" t="n">
-        <v>127678.70745</v>
+        <v>71135.54999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>109.16529486975</v>
+        <v>60.82089524999999</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -5118,21 +4000,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5140,16 +4022,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3765</v>
+        <v>3000</v>
       </c>
       <c r="G30" t="n">
-        <v>33.51674999999999</v>
+        <v>25.6128</v>
       </c>
       <c r="H30" t="n">
-        <v>126190.56375</v>
+        <v>76838.39999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>107.89293200625</v>
+        <v>65.69683199999999</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -5158,21 +4040,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27-3045-BUY</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5180,16 +4062,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>199</v>
+        <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>115.55775</v>
+        <v>42.92144999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>22995.99225</v>
+        <v>42921.44999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>19.66157337375</v>
+        <v>36.69783974999999</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -5198,21 +4080,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27-4904-BUY</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5220,16 +4102,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>227</v>
+        <v>1000</v>
       </c>
       <c r="G32" t="n">
-        <v>101.55075</v>
+        <v>49.0245</v>
       </c>
       <c r="H32" t="n">
-        <v>23052.02025</v>
+        <v>49024.49999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>19.70947731375</v>
+        <v>41.9159475</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
@@ -5238,21 +4120,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5260,16 +4142,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5013</v>
+        <v>2000</v>
       </c>
       <c r="G33" t="n">
-        <v>25.11255</v>
+        <v>36.268125</v>
       </c>
       <c r="H33" t="n">
-        <v>125889.21315</v>
+        <v>72536.25</v>
       </c>
       <c r="I33" t="n">
-        <v>107.63527724325</v>
+        <v>62.01849375</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -5278,38 +4160,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2412-SELL</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2412</v>
+        <v>5880</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>84</v>
+        <v>3000</v>
       </c>
       <c r="G34" t="n">
-        <v>135.932</v>
+        <v>26.31315</v>
       </c>
       <c r="H34" t="n">
-        <v>11418.288</v>
+        <v>78939.45</v>
       </c>
       <c r="I34" t="n">
-        <v>44.01750024</v>
+        <v>67.49322975</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -5318,38 +4200,38 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-3045-SELL</t>
+          <t>2026-09-03-2880-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>99</v>
+        <v>1000</v>
       </c>
       <c r="G35" t="n">
-        <v>114.9425</v>
+        <v>43.771875</v>
       </c>
       <c r="H35" t="n">
-        <v>11379.3075</v>
+        <v>43771.87499999999</v>
       </c>
       <c r="I35" t="n">
-        <v>43.8672304125</v>
+        <v>37.424953125</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -5358,38 +4240,38 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-4904-SELL</t>
+          <t>2026-09-03-2886-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>113</v>
+        <v>1000</v>
       </c>
       <c r="G36" t="n">
-        <v>99.7501</v>
+        <v>50.8254</v>
       </c>
       <c r="H36" t="n">
-        <v>11271.7613</v>
+        <v>50825.4</v>
       </c>
       <c r="I36" t="n">
-        <v>43.4526398115</v>
+        <v>43.45571699999999</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -5398,21 +4280,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-09-03-2892-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>2892</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5420,16 +4302,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>605</v>
+        <v>1000</v>
       </c>
       <c r="G37" t="n">
-        <v>105.6528</v>
+        <v>36.968475</v>
       </c>
       <c r="H37" t="n">
-        <v>63919.94399999999</v>
+        <v>36968.475</v>
       </c>
       <c r="I37" t="n">
-        <v>54.65155211999999</v>
+        <v>31.608046125</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -5438,21 +4320,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2880</v>
+        <v>5880</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5460,1738 +4342,18 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2594</v>
+        <v>2000</v>
       </c>
       <c r="G38" t="n">
-        <v>40.270125</v>
+        <v>26.71335</v>
       </c>
       <c r="H38" t="n">
-        <v>104460.70425</v>
+        <v>53426.7</v>
       </c>
       <c r="I38" t="n">
-        <v>89.31390213374999</v>
+        <v>45.67982849999999</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-08-28-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>2166</v>
-      </c>
-      <c r="G39" t="n">
-        <v>47.92395</v>
-      </c>
-      <c r="H39" t="n">
-        <v>103803.2757</v>
-      </c>
-      <c r="I39" t="n">
-        <v>88.7518007235</v>
-      </c>
-      <c r="J39" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-08-28-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>3036</v>
-      </c>
-      <c r="G40" t="n">
-        <v>34.31715</v>
-      </c>
-      <c r="H40" t="n">
-        <v>104186.8674</v>
-      </c>
-      <c r="I40" t="n">
-        <v>89.07977162699999</v>
-      </c>
-      <c r="J40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-08-28-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>4136</v>
-      </c>
-      <c r="G41" t="n">
-        <v>25.262625</v>
-      </c>
-      <c r="H41" t="n">
-        <v>104486.217</v>
-      </c>
-      <c r="I41" t="n">
-        <v>89.33571553500001</v>
-      </c>
-      <c r="J41" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-31-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>210</v>
-      </c>
-      <c r="G42" t="n">
-        <v>135.932</v>
-      </c>
-      <c r="H42" t="n">
-        <v>28545.72</v>
-      </c>
-      <c r="I42" t="n">
-        <v>110.0437506</v>
-      </c>
-      <c r="J42" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-08-31-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>247</v>
-      </c>
-      <c r="G43" t="n">
-        <v>114.9425</v>
-      </c>
-      <c r="H43" t="n">
-        <v>28390.7975</v>
-      </c>
-      <c r="I43" t="n">
-        <v>109.4465243625</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-08-31-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>284</v>
-      </c>
-      <c r="G44" t="n">
-        <v>100.44975</v>
-      </c>
-      <c r="H44" t="n">
-        <v>28527.729</v>
-      </c>
-      <c r="I44" t="n">
-        <v>109.974395295</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-08-31-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>50</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>398</v>
-      </c>
-      <c r="G45" t="n">
-        <v>106.55325</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42408.1935</v>
-      </c>
-      <c r="I45" t="n">
-        <v>36.25900544249999</v>
-      </c>
-      <c r="J45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-08-31-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>946</v>
-      </c>
-      <c r="G46" t="n">
-        <v>40.82039999999999</v>
-      </c>
-      <c r="H46" t="n">
-        <v>38616.0984</v>
-      </c>
-      <c r="I46" t="n">
-        <v>33.01676413199999</v>
-      </c>
-      <c r="J46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-08-31-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>805</v>
-      </c>
-      <c r="G47" t="n">
-        <v>48.2241</v>
-      </c>
-      <c r="H47" t="n">
-        <v>38820.4005</v>
-      </c>
-      <c r="I47" t="n">
-        <v>33.1914424275</v>
-      </c>
-      <c r="J47" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-08-31-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>1108</v>
-      </c>
-      <c r="G48" t="n">
-        <v>35.067525</v>
-      </c>
-      <c r="H48" t="n">
-        <v>38854.81769999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>33.2208691335</v>
-      </c>
-      <c r="J48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-08-31-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1531</v>
-      </c>
-      <c r="G49" t="n">
-        <v>25.362675</v>
-      </c>
-      <c r="H49" t="n">
-        <v>38830.255425</v>
-      </c>
-      <c r="I49" t="n">
-        <v>33.19986838837499</v>
-      </c>
-      <c r="J49" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-01-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>197</v>
-      </c>
-      <c r="G50" t="n">
-        <v>136.43175</v>
-      </c>
-      <c r="H50" t="n">
-        <v>26877.05475</v>
-      </c>
-      <c r="I50" t="n">
-        <v>103.61104606125</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-09-01-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>232</v>
-      </c>
-      <c r="G51" t="n">
-        <v>115.44225</v>
-      </c>
-      <c r="H51" t="n">
-        <v>26782.602</v>
-      </c>
-      <c r="I51" t="n">
-        <v>103.24693071</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-09-01-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>265</v>
-      </c>
-      <c r="G52" t="n">
-        <v>100.44975</v>
-      </c>
-      <c r="H52" t="n">
-        <v>26619.18375</v>
-      </c>
-      <c r="I52" t="n">
-        <v>102.61695335625</v>
-      </c>
-      <c r="J52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-09-01-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>50</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>325</v>
-      </c>
-      <c r="G53" t="n">
-        <v>107.55375</v>
-      </c>
-      <c r="H53" t="n">
-        <v>34954.96875</v>
-      </c>
-      <c r="I53" t="n">
-        <v>29.88649828125</v>
-      </c>
-      <c r="J53" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-09-01-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>437</v>
-      </c>
-      <c r="G54" t="n">
-        <v>41.970975</v>
-      </c>
-      <c r="H54" t="n">
-        <v>18341.316075</v>
-      </c>
-      <c r="I54" t="n">
-        <v>15.681825244125</v>
-      </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-09-01-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>378</v>
-      </c>
-      <c r="G55" t="n">
-        <v>48.274125</v>
-      </c>
-      <c r="H55" t="n">
-        <v>18247.61925</v>
-      </c>
-      <c r="I55" t="n">
-        <v>15.60171445875</v>
-      </c>
-      <c r="J55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-01-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>511</v>
-      </c>
-      <c r="G56" t="n">
-        <v>35.567775</v>
-      </c>
-      <c r="H56" t="n">
-        <v>18175.133025</v>
-      </c>
-      <c r="I56" t="n">
-        <v>15.539738736375</v>
-      </c>
-      <c r="J56" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-01-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>716</v>
-      </c>
-      <c r="G57" t="n">
-        <v>25.6128</v>
-      </c>
-      <c r="H57" t="n">
-        <v>18338.7648</v>
-      </c>
-      <c r="I57" t="n">
-        <v>15.679643904</v>
-      </c>
-      <c r="J57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-02-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>160</v>
-      </c>
-      <c r="G58" t="n">
-        <v>137.43125</v>
-      </c>
-      <c r="H58" t="n">
-        <v>21989</v>
-      </c>
-      <c r="I58" t="n">
-        <v>84.767595</v>
-      </c>
-      <c r="J58" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-02-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>189</v>
-      </c>
-      <c r="G59" t="n">
-        <v>115.942</v>
-      </c>
-      <c r="H59" t="n">
-        <v>21913.038</v>
-      </c>
-      <c r="I59" t="n">
-        <v>84.47476149000001</v>
-      </c>
-      <c r="J59" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-09-02-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>214</v>
-      </c>
-      <c r="G60" t="n">
-        <v>102.44875</v>
-      </c>
-      <c r="H60" t="n">
-        <v>21924.0325</v>
-      </c>
-      <c r="I60" t="n">
-        <v>84.5171452875</v>
-      </c>
-      <c r="J60" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-02-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>50</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>186</v>
-      </c>
-      <c r="G61" t="n">
-        <v>106.95345</v>
-      </c>
-      <c r="H61" t="n">
-        <v>19893.3417</v>
-      </c>
-      <c r="I61" t="n">
-        <v>17.0088071535</v>
-      </c>
-      <c r="J61" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-02-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>309</v>
-      </c>
-      <c r="G62" t="n">
-        <v>42.92144999999999</v>
-      </c>
-      <c r="H62" t="n">
-        <v>13262.72805</v>
-      </c>
-      <c r="I62" t="n">
-        <v>11.33963248275</v>
-      </c>
-      <c r="J62" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-02-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>271</v>
-      </c>
-      <c r="G63" t="n">
-        <v>49.0245</v>
-      </c>
-      <c r="H63" t="n">
-        <v>13285.6395</v>
-      </c>
-      <c r="I63" t="n">
-        <v>11.3592217725</v>
-      </c>
-      <c r="J63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-02-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>367</v>
-      </c>
-      <c r="G64" t="n">
-        <v>36.268125</v>
-      </c>
-      <c r="H64" t="n">
-        <v>13310.401875</v>
-      </c>
-      <c r="I64" t="n">
-        <v>11.380393603125</v>
-      </c>
-      <c r="J64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-02-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>506</v>
-      </c>
-      <c r="G65" t="n">
-        <v>26.31315</v>
-      </c>
-      <c r="H65" t="n">
-        <v>13314.4539</v>
-      </c>
-      <c r="I65" t="n">
-        <v>11.3838580845</v>
-      </c>
-      <c r="J65" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-03-0050-SELL</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>50</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>130</v>
-      </c>
-      <c r="G66" t="n">
-        <v>107.64615</v>
-      </c>
-      <c r="H66" t="n">
-        <v>13993.9995</v>
-      </c>
-      <c r="I66" t="n">
-        <v>25.9588690725</v>
-      </c>
-      <c r="J66" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-03-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>118</v>
-      </c>
-      <c r="G67" t="n">
-        <v>137.931</v>
-      </c>
-      <c r="H67" t="n">
-        <v>16275.858</v>
-      </c>
-      <c r="I67" t="n">
-        <v>62.74343259</v>
-      </c>
-      <c r="J67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-03-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>138</v>
-      </c>
-      <c r="G68" t="n">
-        <v>117.44125</v>
-      </c>
-      <c r="H68" t="n">
-        <v>16206.8925</v>
-      </c>
-      <c r="I68" t="n">
-        <v>62.4775705875</v>
-      </c>
-      <c r="J68" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-03-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>157</v>
-      </c>
-      <c r="G69" t="n">
-        <v>102.9485</v>
-      </c>
-      <c r="H69" t="n">
-        <v>16162.9145</v>
-      </c>
-      <c r="I69" t="n">
-        <v>62.3080353975</v>
-      </c>
-      <c r="J69" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-03-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>370</v>
-      </c>
-      <c r="G70" t="n">
-        <v>43.771875</v>
-      </c>
-      <c r="H70" t="n">
-        <v>16195.59375</v>
-      </c>
-      <c r="I70" t="n">
-        <v>13.84723265625</v>
-      </c>
-      <c r="J70" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-03-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>319</v>
-      </c>
-      <c r="G71" t="n">
-        <v>50.8254</v>
-      </c>
-      <c r="H71" t="n">
-        <v>16213.3026</v>
-      </c>
-      <c r="I71" t="n">
-        <v>13.862373723</v>
-      </c>
-      <c r="J71" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-03-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>436</v>
-      </c>
-      <c r="G72" t="n">
-        <v>36.968475</v>
-      </c>
-      <c r="H72" t="n">
-        <v>16118.2551</v>
-      </c>
-      <c r="I72" t="n">
-        <v>13.7811081105</v>
-      </c>
-      <c r="J72" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-03-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>593</v>
-      </c>
-      <c r="G73" t="n">
-        <v>26.71335</v>
-      </c>
-      <c r="H73" t="n">
-        <v>15841.01655</v>
-      </c>
-      <c r="I73" t="n">
-        <v>13.54406915025</v>
-      </c>
-      <c r="J73" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-04-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>95</v>
-      </c>
-      <c r="G74" t="n">
-        <v>138.43075</v>
-      </c>
-      <c r="H74" t="n">
-        <v>13150.92125</v>
-      </c>
-      <c r="I74" t="n">
-        <v>50.69680141875001</v>
-      </c>
-      <c r="J74" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-04-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>111</v>
-      </c>
-      <c r="G75" t="n">
-        <v>117.941</v>
-      </c>
-      <c r="H75" t="n">
-        <v>13091.451</v>
-      </c>
-      <c r="I75" t="n">
-        <v>50.467543605</v>
-      </c>
-      <c r="J75" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-04-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>126</v>
-      </c>
-      <c r="G76" t="n">
-        <v>104.44775</v>
-      </c>
-      <c r="H76" t="n">
-        <v>13160.4165</v>
-      </c>
-      <c r="I76" t="n">
-        <v>50.7334056075</v>
-      </c>
-      <c r="J76" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-04-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>50</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>36</v>
-      </c>
-      <c r="G77" t="n">
-        <v>109.104525</v>
-      </c>
-      <c r="H77" t="n">
-        <v>3927.7629</v>
-      </c>
-      <c r="I77" t="n">
-        <v>3.3582372795</v>
-      </c>
-      <c r="J77" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-04-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>202</v>
-      </c>
-      <c r="G78" t="n">
-        <v>44.72235</v>
-      </c>
-      <c r="H78" t="n">
-        <v>9033.914699999999</v>
-      </c>
-      <c r="I78" t="n">
-        <v>7.723997068499999</v>
-      </c>
-      <c r="J78" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-04-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>179</v>
-      </c>
-      <c r="G79" t="n">
-        <v>50.4252</v>
-      </c>
-      <c r="H79" t="n">
-        <v>9026.1108</v>
-      </c>
-      <c r="I79" t="n">
-        <v>7.717324733999998</v>
-      </c>
-      <c r="J79" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-04-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>238</v>
-      </c>
-      <c r="G80" t="n">
-        <v>38.019</v>
-      </c>
-      <c r="H80" t="n">
-        <v>9048.522000000001</v>
-      </c>
-      <c r="I80" t="n">
-        <v>7.736486309999999</v>
-      </c>
-      <c r="J80" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-04-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>306</v>
-      </c>
-      <c r="G81" t="n">
-        <v>26.763375</v>
-      </c>
-      <c r="H81" t="n">
-        <v>8189.59275</v>
-      </c>
-      <c r="I81" t="n">
-        <v>7.002101801249999</v>
-      </c>
-      <c r="J81" t="n">
         <v>5</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:46.451048+00:00</t>
+          <t>2026-09-07T17:02:17.959963+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:47.125700+00:00</t>
+          <t>2026-09-07T17:02:18.674147+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:47.815010+00:00</t>
+          <t>2026-09-07T17:02:19.428691+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:48.524068+00:00</t>
+          <t>2026-09-07T17:02:20.177127+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:49.213495+00:00</t>
+          <t>2026-09-07T17:02:20.919433+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:49.889988+00:00</t>
+          <t>2026-09-07T17:02:21.635111+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:50.565625+00:00</t>
+          <t>2026-09-07T17:02:22.383059+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:51.248585+00:00</t>
+          <t>2026-09-07T17:02:23.103058+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:51.927420+00:00</t>
+          <t>2026-09-07T17:02:23.841450+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:52.604148+00:00</t>
+          <t>2026-09-07T17:02:24.577650+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07T15:21:53.277036+00:00</t>
+          <t>2026-09-07T17:02:25.287190+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3000000</v>
+        <v>15000000</v>
       </c>
       <c r="C2" t="n">
-        <v>3000000</v>
+        <v>15000000</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1330,28 +1330,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3001924.395765</v>
+        <v>15014804.1711105</v>
       </c>
       <c r="C3" t="n">
-        <v>2685574.395765</v>
+        <v>12306554.1711105</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1053824008513653</v>
+        <v>0.1263253238859735</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0540466589342124</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8946175991486346</v>
+        <v>0.8196280171798139</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1378,28 +1378,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2998911.005652251</v>
+        <v>14985455.1789135</v>
       </c>
       <c r="C4" t="n">
-        <v>2417111.005652251</v>
+        <v>9499955.1789135</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1940037563313623</v>
+        <v>0.2514171211363341</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1075709733707852</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.0070668524069268</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8059962436686375</v>
+        <v>0.6339450530859536</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1426,28 +1426,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2994284.317075251</v>
+        <v>14955410.5851835</v>
       </c>
       <c r="C5" t="n">
-        <v>2101884.317075251</v>
+        <v>6844360.585183501</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2980344902155704</v>
+        <v>0.3899558602408268</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.1382108493930484</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0141821582758904</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7019655097844294</v>
+        <v>0.457651132090234</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1474,28 +1474,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3024257.628498252</v>
+        <v>15145673.009127</v>
       </c>
       <c r="C6" t="n">
-        <v>1786657.628498251</v>
+        <v>4120073.009127002</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4092243955468014</v>
+        <v>0.5476316565795237</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.1591543669632506</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0211842682597631</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5907756044531984</v>
+        <v>0.2720297081974623</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1522,28 +1522,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3051687.935647626</v>
+        <v>15352487.94061138</v>
       </c>
       <c r="C7" t="n">
-        <v>1513537.935647627</v>
+        <v>1397637.940611377</v>
       </c>
       <c r="D7" t="n">
-        <v>0.504032532957396</v>
+        <v>0.709744898817102</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.1576943104834374</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.04152421434663</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4959674670426039</v>
+        <v>0.1342914987650466</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1570,28 +1570,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3068713.905429002</v>
+        <v>15469251.782129</v>
       </c>
       <c r="C8" t="n">
-        <v>1237213.905429002</v>
+        <v>299701.7821290023</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5968298304901639</v>
+        <v>0.7682304333380263</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.156310081059862</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0560854534026204</v>
       </c>
       <c r="G8" t="n">
-        <v>0.403170169509836</v>
+        <v>0.1128939204032211</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1618,28 +1618,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3106745.469685002</v>
+        <v>15697598.03592038</v>
       </c>
       <c r="C9" t="n">
-        <v>891145.4696850018</v>
+        <v>45398.03592037737</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6787810654516911</v>
+        <v>0.7960899477362172</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.1329821285538865</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0343768104088773</v>
+        <v>0.068035886608647</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2868421241394314</v>
+        <v>0.08953108877202649</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1666,28 +1666,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3146815.694174252</v>
+        <v>15930765.52356013</v>
       </c>
       <c r="C10" t="n">
-        <v>647515.6941742518</v>
+        <v>6215.523560127462</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7604830509871878</v>
+        <v>0.8165238500788047</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.1097561819872453</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0337484016609583</v>
+        <v>0.07332980943523019</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2057685473518539</v>
+        <v>0.06871671032066549</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1714,28 +1714,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3151865.075629502</v>
+        <v>15968263.16981938</v>
       </c>
       <c r="C11" t="n">
-        <v>462365.0756295018</v>
+        <v>9663.169819377516</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8190705940940044</v>
+        <v>0.829376361045395</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.0956898056945841</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0342336989087167</v>
+        <v>0.0743286848029462</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1466957069972788</v>
+        <v>0.0633020282116603</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1762,28 +1762,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3163015.075629502</v>
+        <v>16027790.18217163</v>
       </c>
       <c r="C12" t="n">
-        <v>462365.0756295018</v>
+        <v>6290.182171627515</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8190760834373798</v>
+        <v>0.8433227442068135</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.08085955613778829</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0347453291787196</v>
+        <v>0.0754252449189601</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1461785873839004</v>
+        <v>0.0334288353774321</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1814,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,7 +1852,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1872,13 +1872,13 @@
         <v>2000</v>
       </c>
       <c r="F2" t="n">
-        <v>39.25</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1895,16 +1895,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="F3" t="n">
-        <v>46.85</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="F4" t="n">
-        <v>33.55</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1947,25 +1947,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1976,22 +1976,22 @@
         <v>2000</v>
       </c>
       <c r="F6" t="n">
-        <v>39.8</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1999,25 +1999,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2025,16 +2025,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="F8" t="n">
-        <v>33.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F9" t="n">
-        <v>25.05</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2080,22 +2080,22 @@
         <v>2000</v>
       </c>
       <c r="F10" t="n">
-        <v>39.6</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2103,25 +2103,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="F11" t="n">
-        <v>46.6</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2129,25 +2129,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="F12" t="n">
-        <v>33.4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,22 +2184,22 @@
         <v>2000</v>
       </c>
       <c r="F14" t="n">
-        <v>39.35</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F15" t="n">
-        <v>46.15</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="F16" t="n">
-        <v>33.35</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,25 +2259,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F17" t="n">
-        <v>25.05</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F18" t="n">
-        <v>40.25</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,25 +2311,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="F19" t="n">
-        <v>48.2</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2337,25 +2337,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="F20" t="n">
-        <v>34.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="F21" t="n">
-        <v>25.25</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2389,25 +2389,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F22" t="n">
-        <v>41.35</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F23" t="n">
-        <v>48.55</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="F24" t="n">
-        <v>35.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2467,25 +2467,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F25" t="n">
-        <v>25.55</v>
+        <v>106.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>2412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2496,18 +2496,18 @@
         <v>1000</v>
       </c>
       <c r="F26" t="n">
-        <v>108.45</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2519,21 +2519,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="F27" t="n">
-        <v>41.95</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="F28" t="n">
-        <v>48.5</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2571,25 +2571,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="F29" t="n">
-        <v>35.9</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5880</v>
+        <v>3045</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2597,25 +2597,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F30" t="n">
-        <v>25.6</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2880</v>
+        <v>4904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2626,22 +2626,22 @@
         <v>1000</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1000</v>
+        <v>23000</v>
       </c>
       <c r="F32" t="n">
-        <v>49</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2892</v>
+        <v>50</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2675,25 +2675,25 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F33" t="n">
-        <v>36.25</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5880</v>
+        <v>2880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="F34" t="n">
-        <v>26.3</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="F35" t="n">
-        <v>43.45</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2753,25 +2753,25 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="F36" t="n">
-        <v>50.4</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2779,25 +2779,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1000</v>
+        <v>24000</v>
       </c>
       <c r="F37" t="n">
-        <v>36.85</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-03-5880-BUY</t>
+          <t>2026-08-31-0050-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2808,7 +2808,917 @@
         <v>2000</v>
       </c>
       <c r="F38" t="n">
+        <v>106.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F39" t="n">
+        <v>41.35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>48.55</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F42" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-01-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-01-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>50</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>108.45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>41.95</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F49" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-02-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>137.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-02-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F52" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F53" t="n">
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>50</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F54" t="n">
+        <v>106.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F55" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F57" t="n">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F58" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-03-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F59" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>103.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>43.45</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F62" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-03-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-03-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F64" t="n">
         <v>26.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-04-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F65" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F66" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F67" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F68" t="n">
+        <v>49.55</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F69" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F70" t="n">
+        <v>26.65</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-07-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F71" t="n">
+        <v>44.35</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-07-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F72" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-07-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F73" t="n">
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>
@@ -2822,7 +3732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,7 +3790,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2894,7 +3804,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2905,13 +3815,13 @@
         <v>2000</v>
       </c>
       <c r="G2" t="n">
-        <v>39.169575</v>
+        <v>136.56825</v>
       </c>
       <c r="H2" t="n">
-        <v>78339.14999999999</v>
+        <v>273136.5</v>
       </c>
       <c r="I2" t="n">
-        <v>66.97997324999999</v>
+        <v>233.5317075</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -2920,7 +3830,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2934,7 +3844,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2942,16 +3852,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="G3" t="n">
-        <v>46.873425</v>
+        <v>39.169575</v>
       </c>
       <c r="H3" t="n">
-        <v>93746.85000000001</v>
+        <v>470034.9</v>
       </c>
       <c r="I3" t="n">
-        <v>80.15355674999999</v>
+        <v>401.8798395</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -2960,7 +3870,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2974,7 +3884,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2982,16 +3892,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="G4" t="n">
-        <v>33.51674999999999</v>
+        <v>46.873425</v>
       </c>
       <c r="H4" t="n">
-        <v>67033.49999999999</v>
+        <v>468734.25</v>
       </c>
       <c r="I4" t="n">
-        <v>57.31364249999999</v>
+        <v>400.76778375</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -3000,7 +3910,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3014,7 +3924,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3022,16 +3932,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="G5" t="n">
-        <v>25.0125</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>75037.5</v>
+        <v>469234.5</v>
       </c>
       <c r="I5" t="n">
-        <v>64.15706249999999</v>
+        <v>401.1954974999999</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -3040,21 +3950,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D6" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3065,13 +3975,13 @@
         <v>2000</v>
       </c>
       <c r="G6" t="n">
-        <v>39.6198</v>
+        <v>115.0575</v>
       </c>
       <c r="H6" t="n">
-        <v>79239.59999999999</v>
+        <v>230115</v>
       </c>
       <c r="I6" t="n">
-        <v>67.74985799999999</v>
+        <v>196.748325</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -3080,21 +3990,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D7" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3102,16 +4012,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G7" t="n">
-        <v>46.92345</v>
+        <v>101.55075</v>
       </c>
       <c r="H7" t="n">
-        <v>46923.45</v>
+        <v>304652.25</v>
       </c>
       <c r="I7" t="n">
-        <v>40.11954975</v>
+        <v>260.47767375</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -3120,21 +4030,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D8" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3142,16 +4052,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="G8" t="n">
-        <v>33.51674999999999</v>
+        <v>25.0125</v>
       </c>
       <c r="H8" t="n">
-        <v>67033.49999999999</v>
+        <v>475237.5</v>
       </c>
       <c r="I8" t="n">
-        <v>57.31364249999999</v>
+        <v>406.3280625</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -3160,7 +4070,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3174,7 +4084,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3182,16 +4092,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G9" t="n">
-        <v>25.0125</v>
+        <v>104.15205</v>
       </c>
       <c r="H9" t="n">
-        <v>75037.5</v>
+        <v>104152.05</v>
       </c>
       <c r="I9" t="n">
-        <v>64.15706249999999</v>
+        <v>89.05000274999999</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -3200,21 +4110,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D10" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3225,13 +4135,13 @@
         <v>2000</v>
       </c>
       <c r="G10" t="n">
-        <v>39.8199</v>
+        <v>136.56825</v>
       </c>
       <c r="H10" t="n">
-        <v>79639.79999999999</v>
+        <v>273136.5</v>
       </c>
       <c r="I10" t="n">
-        <v>68.09202899999998</v>
+        <v>233.5317075</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -3240,21 +4150,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D11" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3262,16 +4172,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="G11" t="n">
-        <v>46.6233</v>
+        <v>39.6198</v>
       </c>
       <c r="H11" t="n">
-        <v>93246.60000000001</v>
+        <v>475437.6</v>
       </c>
       <c r="I11" t="n">
-        <v>79.725843</v>
+        <v>406.499148</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -3280,21 +4190,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D12" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3302,16 +4212,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="G12" t="n">
-        <v>33.51674999999999</v>
+        <v>46.92345</v>
       </c>
       <c r="H12" t="n">
-        <v>67033.49999999999</v>
+        <v>469234.5</v>
       </c>
       <c r="I12" t="n">
-        <v>57.31364249999999</v>
+        <v>401.1954974999999</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -3320,21 +4230,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D13" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3342,16 +4252,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="G13" t="n">
-        <v>25.0125</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>75037.5</v>
+        <v>469234.5</v>
       </c>
       <c r="I13" t="n">
-        <v>64.15706249999999</v>
+        <v>401.1954974999999</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -3360,21 +4270,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3385,13 +4295,13 @@
         <v>2000</v>
       </c>
       <c r="G14" t="n">
-        <v>39.369675</v>
+        <v>115.0575</v>
       </c>
       <c r="H14" t="n">
-        <v>78739.35000000001</v>
+        <v>230115</v>
       </c>
       <c r="I14" t="n">
-        <v>67.32214425000001</v>
+        <v>196.748325</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -3400,21 +4310,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3422,16 +4332,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G15" t="n">
-        <v>46.92345</v>
+        <v>102.55125</v>
       </c>
       <c r="H15" t="n">
-        <v>93846.89999999999</v>
+        <v>307653.75</v>
       </c>
       <c r="I15" t="n">
-        <v>80.23909949999999</v>
+        <v>263.04395625</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -3440,21 +4350,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3462,16 +4372,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="G16" t="n">
-        <v>33.51674999999999</v>
+        <v>25.0125</v>
       </c>
       <c r="H16" t="n">
-        <v>67033.49999999999</v>
+        <v>475237.5</v>
       </c>
       <c r="I16" t="n">
-        <v>57.31364249999999</v>
+        <v>406.3280625</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -3480,21 +4390,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="D17" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3502,16 +4412,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G17" t="n">
-        <v>25.11255</v>
+        <v>106.55325</v>
       </c>
       <c r="H17" t="n">
-        <v>75337.64999999999</v>
+        <v>106553.25</v>
       </c>
       <c r="I17" t="n">
-        <v>64.41369074999999</v>
+        <v>91.10302874999998</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -3520,21 +4430,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3542,16 +4452,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G18" t="n">
-        <v>40.270125</v>
+        <v>136.56825</v>
       </c>
       <c r="H18" t="n">
-        <v>80540.25</v>
+        <v>136568.25</v>
       </c>
       <c r="I18" t="n">
-        <v>68.86191375</v>
+        <v>116.76585375</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -3560,21 +4470,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3582,16 +4492,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="G19" t="n">
-        <v>47.92395</v>
+        <v>39.8199</v>
       </c>
       <c r="H19" t="n">
-        <v>47923.95</v>
+        <v>517658.7</v>
       </c>
       <c r="I19" t="n">
-        <v>40.97497725</v>
+        <v>442.5981885</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -3600,21 +4510,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3622,16 +4532,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="G20" t="n">
-        <v>34.31715</v>
+        <v>46.6233</v>
       </c>
       <c r="H20" t="n">
-        <v>68634.3</v>
+        <v>512856.3</v>
       </c>
       <c r="I20" t="n">
-        <v>58.6823265</v>
+        <v>438.4921365</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -3640,21 +4550,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3662,16 +4572,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="G21" t="n">
-        <v>25.262625</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>75787.875</v>
+        <v>536267.9999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>64.79863312499999</v>
+        <v>458.5091399999999</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -3680,21 +4590,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3702,16 +4612,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G22" t="n">
-        <v>40.82039999999999</v>
+        <v>116.058</v>
       </c>
       <c r="H22" t="n">
-        <v>81640.79999999999</v>
+        <v>116058</v>
       </c>
       <c r="I22" t="n">
-        <v>69.80288399999999</v>
+        <v>99.22959</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -3720,21 +4630,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3742,16 +4652,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G23" t="n">
-        <v>48.2241</v>
+        <v>101.0505</v>
       </c>
       <c r="H23" t="n">
-        <v>48224.1</v>
+        <v>202101</v>
       </c>
       <c r="I23" t="n">
-        <v>41.2316055</v>
+        <v>172.796355</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -3760,21 +4670,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3782,16 +4692,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="G24" t="n">
-        <v>35.067525</v>
+        <v>25.0125</v>
       </c>
       <c r="H24" t="n">
-        <v>70135.04999999999</v>
+        <v>525262.5</v>
       </c>
       <c r="I24" t="n">
-        <v>59.96546774999999</v>
+        <v>449.0994375</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -3800,21 +4710,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3822,16 +4732,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G25" t="n">
-        <v>25.362675</v>
+        <v>107.15355</v>
       </c>
       <c r="H25" t="n">
-        <v>76088.02499999999</v>
+        <v>107153.55</v>
       </c>
       <c r="I25" t="n">
-        <v>65.05526137499999</v>
+        <v>91.61628525</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -3840,21 +4750,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>2412</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3865,13 +4775,13 @@
         <v>1000</v>
       </c>
       <c r="G26" t="n">
-        <v>107.55375</v>
+        <v>136.068</v>
       </c>
       <c r="H26" t="n">
-        <v>107553.75</v>
+        <v>136068</v>
       </c>
       <c r="I26" t="n">
-        <v>91.95845625</v>
+        <v>116.33814</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -3880,17 +4790,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3902,16 +4812,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="G27" t="n">
-        <v>41.970975</v>
+        <v>39.369675</v>
       </c>
       <c r="H27" t="n">
-        <v>41970.97500000001</v>
+        <v>551175.4500000001</v>
       </c>
       <c r="I27" t="n">
-        <v>35.885183625</v>
+        <v>471.2550097500001</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -3920,17 +4830,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -3942,16 +4852,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="G28" t="n">
-        <v>48.274125</v>
+        <v>46.92345</v>
       </c>
       <c r="H28" t="n">
-        <v>48274.125</v>
+        <v>563081.3999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>41.274376875</v>
+        <v>481.4345969999999</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -3960,17 +4870,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3982,16 +4892,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="G29" t="n">
-        <v>35.567775</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>71135.54999999999</v>
+        <v>569784.7499999999</v>
       </c>
       <c r="I29" t="n">
-        <v>60.82089524999999</v>
+        <v>487.1659612499999</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -4000,21 +4910,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5880</v>
+        <v>3045</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4022,16 +4932,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G30" t="n">
-        <v>25.6128</v>
+        <v>115.55775</v>
       </c>
       <c r="H30" t="n">
-        <v>76838.39999999999</v>
+        <v>115557.75</v>
       </c>
       <c r="I30" t="n">
-        <v>65.69683199999999</v>
+        <v>98.80187625000001</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -4040,21 +4950,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2880</v>
+        <v>4904</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4065,13 +4975,13 @@
         <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>42.92144999999999</v>
+        <v>101.55075</v>
       </c>
       <c r="H31" t="n">
-        <v>42921.44999999999</v>
+        <v>101550.75</v>
       </c>
       <c r="I31" t="n">
-        <v>36.69783974999999</v>
+        <v>86.82589125</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -4080,21 +4990,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2886</v>
+        <v>5880</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4102,16 +5012,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1000</v>
+        <v>23000</v>
       </c>
       <c r="G32" t="n">
-        <v>49.0245</v>
+        <v>25.11255</v>
       </c>
       <c r="H32" t="n">
-        <v>49024.49999999999</v>
+        <v>577588.65</v>
       </c>
       <c r="I32" t="n">
-        <v>41.9159475</v>
+        <v>493.83829575</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
@@ -4120,21 +5030,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2892</v>
+        <v>50</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -4142,16 +5052,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G33" t="n">
-        <v>36.268125</v>
+        <v>105.6528</v>
       </c>
       <c r="H33" t="n">
-        <v>72536.25</v>
+        <v>316958.4</v>
       </c>
       <c r="I33" t="n">
-        <v>62.01849375</v>
+        <v>270.999432</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -4160,21 +5070,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5880</v>
+        <v>2880</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -4182,16 +5092,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="G34" t="n">
-        <v>26.31315</v>
+        <v>40.270125</v>
       </c>
       <c r="H34" t="n">
-        <v>78939.45</v>
+        <v>604051.875</v>
       </c>
       <c r="I34" t="n">
-        <v>67.49322975</v>
+        <v>516.464353125</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -4200,21 +5110,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -4222,16 +5132,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1000</v>
+        <v>12000</v>
       </c>
       <c r="G35" t="n">
-        <v>43.771875</v>
+        <v>47.92395</v>
       </c>
       <c r="H35" t="n">
-        <v>43771.87499999999</v>
+        <v>575087.4</v>
       </c>
       <c r="I35" t="n">
-        <v>37.424953125</v>
+        <v>491.699727</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -4240,21 +5150,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -4262,16 +5172,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="G36" t="n">
-        <v>50.8254</v>
+        <v>34.31715</v>
       </c>
       <c r="H36" t="n">
-        <v>50825.4</v>
+        <v>617708.7</v>
       </c>
       <c r="I36" t="n">
-        <v>43.45571699999999</v>
+        <v>528.1409384999999</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -4280,21 +5190,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -4302,16 +5212,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1000</v>
+        <v>24000</v>
       </c>
       <c r="G37" t="n">
-        <v>36.968475</v>
+        <v>25.262625</v>
       </c>
       <c r="H37" t="n">
-        <v>36968.475</v>
+        <v>606303</v>
       </c>
       <c r="I37" t="n">
-        <v>31.608046125</v>
+        <v>518.389065</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -4320,21 +5230,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-03-5880-BUY</t>
+          <t>2026-08-31-0050-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5880</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -4345,15 +5255,1255 @@
         <v>2000</v>
       </c>
       <c r="G38" t="n">
+        <v>106.55325</v>
+      </c>
+      <c r="H38" t="n">
+        <v>213106.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>182.2060575</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>40.82039999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>204102</v>
+      </c>
+      <c r="I39" t="n">
+        <v>174.50721</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>48.2241</v>
+      </c>
+      <c r="H40" t="n">
+        <v>241120.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>206.1580275</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>35.067525</v>
+      </c>
+      <c r="H41" t="n">
+        <v>210405.15</v>
+      </c>
+      <c r="I41" t="n">
+        <v>179.89640325</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>25.362675</v>
+      </c>
+      <c r="H42" t="n">
+        <v>228264.075</v>
+      </c>
+      <c r="I42" t="n">
+        <v>195.165784125</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-01-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>136.43175</v>
+      </c>
+      <c r="H43" t="n">
+        <v>136431.75</v>
+      </c>
+      <c r="I43" t="n">
+        <v>525.94439625</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-01-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>115.44225</v>
+      </c>
+      <c r="H44" t="n">
+        <v>115442.25</v>
+      </c>
+      <c r="I44" t="n">
+        <v>445.02987375</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>100.44975</v>
+      </c>
+      <c r="H45" t="n">
+        <v>100449.75</v>
+      </c>
+      <c r="I45" t="n">
+        <v>387.23378625</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>107.55375</v>
+      </c>
+      <c r="H46" t="n">
+        <v>215107.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>183.9169125</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>41.970975</v>
+      </c>
+      <c r="H47" t="n">
+        <v>83941.95000000001</v>
+      </c>
+      <c r="I47" t="n">
+        <v>71.77036725000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>48.274125</v>
+      </c>
+      <c r="H48" t="n">
+        <v>96548.25</v>
+      </c>
+      <c r="I48" t="n">
+        <v>82.54875375</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>35.567775</v>
+      </c>
+      <c r="H49" t="n">
+        <v>106703.325</v>
+      </c>
+      <c r="I49" t="n">
+        <v>91.231342875</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>25.6128</v>
+      </c>
+      <c r="H50" t="n">
+        <v>102451.2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>87.595776</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-02-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>137.43125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>137431.25</v>
+      </c>
+      <c r="I51" t="n">
+        <v>529.79746875</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-02-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>115.942</v>
+      </c>
+      <c r="H52" t="n">
+        <v>115942</v>
+      </c>
+      <c r="I52" t="n">
+        <v>446.95641</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>102.44875</v>
+      </c>
+      <c r="H53" t="n">
+        <v>102448.75</v>
+      </c>
+      <c r="I53" t="n">
+        <v>394.93993125</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>50</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>106.95345</v>
+      </c>
+      <c r="H54" t="n">
+        <v>106953.45</v>
+      </c>
+      <c r="I54" t="n">
+        <v>91.44519975</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>42.92144999999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>85842.89999999998</v>
+      </c>
+      <c r="I55" t="n">
+        <v>73.39567949999999</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>49.0245</v>
+      </c>
+      <c r="H56" t="n">
+        <v>49024.49999999999</v>
+      </c>
+      <c r="I56" t="n">
+        <v>41.9159475</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>36.268125</v>
+      </c>
+      <c r="H57" t="n">
+        <v>72536.25</v>
+      </c>
+      <c r="I57" t="n">
+        <v>62.01849375</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>26.31315</v>
+      </c>
+      <c r="H58" t="n">
+        <v>78939.45</v>
+      </c>
+      <c r="I58" t="n">
+        <v>67.49322975</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-03-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>117.44125</v>
+      </c>
+      <c r="H59" t="n">
+        <v>117441.25</v>
+      </c>
+      <c r="I59" t="n">
+        <v>452.73601875</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>102.9485</v>
+      </c>
+      <c r="H60" t="n">
+        <v>102948.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>396.8664675000001</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>43.771875</v>
+      </c>
+      <c r="H61" t="n">
+        <v>87543.74999999999</v>
+      </c>
+      <c r="I61" t="n">
+        <v>74.84990624999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>50.8254</v>
+      </c>
+      <c r="H62" t="n">
+        <v>101650.8</v>
+      </c>
+      <c r="I62" t="n">
+        <v>86.91143399999999</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-03-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G63" t="n">
         <v>26.71335</v>
       </c>
-      <c r="H38" t="n">
-        <v>53426.7</v>
-      </c>
-      <c r="I38" t="n">
-        <v>45.67982849999999</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="H63" t="n">
+        <v>26713.35</v>
+      </c>
+      <c r="I63" t="n">
+        <v>22.83991425</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-04-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>117.941</v>
+      </c>
+      <c r="H64" t="n">
+        <v>117941</v>
+      </c>
+      <c r="I64" t="n">
+        <v>454.662555</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G65" t="n">
+        <v>104.44775</v>
+      </c>
+      <c r="H65" t="n">
+        <v>104447.75</v>
+      </c>
+      <c r="I65" t="n">
+        <v>402.64607625</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>44.72235</v>
+      </c>
+      <c r="H66" t="n">
+        <v>44722.35</v>
+      </c>
+      <c r="I66" t="n">
+        <v>38.23760925</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>50.4252</v>
+      </c>
+      <c r="H67" t="n">
+        <v>50425.2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>43.11354599999999</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>38.019</v>
+      </c>
+      <c r="H68" t="n">
+        <v>76038</v>
+      </c>
+      <c r="I68" t="n">
+        <v>65.01249</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>26.763375</v>
+      </c>
+      <c r="H69" t="n">
+        <v>53526.75</v>
+      </c>
+      <c r="I69" t="n">
+        <v>45.76537125</v>
+      </c>
+      <c r="J69" t="n">
         <v>5</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:17.959963+00:00</t>
+          <t>2026-09-07T17:20:06.463234+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,22 +561,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6586994606191088</v>
+        <v>0.6096036287295321</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3074378163576171</v>
+        <v>0.2895671773992635</v>
       </c>
       <c r="N2" t="n">
-        <v>0.033862723023274</v>
+        <v>0.1008291938712045</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6586994606191088</v>
+        <v>0.6096036287295321</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3074378163576171</v>
+        <v>0.2895671773992635</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.033862723023274</v>
+        <v>0.1008291938712045</v>
       </c>
     </row>
     <row r="3">
@@ -587,7 +587,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:18.674147+00:00</t>
+          <t>2026-09-07T17:20:07.202872+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -622,22 +622,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6586994606191088</v>
+        <v>0.5981710983910525</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3074378163576171</v>
+        <v>0.3012070062055442</v>
       </c>
       <c r="N3" t="n">
-        <v>0.033862723023274</v>
+        <v>0.1006218954034034</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6586994606191088</v>
+        <v>0.5981710983910525</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3074378163576171</v>
+        <v>0.3012070062055442</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.033862723023274</v>
+        <v>0.1006218954034034</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:19.428691+00:00</t>
+          <t>2026-09-07T17:20:07.945289+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,22 +683,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7102101090133827</v>
+        <v>0.6486283237932895</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2530927304298557</v>
+        <v>0.2509052546541581</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0366971605567614</v>
+        <v>0.1004664215525525</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7102101090133827</v>
+        <v>0.6486283237932895</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2530927304298557</v>
+        <v>0.2509052546541581</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0366971605567614</v>
+        <v>0.1004664215525525</v>
       </c>
     </row>
     <row r="5">
@@ -709,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:20.177127+00:00</t>
+          <t>2026-09-07T17:20:08.719156+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -744,22 +744,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7478820946012026</v>
+        <v>0.6864712428449671</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2127714526797224</v>
+        <v>0.2131789409906186</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0393464527190748</v>
+        <v>0.1003498161644144</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7478820946012026</v>
+        <v>0.6864712428449671</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2127714526797224</v>
+        <v>0.2131789409906186</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0393464527190748</v>
+        <v>0.1003498161644144</v>
       </c>
     </row>
     <row r="6">
@@ -770,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:20.919433+00:00</t>
+          <t>2026-09-07T17:20:09.462471+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7700909121334123</v>
+        <v>0.7108186119375897</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1712221378720195</v>
+        <v>0.1848842057429639</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0586869499945679</v>
+        <v>0.1042971823194464</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7700909121334123</v>
+        <v>0.7108186119375897</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1712221378720195</v>
+        <v>0.1848842057429639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0586869499945679</v>
+        <v>0.1042971823194464</v>
       </c>
     </row>
     <row r="7">
@@ -831,7 +831,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:21.635111+00:00</t>
+          <t>2026-09-07T17:20:10.210558+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -866,22 +866,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7950658226458608</v>
+        <v>0.7331139589531923</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1360668492773293</v>
+        <v>0.1636631543072229</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0688673280768098</v>
+        <v>0.1032228867395848</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7950658226458608</v>
+        <v>0.7331139589531923</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1360668492773293</v>
+        <v>0.1636631543072229</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0688673280768098</v>
+        <v>0.1032228867395848</v>
       </c>
     </row>
     <row r="8">
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:22.383059+00:00</t>
+          <t>2026-09-07T17:20:10.934867+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -927,22 +927,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8101534576014104</v>
+        <v>0.7471184822986315</v>
       </c>
       <c r="M8" t="n">
-        <v>0.109550136957997</v>
+        <v>0.1477473657304172</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08029640544059249</v>
+        <v>0.1051341519709513</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8101534576014104</v>
+        <v>0.7471184822986315</v>
       </c>
       <c r="P8" t="n">
-        <v>0.109550136957997</v>
+        <v>0.1477473657304172</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.08029640544059249</v>
+        <v>0.1051341519709513</v>
       </c>
     </row>
     <row r="9">
@@ -953,7 +953,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:23.103058+00:00</t>
+          <t>2026-09-07T17:20:11.705257+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -988,22 +988,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8276311681627325</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0896626027184977</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0827062291187696</v>
+        <v>0.1038506139782134</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8276311681627325</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0896626027184977</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0827062291187696</v>
+        <v>0.1038506139782134</v>
       </c>
     </row>
     <row r="10">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:23.841450+00:00</t>
+          <t>2026-09-07T17:20:12.436279+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1049,22 +1049,22 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8510772844884973</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0757884877563883</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0731342277551144</v>
+        <v>0.1038506139782134</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8510772844884973</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0757884877563883</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0731342277551144</v>
+        <v>0.1038506139782134</v>
       </c>
     </row>
     <row r="11">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:24.577650+00:00</t>
+          <t>2026-09-07T17:20:13.151808+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1110,22 +1110,22 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8584151489712601</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0643413658172912</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0772434852114485</v>
+        <v>0.1038506139782134</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8584151489712601</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0643413658172912</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0772434852114485</v>
+        <v>0.1038506139782134</v>
       </c>
     </row>
     <row r="12">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:25.287190+00:00</t>
+          <t>2026-09-07T17:20:13.871246+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1171,22 +1171,22 @@
         <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8584151489712601</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0643413658172912</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0772434852114485</v>
+        <v>0.1038506139782134</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8584151489712601</v>
+        <v>0.7603388617239737</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0643413658172912</v>
+        <v>0.1358105242978129</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0772434852114485</v>
+        <v>0.1038506139782134</v>
       </c>
     </row>
   </sheetData>
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1330,28 +1330,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15014804.1711105</v>
+        <v>15015708.659296</v>
       </c>
       <c r="C3" t="n">
-        <v>12306554.1711105</v>
+        <v>12346808.659296</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1263253238859735</v>
+        <v>0.1166178726380603</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0540466589342124</v>
+        <v>0.0472172187198816</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0139054376145434</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8196280171798139</v>
+        <v>0.8222594710275148</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1378,22 +1378,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14985455.1789135</v>
+        <v>14995857.8897685</v>
       </c>
       <c r="C4" t="n">
-        <v>9499955.1789135</v>
+        <v>9501957.889768502</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2514171211363341</v>
+        <v>0.2302902591759164</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1075709733707852</v>
+        <v>0.1007611575881188</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0070668524069268</v>
+        <v>0.0353097504585764</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6339450530859536</v>
+        <v>0.6336388327773884</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -1426,22 +1426,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14955410.5851835</v>
+        <v>14967387.40737325</v>
       </c>
       <c r="C5" t="n">
-        <v>6844360.585183501</v>
+        <v>6827237.407373251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3899558602408268</v>
+        <v>0.3552256553058038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1382108493930484</v>
+        <v>0.1390356208041261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0141821582758904</v>
+        <v>0.0495978342642686</v>
       </c>
       <c r="G5" t="n">
-        <v>0.457651132090234</v>
+        <v>0.4561408896258014</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -1474,22 +1474,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15145673.009127</v>
+        <v>15145339.85364988</v>
       </c>
       <c r="C6" t="n">
-        <v>4120073.009127002</v>
+        <v>4058639.853649877</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5476316565795237</v>
+        <v>0.5012564969395834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1591543669632506</v>
+        <v>0.1601482715764531</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0211842682597631</v>
+        <v>0.0706157808497285</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2720297081974623</v>
+        <v>0.2679794506342349</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -1522,22 +1522,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15352487.94061138</v>
+        <v>15332590.05679875</v>
       </c>
       <c r="C7" t="n">
-        <v>1397637.940611377</v>
+        <v>1436140.056798752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.709744898817102</v>
+        <v>0.6573709962023473</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1576943104834374</v>
+        <v>0.1588772667224499</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04152421434663</v>
+        <v>0.0900858886126371</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1342914987650466</v>
+        <v>0.09366584846256561</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -1570,25 +1570,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15469251.782129</v>
+        <v>15455197.94303775</v>
       </c>
       <c r="C8" t="n">
-        <v>299701.7821290023</v>
+        <v>518497.9430377525</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7682304333380263</v>
+        <v>0.7108223421330505</v>
       </c>
       <c r="E8" t="n">
-        <v>0.156310081059862</v>
+        <v>0.1573904138248705</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0560854534026204</v>
+        <v>0.09823879354996951</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1128939204032211</v>
+        <v>0.0528345466810161</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>5</v>
@@ -1618,28 +1618,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15697598.03592038</v>
+        <v>15662568.2572455</v>
       </c>
       <c r="C9" t="n">
-        <v>45398.03592037737</v>
+        <v>164118.2572455025</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7960899477362172</v>
+        <v>0.737187529552103</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1329821285538865</v>
+        <v>0.1568708247361279</v>
       </c>
       <c r="F9" t="n">
-        <v>0.068035886608647</v>
+        <v>0.0954632711214727</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08953108877202649</v>
+        <v>0.0525989754669265</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1666,28 +1666,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15930765.52356013</v>
+        <v>15884908.91146813</v>
       </c>
       <c r="C10" t="n">
-        <v>6215.523560127462</v>
+        <v>9458.91146812751</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8165238500788047</v>
+        <v>0.7495573356044857</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1097561819872453</v>
+        <v>0.1562489287054153</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07332980943523019</v>
+        <v>0.0935982704267572</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06871671032066549</v>
+        <v>0.0414722740785466</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1714,28 +1714,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15968263.16981938</v>
+        <v>15929708.91146813</v>
       </c>
       <c r="C11" t="n">
-        <v>9663.169819377516</v>
+        <v>9458.91146812751</v>
       </c>
       <c r="D11" t="n">
-        <v>0.829376361045395</v>
+        <v>0.7487048298424184</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0956898056945841</v>
+        <v>0.1558722770013981</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0743286848029462</v>
+        <v>0.094829102552683</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0633020282116603</v>
+        <v>0.0407172960106709</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1762,28 +1762,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16027790.18217163</v>
+        <v>15982908.91146813</v>
       </c>
       <c r="C12" t="n">
-        <v>6290.182171627515</v>
+        <v>9458.91146812751</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8433227442068135</v>
+        <v>0.7490407451055361</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08085955613778829</v>
+        <v>0.1541021108011657</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0754252449189601</v>
+        <v>0.0962653299548004</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0334288353774321</v>
+        <v>0.0371749871452034</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1814,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,7 +1852,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1872,13 +1872,13 @@
         <v>2000</v>
       </c>
       <c r="F2" t="n">
-        <v>136.5</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1895,16 +1895,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F3" t="n">
-        <v>39.25</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="F4" t="n">
-        <v>46.85</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1947,16 +1947,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="F5" t="n">
-        <v>33.55</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-3045-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1973,16 +1973,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24-4904-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1999,16 +1999,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F7" t="n">
-        <v>101.5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2051,16 +2051,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="F9" t="n">
-        <v>104.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F10" t="n">
-        <v>136.5</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F11" t="n">
-        <v>39.8</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="F13" t="n">
-        <v>33.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-3045-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="F14" t="n">
-        <v>115.5</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25-4904-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,16 +2207,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F15" t="n">
-        <v>102.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19000</v>
+        <v>3000</v>
       </c>
       <c r="F16" t="n">
-        <v>25.05</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,16 +2259,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1000</v>
+        <v>17000</v>
       </c>
       <c r="F17" t="n">
-        <v>105.9</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,16 +2285,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F18" t="n">
-        <v>136</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="F19" t="n">
-        <v>39.6</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2337,16 +2337,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F20" t="n">
-        <v>46.6</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2363,16 +2363,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="F21" t="n">
-        <v>33.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-3045-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="F22" t="n">
-        <v>115.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26-4904-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2418,13 +2418,13 @@
         <v>2000</v>
       </c>
       <c r="F23" t="n">
-        <v>101</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2467,16 +2467,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="F25" t="n">
-        <v>106.05</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2493,16 +2493,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F26" t="n">
-        <v>135.5</v>
+        <v>106.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2519,16 +2519,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
       <c r="F27" t="n">
-        <v>39.35</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2545,16 +2545,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="F28" t="n">
-        <v>46.15</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2571,16 +2571,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="F29" t="n">
-        <v>33.35</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-3045-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2597,16 +2597,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="F30" t="n">
-        <v>115.5</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27-4904-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2626,13 +2626,13 @@
         <v>1000</v>
       </c>
       <c r="F31" t="n">
-        <v>101.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>23000</v>
+        <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>25.05</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3000</v>
+        <v>21000</v>
       </c>
       <c r="F33" t="n">
-        <v>106.95</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2701,16 +2701,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="F34" t="n">
-        <v>40.25</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="F35" t="n">
-        <v>48.2</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="F36" t="n">
-        <v>34.4</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2779,25 +2779,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>24000</v>
+        <v>17000</v>
       </c>
       <c r="F37" t="n">
-        <v>25.25</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31-0050-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2805,16 +2805,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="F38" t="n">
-        <v>106.25</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-31-0050-BUY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F39" t="n">
-        <v>41.35</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2860,13 +2860,13 @@
         <v>5000</v>
       </c>
       <c r="F40" t="n">
-        <v>48.55</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2883,16 +2883,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="F41" t="n">
-        <v>35.3</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2909,42 +2909,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="F42" t="n">
-        <v>25.55</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01-2412-SELL</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2412</v>
+        <v>5880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="F43" t="n">
-        <v>136</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01-3045-SELL</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2953,24 +2953,24 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F44" t="n">
-        <v>115.5</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01-4904-SELL</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2979,24 +2979,24 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F45" t="n">
-        <v>101</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>2892</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3016,13 +3016,13 @@
         <v>2000</v>
       </c>
       <c r="F46" t="n">
-        <v>108.45</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2880</v>
+        <v>5880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F47" t="n">
-        <v>41.95</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3065,25 +3065,25 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F48" t="n">
-        <v>48.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3091,25 +3091,25 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F49" t="n">
-        <v>35.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="F50" t="n">
-        <v>25.6</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02-2412-SELL</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3135,85 +3135,85 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2412</v>
+        <v>5880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F51" t="n">
-        <v>137.5</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02-3045-SELL</t>
+          <t>2026-09-03-0050-BUY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3045</v>
+        <v>50</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>1000</v>
       </c>
       <c r="F52" t="n">
-        <v>116</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02-4904-SELL</t>
+          <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4904</v>
+        <v>5880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>1000</v>
       </c>
       <c r="F53" t="n">
-        <v>102.5</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02-0050-BUY</t>
+          <t>2026-09-04-5880-BUY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3224,22 +3224,22 @@
         <v>1000</v>
       </c>
       <c r="F54" t="n">
-        <v>106.8</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-09-07-5880-BUY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2880</v>
+        <v>5880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3247,477 +3247,9 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F55" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-02-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F56" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-02-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F57" t="n">
-        <v>36.25</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-02-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F58" t="n">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-03-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F59" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-09-03-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F60" t="n">
-        <v>103.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-03-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F61" t="n">
-        <v>43.45</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-03-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F62" t="n">
-        <v>50.4</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-03-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F63" t="n">
-        <v>36.85</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-03-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F64" t="n">
-        <v>26.7</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-04-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F65" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-04-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F66" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-04-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F67" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-04-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F68" t="n">
-        <v>49.55</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-04-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F69" t="n">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-04-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F70" t="n">
-        <v>26.65</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-07-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F71" t="n">
-        <v>44.35</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-07-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F72" t="n">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-07-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F73" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -3732,7 +3264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3790,7 +3322,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3804,7 +3336,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3815,13 +3347,13 @@
         <v>2000</v>
       </c>
       <c r="G2" t="n">
-        <v>136.56825</v>
+        <v>102.95145</v>
       </c>
       <c r="H2" t="n">
-        <v>273136.5</v>
+        <v>205902.9</v>
       </c>
       <c r="I2" t="n">
-        <v>233.5317075</v>
+        <v>176.0469795</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -3830,7 +3362,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3844,7 +3376,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3852,16 +3384,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="G3" t="n">
-        <v>39.169575</v>
+        <v>136.56825</v>
       </c>
       <c r="H3" t="n">
-        <v>470034.9</v>
+        <v>273136.5</v>
       </c>
       <c r="I3" t="n">
-        <v>401.8798395</v>
+        <v>233.5317075</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -3870,7 +3402,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3884,7 +3416,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3892,16 +3424,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G4" t="n">
-        <v>46.873425</v>
+        <v>39.169575</v>
       </c>
       <c r="H4" t="n">
-        <v>468734.25</v>
+        <v>430865.325</v>
       </c>
       <c r="I4" t="n">
-        <v>400.76778375</v>
+        <v>368.3898528749999</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -3910,7 +3442,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3924,7 +3456,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3932,16 +3464,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="G5" t="n">
-        <v>33.51674999999999</v>
+        <v>46.873425</v>
       </c>
       <c r="H5" t="n">
-        <v>469234.5</v>
+        <v>421860.825</v>
       </c>
       <c r="I5" t="n">
-        <v>401.1954974999999</v>
+        <v>360.6910053749999</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -3950,7 +3482,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-3045-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3964,7 +3496,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3972,16 +3504,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="G6" t="n">
-        <v>115.0575</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>230115</v>
+        <v>435717.75</v>
       </c>
       <c r="I6" t="n">
-        <v>196.748325</v>
+        <v>372.5386762499999</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -3990,7 +3522,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24-4904-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4004,7 +3536,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4012,16 +3544,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G7" t="n">
-        <v>101.55075</v>
+        <v>115.0575</v>
       </c>
       <c r="H7" t="n">
-        <v>304652.25</v>
+        <v>230115</v>
       </c>
       <c r="I7" t="n">
-        <v>260.47767375</v>
+        <v>196.748325</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -4030,7 +3562,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4044,7 +3576,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4052,16 +3584,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="G8" t="n">
-        <v>25.0125</v>
+        <v>101.55075</v>
       </c>
       <c r="H8" t="n">
-        <v>475237.5</v>
+        <v>203101.5</v>
       </c>
       <c r="I8" t="n">
-        <v>406.3280625</v>
+        <v>173.6517825</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -4070,21 +3602,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4092,16 +3624,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="G9" t="n">
-        <v>104.15205</v>
+        <v>25.0125</v>
       </c>
       <c r="H9" t="n">
-        <v>104152.05</v>
+        <v>450225</v>
       </c>
       <c r="I9" t="n">
-        <v>89.05000274999999</v>
+        <v>384.942375</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -4110,7 +3642,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4124,7 +3656,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4132,16 +3664,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G10" t="n">
-        <v>136.56825</v>
+        <v>104.15205</v>
       </c>
       <c r="H10" t="n">
-        <v>273136.5</v>
+        <v>312456.15</v>
       </c>
       <c r="I10" t="n">
-        <v>233.5317075</v>
+        <v>267.15000825</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -4150,7 +3682,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4164,7 +3696,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4172,16 +3704,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="G11" t="n">
-        <v>39.6198</v>
+        <v>136.56825</v>
       </c>
       <c r="H11" t="n">
-        <v>475437.6</v>
+        <v>273136.5</v>
       </c>
       <c r="I11" t="n">
-        <v>406.499148</v>
+        <v>233.5317075</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -4190,7 +3722,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4204,7 +3736,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4212,16 +3744,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G12" t="n">
-        <v>46.92345</v>
+        <v>39.6198</v>
       </c>
       <c r="H12" t="n">
-        <v>469234.5</v>
+        <v>435817.8</v>
       </c>
       <c r="I12" t="n">
-        <v>401.1954974999999</v>
+        <v>372.624219</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -4230,7 +3762,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4244,7 +3776,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4252,16 +3784,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="G13" t="n">
-        <v>33.51674999999999</v>
+        <v>46.92345</v>
       </c>
       <c r="H13" t="n">
-        <v>469234.5</v>
+        <v>422311.0499999999</v>
       </c>
       <c r="I13" t="n">
-        <v>401.1954974999999</v>
+        <v>361.0759477499999</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -4270,7 +3802,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-3045-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4284,7 +3816,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4292,16 +3824,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="G14" t="n">
-        <v>115.0575</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>230115</v>
+        <v>435717.75</v>
       </c>
       <c r="I14" t="n">
-        <v>196.748325</v>
+        <v>372.5386762499999</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -4310,7 +3842,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25-4904-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4324,7 +3856,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4332,16 +3864,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G15" t="n">
-        <v>102.55125</v>
+        <v>115.0575</v>
       </c>
       <c r="H15" t="n">
-        <v>307653.75</v>
+        <v>230115</v>
       </c>
       <c r="I15" t="n">
-        <v>263.04395625</v>
+        <v>196.748325</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -4350,7 +3882,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4364,7 +3896,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4372,16 +3904,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19000</v>
+        <v>3000</v>
       </c>
       <c r="G16" t="n">
-        <v>25.0125</v>
+        <v>102.55125</v>
       </c>
       <c r="H16" t="n">
-        <v>475237.5</v>
+        <v>307653.75</v>
       </c>
       <c r="I16" t="n">
-        <v>406.3280625</v>
+        <v>263.04395625</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -4390,21 +3922,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4412,16 +3944,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1000</v>
+        <v>17000</v>
       </c>
       <c r="G17" t="n">
-        <v>106.55325</v>
+        <v>25.0125</v>
       </c>
       <c r="H17" t="n">
-        <v>106553.25</v>
+        <v>425212.5</v>
       </c>
       <c r="I17" t="n">
-        <v>91.10302874999998</v>
+        <v>363.5566875</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -4430,7 +3962,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4444,7 +3976,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4452,16 +3984,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G18" t="n">
-        <v>136.56825</v>
+        <v>106.55325</v>
       </c>
       <c r="H18" t="n">
-        <v>136568.25</v>
+        <v>213106.5</v>
       </c>
       <c r="I18" t="n">
-        <v>116.76585375</v>
+        <v>182.2060575</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -4470,7 +4002,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4484,7 +4016,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4492,16 +4024,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="G19" t="n">
-        <v>39.8199</v>
+        <v>136.56825</v>
       </c>
       <c r="H19" t="n">
-        <v>517658.7</v>
+        <v>136568.25</v>
       </c>
       <c r="I19" t="n">
-        <v>442.5981885</v>
+        <v>116.76585375</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -4510,7 +4042,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4524,7 +4056,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4532,16 +4064,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="G20" t="n">
-        <v>46.6233</v>
+        <v>39.8199</v>
       </c>
       <c r="H20" t="n">
-        <v>512856.3</v>
+        <v>477838.8</v>
       </c>
       <c r="I20" t="n">
-        <v>438.4921365</v>
+        <v>408.552174</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -4550,7 +4082,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4564,7 +4096,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4572,16 +4104,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="G21" t="n">
-        <v>33.51674999999999</v>
+        <v>46.6233</v>
       </c>
       <c r="H21" t="n">
-        <v>536267.9999999999</v>
+        <v>466233</v>
       </c>
       <c r="I21" t="n">
-        <v>458.5091399999999</v>
+        <v>398.629215</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -4590,7 +4122,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-3045-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4604,7 +4136,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4612,16 +4144,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="G22" t="n">
-        <v>116.058</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>116058</v>
+        <v>469234.5</v>
       </c>
       <c r="I22" t="n">
-        <v>99.22959</v>
+        <v>401.1954974999999</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -4630,7 +4162,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26-4904-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4644,7 +4176,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4655,13 +4187,13 @@
         <v>2000</v>
       </c>
       <c r="G23" t="n">
-        <v>101.0505</v>
+        <v>116.058</v>
       </c>
       <c r="H23" t="n">
-        <v>202101</v>
+        <v>232116</v>
       </c>
       <c r="I23" t="n">
-        <v>172.796355</v>
+        <v>198.45918</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -4670,7 +4202,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4684,7 +4216,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4692,16 +4224,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="G24" t="n">
-        <v>25.0125</v>
+        <v>101.0505</v>
       </c>
       <c r="H24" t="n">
-        <v>525262.5</v>
+        <v>202101</v>
       </c>
       <c r="I24" t="n">
-        <v>449.0994375</v>
+        <v>172.796355</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -4710,21 +4242,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4732,16 +4264,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="G25" t="n">
-        <v>107.15355</v>
+        <v>25.0125</v>
       </c>
       <c r="H25" t="n">
-        <v>107153.55</v>
+        <v>475237.5</v>
       </c>
       <c r="I25" t="n">
-        <v>91.61628525</v>
+        <v>406.3280625</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -4750,7 +4282,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4764,7 +4296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4772,16 +4304,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G26" t="n">
-        <v>136.068</v>
+        <v>107.15355</v>
       </c>
       <c r="H26" t="n">
-        <v>136068</v>
+        <v>321460.65</v>
       </c>
       <c r="I26" t="n">
-        <v>116.33814</v>
+        <v>274.84885575</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -4790,7 +4322,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4804,7 +4336,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4812,16 +4344,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
       <c r="G27" t="n">
-        <v>39.369675</v>
+        <v>136.068</v>
       </c>
       <c r="H27" t="n">
-        <v>551175.4500000001</v>
+        <v>136068</v>
       </c>
       <c r="I27" t="n">
-        <v>471.2550097500001</v>
+        <v>116.33814</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -4830,7 +4362,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4844,7 +4376,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4852,16 +4384,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="G28" t="n">
-        <v>46.92345</v>
+        <v>39.369675</v>
       </c>
       <c r="H28" t="n">
-        <v>563081.3999999999</v>
+        <v>511805.775</v>
       </c>
       <c r="I28" t="n">
-        <v>481.4345969999999</v>
+        <v>437.593937625</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -4870,7 +4402,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4884,7 +4416,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4892,16 +4424,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="G29" t="n">
-        <v>33.51674999999999</v>
+        <v>46.92345</v>
       </c>
       <c r="H29" t="n">
-        <v>569784.7499999999</v>
+        <v>516157.95</v>
       </c>
       <c r="I29" t="n">
-        <v>487.1659612499999</v>
+        <v>441.31504725</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -4910,7 +4442,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-3045-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4924,7 +4456,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3045</v>
+        <v>2892</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4932,16 +4464,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="G30" t="n">
-        <v>115.55775</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>115557.75</v>
+        <v>536267.9999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>98.80187625000001</v>
+        <v>458.5091399999999</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -4950,7 +4482,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27-4904-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4964,7 +4496,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4904</v>
+        <v>3045</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4975,13 +4507,13 @@
         <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>101.55075</v>
+        <v>115.55775</v>
       </c>
       <c r="H31" t="n">
-        <v>101550.75</v>
+        <v>115557.75</v>
       </c>
       <c r="I31" t="n">
-        <v>86.82589125</v>
+        <v>98.80187625000001</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -4990,7 +4522,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5004,7 +4536,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5880</v>
+        <v>4904</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5012,16 +4544,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>23000</v>
+        <v>1000</v>
       </c>
       <c r="G32" t="n">
-        <v>25.11255</v>
+        <v>101.55075</v>
       </c>
       <c r="H32" t="n">
-        <v>577588.65</v>
+        <v>101550.75</v>
       </c>
       <c r="I32" t="n">
-        <v>493.83829575</v>
+        <v>86.82589125</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
@@ -5030,21 +4562,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5052,16 +4584,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3000</v>
+        <v>21000</v>
       </c>
       <c r="G33" t="n">
-        <v>105.6528</v>
+        <v>25.11255</v>
       </c>
       <c r="H33" t="n">
-        <v>316958.4</v>
+        <v>527363.5499999999</v>
       </c>
       <c r="I33" t="n">
-        <v>270.999432</v>
+        <v>450.89583525</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -5070,7 +4602,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5084,7 +4616,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5092,16 +4624,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="G34" t="n">
-        <v>40.270125</v>
+        <v>105.6528</v>
       </c>
       <c r="H34" t="n">
-        <v>604051.875</v>
+        <v>316958.4</v>
       </c>
       <c r="I34" t="n">
-        <v>516.464353125</v>
+        <v>270.999432</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -5110,7 +4642,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5124,7 +4656,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5132,16 +4664,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="G35" t="n">
-        <v>47.92395</v>
+        <v>40.270125</v>
       </c>
       <c r="H35" t="n">
-        <v>575087.4</v>
+        <v>563781.75</v>
       </c>
       <c r="I35" t="n">
-        <v>491.699727</v>
+        <v>482.03339625</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -5150,7 +4682,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5164,7 +4696,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5172,16 +4704,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="G36" t="n">
-        <v>34.31715</v>
+        <v>47.92395</v>
       </c>
       <c r="H36" t="n">
-        <v>617708.7</v>
+        <v>575087.4</v>
       </c>
       <c r="I36" t="n">
-        <v>528.1409384999999</v>
+        <v>491.699727</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -5190,7 +4722,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5204,7 +4736,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5212,16 +4744,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>24000</v>
+        <v>17000</v>
       </c>
       <c r="G37" t="n">
-        <v>25.262625</v>
+        <v>34.31715</v>
       </c>
       <c r="H37" t="n">
-        <v>606303</v>
+        <v>583391.5499999999</v>
       </c>
       <c r="I37" t="n">
-        <v>518.389065</v>
+        <v>498.7997752499999</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -5230,21 +4762,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31-0050-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5252,16 +4784,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="G38" t="n">
-        <v>106.55325</v>
+        <v>25.262625</v>
       </c>
       <c r="H38" t="n">
-        <v>213106.5</v>
+        <v>581040.375</v>
       </c>
       <c r="I38" t="n">
-        <v>182.2060575</v>
+        <v>496.789520625</v>
       </c>
       <c r="J38" t="n">
         <v>5</v>
@@ -5270,7 +4802,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-31-0050-BUY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5284,7 +4816,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5292,16 +4824,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="G39" t="n">
-        <v>40.82039999999999</v>
+        <v>106.55325</v>
       </c>
       <c r="H39" t="n">
-        <v>204102</v>
+        <v>106553.25</v>
       </c>
       <c r="I39" t="n">
-        <v>174.50721</v>
+        <v>91.10302874999998</v>
       </c>
       <c r="J39" t="n">
         <v>5</v>
@@ -5310,7 +4842,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5324,7 +4856,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -5335,13 +4867,13 @@
         <v>5000</v>
       </c>
       <c r="G40" t="n">
-        <v>48.2241</v>
+        <v>40.82039999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>241120.5</v>
+        <v>204102</v>
       </c>
       <c r="I40" t="n">
-        <v>206.1580275</v>
+        <v>174.50721</v>
       </c>
       <c r="J40" t="n">
         <v>5</v>
@@ -5350,7 +4882,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5364,7 +4896,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5372,16 +4904,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G41" t="n">
-        <v>35.067525</v>
+        <v>48.2241</v>
       </c>
       <c r="H41" t="n">
-        <v>210405.15</v>
+        <v>192896.4</v>
       </c>
       <c r="I41" t="n">
-        <v>179.89640325</v>
+        <v>164.926422</v>
       </c>
       <c r="J41" t="n">
         <v>5</v>
@@ -5390,7 +4922,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5404,7 +4936,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -5412,16 +4944,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="G42" t="n">
-        <v>25.362675</v>
+        <v>35.067525</v>
       </c>
       <c r="H42" t="n">
-        <v>228264.075</v>
+        <v>210405.15</v>
       </c>
       <c r="I42" t="n">
-        <v>195.165784125</v>
+        <v>179.89640325</v>
       </c>
       <c r="J42" t="n">
         <v>5</v>
@@ -5430,38 +4962,38 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01-2412-SELL</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
       <c r="D43" t="n">
-        <v>2412</v>
+        <v>5880</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="G43" t="n">
-        <v>136.43175</v>
+        <v>25.362675</v>
       </c>
       <c r="H43" t="n">
-        <v>136431.75</v>
+        <v>202901.4</v>
       </c>
       <c r="I43" t="n">
-        <v>525.94439625</v>
+        <v>173.480697</v>
       </c>
       <c r="J43" t="n">
         <v>5</v>
@@ -5470,7 +5002,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01-3045-SELL</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5484,24 +5016,24 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G44" t="n">
-        <v>115.44225</v>
+        <v>41.970975</v>
       </c>
       <c r="H44" t="n">
-        <v>115442.25</v>
+        <v>83941.95000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>445.02987375</v>
+        <v>71.77036725000001</v>
       </c>
       <c r="J44" t="n">
         <v>5</v>
@@ -5510,7 +5042,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01-4904-SELL</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5524,24 +5056,24 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G45" t="n">
-        <v>100.44975</v>
+        <v>48.274125</v>
       </c>
       <c r="H45" t="n">
-        <v>100449.75</v>
+        <v>96548.25</v>
       </c>
       <c r="I45" t="n">
-        <v>387.23378625</v>
+        <v>82.54875375</v>
       </c>
       <c r="J45" t="n">
         <v>5</v>
@@ -5550,7 +5082,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5564,7 +5096,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>50</v>
+        <v>2892</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -5575,13 +5107,13 @@
         <v>2000</v>
       </c>
       <c r="G46" t="n">
-        <v>107.55375</v>
+        <v>35.567775</v>
       </c>
       <c r="H46" t="n">
-        <v>215107.5</v>
+        <v>71135.54999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>183.9169125</v>
+        <v>60.82089524999999</v>
       </c>
       <c r="J46" t="n">
         <v>5</v>
@@ -5590,7 +5122,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5604,7 +5136,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2880</v>
+        <v>5880</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5612,16 +5144,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G47" t="n">
-        <v>41.970975</v>
+        <v>25.6128</v>
       </c>
       <c r="H47" t="n">
-        <v>83941.95000000001</v>
+        <v>102451.2</v>
       </c>
       <c r="I47" t="n">
-        <v>71.77036725000001</v>
+        <v>87.595776</v>
       </c>
       <c r="J47" t="n">
         <v>5</v>
@@ -5630,21 +5162,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -5652,16 +5184,16 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G48" t="n">
-        <v>48.274125</v>
+        <v>42.92144999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>96548.25</v>
+        <v>42921.44999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>82.54875375</v>
+        <v>36.69783974999999</v>
       </c>
       <c r="J48" t="n">
         <v>5</v>
@@ -5670,21 +5202,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5692,16 +5224,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G49" t="n">
-        <v>35.567775</v>
+        <v>49.0245</v>
       </c>
       <c r="H49" t="n">
-        <v>106703.325</v>
+        <v>49024.49999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>91.231342875</v>
+        <v>41.9159475</v>
       </c>
       <c r="J49" t="n">
         <v>5</v>
@@ -5710,21 +5242,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -5732,16 +5264,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="G50" t="n">
-        <v>25.6128</v>
+        <v>36.268125</v>
       </c>
       <c r="H50" t="n">
-        <v>102451.2</v>
+        <v>36268.125</v>
       </c>
       <c r="I50" t="n">
-        <v>87.595776</v>
+        <v>31.009246875</v>
       </c>
       <c r="J50" t="n">
         <v>5</v>
@@ -5750,7 +5282,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02-2412-SELL</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5764,746 +5296,26 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2412</v>
+        <v>5880</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1000</v>
       </c>
       <c r="G51" t="n">
-        <v>137.43125</v>
+        <v>26.31315</v>
       </c>
       <c r="H51" t="n">
-        <v>137431.25</v>
+        <v>26313.15</v>
       </c>
       <c r="I51" t="n">
-        <v>529.79746875</v>
+        <v>22.49774325</v>
       </c>
       <c r="J51" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-09-02-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G52" t="n">
-        <v>115.942</v>
-      </c>
-      <c r="H52" t="n">
-        <v>115942</v>
-      </c>
-      <c r="I52" t="n">
-        <v>446.95641</v>
-      </c>
-      <c r="J52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-09-02-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G53" t="n">
-        <v>102.44875</v>
-      </c>
-      <c r="H53" t="n">
-        <v>102448.75</v>
-      </c>
-      <c r="I53" t="n">
-        <v>394.93993125</v>
-      </c>
-      <c r="J53" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-09-02-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>50</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G54" t="n">
-        <v>106.95345</v>
-      </c>
-      <c r="H54" t="n">
-        <v>106953.45</v>
-      </c>
-      <c r="I54" t="n">
-        <v>91.44519975</v>
-      </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-09-02-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G55" t="n">
-        <v>42.92144999999999</v>
-      </c>
-      <c r="H55" t="n">
-        <v>85842.89999999998</v>
-      </c>
-      <c r="I55" t="n">
-        <v>73.39567949999999</v>
-      </c>
-      <c r="J55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-02-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G56" t="n">
-        <v>49.0245</v>
-      </c>
-      <c r="H56" t="n">
-        <v>49024.49999999999</v>
-      </c>
-      <c r="I56" t="n">
-        <v>41.9159475</v>
-      </c>
-      <c r="J56" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-02-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G57" t="n">
-        <v>36.268125</v>
-      </c>
-      <c r="H57" t="n">
-        <v>72536.25</v>
-      </c>
-      <c r="I57" t="n">
-        <v>62.01849375</v>
-      </c>
-      <c r="J57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-02-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G58" t="n">
-        <v>26.31315</v>
-      </c>
-      <c r="H58" t="n">
-        <v>78939.45</v>
-      </c>
-      <c r="I58" t="n">
-        <v>67.49322975</v>
-      </c>
-      <c r="J58" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-03-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G59" t="n">
-        <v>117.44125</v>
-      </c>
-      <c r="H59" t="n">
-        <v>117441.25</v>
-      </c>
-      <c r="I59" t="n">
-        <v>452.73601875</v>
-      </c>
-      <c r="J59" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-09-03-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G60" t="n">
-        <v>102.9485</v>
-      </c>
-      <c r="H60" t="n">
-        <v>102948.5</v>
-      </c>
-      <c r="I60" t="n">
-        <v>396.8664675000001</v>
-      </c>
-      <c r="J60" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-03-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G61" t="n">
-        <v>43.771875</v>
-      </c>
-      <c r="H61" t="n">
-        <v>87543.74999999999</v>
-      </c>
-      <c r="I61" t="n">
-        <v>74.84990624999999</v>
-      </c>
-      <c r="J61" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-03-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G62" t="n">
-        <v>50.8254</v>
-      </c>
-      <c r="H62" t="n">
-        <v>101650.8</v>
-      </c>
-      <c r="I62" t="n">
-        <v>86.91143399999999</v>
-      </c>
-      <c r="J62" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-03-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G63" t="n">
-        <v>26.71335</v>
-      </c>
-      <c r="H63" t="n">
-        <v>26713.35</v>
-      </c>
-      <c r="I63" t="n">
-        <v>22.83991425</v>
-      </c>
-      <c r="J63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-04-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G64" t="n">
-        <v>117.941</v>
-      </c>
-      <c r="H64" t="n">
-        <v>117941</v>
-      </c>
-      <c r="I64" t="n">
-        <v>454.662555</v>
-      </c>
-      <c r="J64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-04-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G65" t="n">
-        <v>104.44775</v>
-      </c>
-      <c r="H65" t="n">
-        <v>104447.75</v>
-      </c>
-      <c r="I65" t="n">
-        <v>402.64607625</v>
-      </c>
-      <c r="J65" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-04-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G66" t="n">
-        <v>44.72235</v>
-      </c>
-      <c r="H66" t="n">
-        <v>44722.35</v>
-      </c>
-      <c r="I66" t="n">
-        <v>38.23760925</v>
-      </c>
-      <c r="J66" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-04-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G67" t="n">
-        <v>50.4252</v>
-      </c>
-      <c r="H67" t="n">
-        <v>50425.2</v>
-      </c>
-      <c r="I67" t="n">
-        <v>43.11354599999999</v>
-      </c>
-      <c r="J67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-04-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G68" t="n">
-        <v>38.019</v>
-      </c>
-      <c r="H68" t="n">
-        <v>76038</v>
-      </c>
-      <c r="I68" t="n">
-        <v>65.01249</v>
-      </c>
-      <c r="J68" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-04-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G69" t="n">
-        <v>26.763375</v>
-      </c>
-      <c r="H69" t="n">
-        <v>53526.75</v>
-      </c>
-      <c r="I69" t="n">
-        <v>45.76537125</v>
-      </c>
-      <c r="J69" t="n">
         <v>5</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:17.959963+00:00</t>
+          <t>2026-09-08T00:51:54.587142+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:18.674147+00:00</t>
+          <t>2026-09-08T00:51:55.260389+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:19.428691+00:00</t>
+          <t>2026-09-08T00:51:55.953983+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:20.177127+00:00</t>
+          <t>2026-09-08T00:51:56.625361+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:20.919433+00:00</t>
+          <t>2026-09-08T00:51:57.302543+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:21.635111+00:00</t>
+          <t>2026-09-08T00:51:57.984715+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:22.383059+00:00</t>
+          <t>2026-09-08T00:51:58.675569+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:23.103058+00:00</t>
+          <t>2026-09-08T00:51:59.360649+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:23.841450+00:00</t>
+          <t>2026-09-08T00:52:00.028473+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:24.577650+00:00</t>
+          <t>2026-09-08T00:52:00.693783+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07T17:02:25.287190+00:00</t>
+          <t>2026-09-08T00:52:01.341982+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15000000</v>
+        <v>3000000</v>
       </c>
       <c r="C2" t="n">
-        <v>15000000</v>
+        <v>3000000</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1330,28 +1330,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15014804.1711105</v>
+        <v>3001924.395765</v>
       </c>
       <c r="C3" t="n">
-        <v>12306554.1711105</v>
+        <v>2685574.395765</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1263253238859735</v>
+        <v>0.1053824008513653</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0540466589342124</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8196280171798139</v>
+        <v>0.8946175991486346</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1378,28 +1378,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14985455.1789135</v>
+        <v>2998911.005652251</v>
       </c>
       <c r="C4" t="n">
-        <v>9499955.1789135</v>
+        <v>2417111.005652251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2514171211363341</v>
+        <v>0.1940037563313623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1075709733707852</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0070668524069268</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6339450530859536</v>
+        <v>0.8059962436686375</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1426,28 +1426,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14955410.5851835</v>
+        <v>2994284.317075251</v>
       </c>
       <c r="C5" t="n">
-        <v>6844360.585183501</v>
+        <v>2101884.317075251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3899558602408268</v>
+        <v>0.2980344902155704</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1382108493930484</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0141821582758904</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.457651132090234</v>
+        <v>0.7019655097844294</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1474,28 +1474,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15145673.009127</v>
+        <v>3024257.628498252</v>
       </c>
       <c r="C6" t="n">
-        <v>4120073.009127002</v>
+        <v>1786657.628498251</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5476316565795237</v>
+        <v>0.4092243955468014</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1591543669632506</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0211842682597631</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2720297081974623</v>
+        <v>0.5907756044531984</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1522,28 +1522,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15352487.94061138</v>
+        <v>3051687.935647626</v>
       </c>
       <c r="C7" t="n">
-        <v>1397637.940611377</v>
+        <v>1513537.935647627</v>
       </c>
       <c r="D7" t="n">
-        <v>0.709744898817102</v>
+        <v>0.504032532957396</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1576943104834374</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04152421434663</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1342914987650466</v>
+        <v>0.4959674670426039</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1570,28 +1570,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15469251.782129</v>
+        <v>3068713.905429002</v>
       </c>
       <c r="C8" t="n">
-        <v>299701.7821290023</v>
+        <v>1237213.905429002</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7682304333380263</v>
+        <v>0.5968298304901639</v>
       </c>
       <c r="E8" t="n">
-        <v>0.156310081059862</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0560854534026204</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1128939204032211</v>
+        <v>0.403170169509836</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1618,28 +1618,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15697598.03592038</v>
+        <v>3106745.469685002</v>
       </c>
       <c r="C9" t="n">
-        <v>45398.03592037737</v>
+        <v>891145.4696850018</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7960899477362172</v>
+        <v>0.6787810654516911</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1329821285538865</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.068035886608647</v>
+        <v>0.0343768104088773</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08953108877202649</v>
+        <v>0.2868421241394314</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1666,28 +1666,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15930765.52356013</v>
+        <v>3146815.694174252</v>
       </c>
       <c r="C10" t="n">
-        <v>6215.523560127462</v>
+        <v>647515.6941742518</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8165238500788047</v>
+        <v>0.7604830509871878</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1097561819872453</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07332980943523019</v>
+        <v>0.0337484016609583</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06871671032066549</v>
+        <v>0.2057685473518539</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1714,28 +1714,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15968263.16981938</v>
+        <v>3151865.075629502</v>
       </c>
       <c r="C11" t="n">
-        <v>9663.169819377516</v>
+        <v>462365.0756295018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.829376361045395</v>
+        <v>0.8190705940940044</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0956898056945841</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0743286848029462</v>
+        <v>0.0342336989087167</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0633020282116603</v>
+        <v>0.1466957069972788</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1762,28 +1762,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16027790.18217163</v>
+        <v>3163015.075629502</v>
       </c>
       <c r="C12" t="n">
-        <v>6290.182171627515</v>
+        <v>462365.0756295018</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8433227442068135</v>
+        <v>0.8190760834373798</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08085955613778829</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0754252449189601</v>
+        <v>0.0347453291787196</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0334288353774321</v>
+        <v>0.1461785873839004</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1814,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,7 +1852,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1872,13 +1872,13 @@
         <v>2000</v>
       </c>
       <c r="F2" t="n">
-        <v>136.5</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1895,16 +1895,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F3" t="n">
-        <v>39.25</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F4" t="n">
-        <v>46.85</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1947,25 +1947,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="F5" t="n">
-        <v>33.55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-3045-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1976,22 +1976,22 @@
         <v>2000</v>
       </c>
       <c r="F6" t="n">
-        <v>115</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24-4904-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1999,25 +1999,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F7" t="n">
-        <v>101.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2025,16 +2025,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F9" t="n">
-        <v>104.4</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2080,22 +2080,22 @@
         <v>2000</v>
       </c>
       <c r="F10" t="n">
-        <v>136.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2103,25 +2103,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F11" t="n">
-        <v>39.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2129,25 +2129,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="F13" t="n">
-        <v>33.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-3045-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,22 +2184,22 @@
         <v>2000</v>
       </c>
       <c r="F14" t="n">
-        <v>115.5</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25-4904-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F15" t="n">
-        <v>102.5</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="F16" t="n">
-        <v>25.05</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,25 +2259,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F17" t="n">
-        <v>105.9</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F18" t="n">
-        <v>136</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2311,25 +2311,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="F19" t="n">
-        <v>39.6</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2337,25 +2337,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="F20" t="n">
-        <v>46.6</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="F21" t="n">
-        <v>33.4</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-3045-BUY</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2389,25 +2389,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F22" t="n">
-        <v>115.5</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26-4904-BUY</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F23" t="n">
-        <v>101</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2467,25 +2467,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F25" t="n">
-        <v>106.05</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-09-01-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2496,18 +2496,18 @@
         <v>1000</v>
       </c>
       <c r="F26" t="n">
-        <v>135.5</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2519,21 +2519,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
       <c r="F27" t="n">
-        <v>39.35</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="F28" t="n">
-        <v>46.15</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2571,25 +2571,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="F29" t="n">
-        <v>33.35</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-3045-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3045</v>
+        <v>5880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2597,25 +2597,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F30" t="n">
-        <v>115.5</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27-4904-BUY</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4904</v>
+        <v>2880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2626,22 +2626,22 @@
         <v>1000</v>
       </c>
       <c r="F31" t="n">
-        <v>101.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>23000</v>
+        <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>25.05</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>2892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2675,25 +2675,25 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F33" t="n">
-        <v>106.95</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2880</v>
+        <v>5880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="F34" t="n">
-        <v>40.25</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-09-03-2880-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="F35" t="n">
-        <v>48.2</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-09-03-2886-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2753,25 +2753,25 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>18000</v>
+        <v>1000</v>
       </c>
       <c r="F36" t="n">
-        <v>34.4</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-09-03-2892-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2779,25 +2779,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>24000</v>
+        <v>1000</v>
       </c>
       <c r="F37" t="n">
-        <v>25.25</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31-0050-BUY</t>
+          <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2808,917 +2808,7 @@
         <v>2000</v>
       </c>
       <c r="F38" t="n">
-        <v>106.25</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-08-31-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F39" t="n">
-        <v>41.35</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-08-31-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F40" t="n">
-        <v>48.55</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-08-31-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F41" t="n">
-        <v>35.3</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-31-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F42" t="n">
-        <v>25.55</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-09-01-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2412</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F43" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-09-01-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F44" t="n">
-        <v>115.5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-09-01-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F45" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-09-01-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>50</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F46" t="n">
-        <v>108.45</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-09-01-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F47" t="n">
-        <v>41.95</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-09-01-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F48" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-09-01-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F49" t="n">
-        <v>35.9</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-01-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F50" t="n">
-        <v>25.6</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-09-02-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2412</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F51" t="n">
-        <v>137.5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-09-02-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F52" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-09-02-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F53" t="n">
-        <v>102.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-09-02-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>50</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F54" t="n">
-        <v>106.8</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-09-02-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F55" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-02-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F56" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-02-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F57" t="n">
-        <v>36.25</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-02-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F58" t="n">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-03-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F59" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-09-03-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F60" t="n">
-        <v>103.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-03-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F61" t="n">
-        <v>43.45</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-03-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F62" t="n">
-        <v>50.4</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-03-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F63" t="n">
-        <v>36.85</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-03-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F64" t="n">
         <v>26.7</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-04-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>3045</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F65" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-04-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>4904</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F66" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-04-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F67" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-04-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>2886</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F68" t="n">
-        <v>49.55</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-04-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F69" t="n">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-04-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F70" t="n">
-        <v>26.65</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-07-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F71" t="n">
-        <v>44.35</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-07-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>2892</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F72" t="n">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-07-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F73" t="n">
-        <v>26.5</v>
       </c>
     </row>
   </sheetData>
@@ -3732,7 +2822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3790,7 +2880,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2412-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3804,7 +2894,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3815,13 +2905,13 @@
         <v>2000</v>
       </c>
       <c r="G2" t="n">
-        <v>136.56825</v>
+        <v>39.169575</v>
       </c>
       <c r="H2" t="n">
-        <v>273136.5</v>
+        <v>78339.14999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>233.5317075</v>
+        <v>66.97997324999999</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -3830,7 +2920,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3844,7 +2934,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3852,16 +2942,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="G3" t="n">
-        <v>39.169575</v>
+        <v>46.873425</v>
       </c>
       <c r="H3" t="n">
-        <v>470034.9</v>
+        <v>93746.85000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>401.8798395</v>
+        <v>80.15355674999999</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -3870,7 +2960,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3884,7 +2974,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3892,16 +2982,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="G4" t="n">
-        <v>46.873425</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>468734.25</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>400.76778375</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -3910,7 +3000,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3924,7 +3014,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3932,16 +3022,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="G5" t="n">
-        <v>33.51674999999999</v>
+        <v>25.0125</v>
       </c>
       <c r="H5" t="n">
-        <v>469234.5</v>
+        <v>75037.5</v>
       </c>
       <c r="I5" t="n">
-        <v>401.1954974999999</v>
+        <v>64.15706249999999</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -3950,21 +3040,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24-3045-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3975,13 +3065,13 @@
         <v>2000</v>
       </c>
       <c r="G6" t="n">
-        <v>115.0575</v>
+        <v>39.6198</v>
       </c>
       <c r="H6" t="n">
-        <v>230115</v>
+        <v>79239.59999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>196.748325</v>
+        <v>67.74985799999999</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -3990,21 +3080,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24-4904-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4012,16 +3102,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G7" t="n">
-        <v>101.55075</v>
+        <v>46.92345</v>
       </c>
       <c r="H7" t="n">
-        <v>304652.25</v>
+        <v>46923.45</v>
       </c>
       <c r="I7" t="n">
-        <v>260.47767375</v>
+        <v>40.11954975</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -4030,21 +3120,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4052,16 +3142,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="G8" t="n">
-        <v>25.0125</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>475237.5</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>406.3280625</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -4070,7 +3160,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-0050-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4084,7 +3174,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4092,16 +3182,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G9" t="n">
-        <v>104.15205</v>
+        <v>25.0125</v>
       </c>
       <c r="H9" t="n">
-        <v>104152.05</v>
+        <v>75037.5</v>
       </c>
       <c r="I9" t="n">
-        <v>89.05000274999999</v>
+        <v>64.15706249999999</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -4110,21 +3200,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25-2412-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4135,13 +3225,13 @@
         <v>2000</v>
       </c>
       <c r="G10" t="n">
-        <v>136.56825</v>
+        <v>39.8199</v>
       </c>
       <c r="H10" t="n">
-        <v>273136.5</v>
+        <v>79639.79999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>233.5317075</v>
+        <v>68.09202899999998</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -4150,21 +3240,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4172,16 +3262,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="G11" t="n">
-        <v>39.6198</v>
+        <v>46.6233</v>
       </c>
       <c r="H11" t="n">
-        <v>475437.6</v>
+        <v>93246.60000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>406.499148</v>
+        <v>79.725843</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -4190,21 +3280,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4212,16 +3302,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="G12" t="n">
-        <v>46.92345</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>469234.5</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>401.1954974999999</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -4230,21 +3320,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4252,16 +3342,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="G13" t="n">
-        <v>33.51674999999999</v>
+        <v>25.0125</v>
       </c>
       <c r="H13" t="n">
-        <v>469234.5</v>
+        <v>75037.5</v>
       </c>
       <c r="I13" t="n">
-        <v>401.1954974999999</v>
+        <v>64.15706249999999</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -4270,21 +3360,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25-3045-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4295,13 +3385,13 @@
         <v>2000</v>
       </c>
       <c r="G14" t="n">
-        <v>115.0575</v>
+        <v>39.369675</v>
       </c>
       <c r="H14" t="n">
-        <v>230115</v>
+        <v>78739.35000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>196.748325</v>
+        <v>67.32214425000001</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -4310,21 +3400,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25-4904-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4332,16 +3422,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G15" t="n">
-        <v>102.55125</v>
+        <v>46.92345</v>
       </c>
       <c r="H15" t="n">
-        <v>307653.75</v>
+        <v>93846.89999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>263.04395625</v>
+        <v>80.23909949999999</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -4350,21 +3440,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4372,16 +3462,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="G16" t="n">
-        <v>25.0125</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>475237.5</v>
+        <v>67033.49999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>406.3280625</v>
+        <v>57.31364249999999</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -4390,21 +3480,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26-0050-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4412,16 +3502,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G17" t="n">
-        <v>106.55325</v>
+        <v>25.11255</v>
       </c>
       <c r="H17" t="n">
-        <v>106553.25</v>
+        <v>75337.64999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>91.10302874999998</v>
+        <v>64.41369074999999</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -4430,21 +3520,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26-2412-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2412</v>
+        <v>2880</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4452,16 +3542,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G18" t="n">
-        <v>136.56825</v>
+        <v>40.270125</v>
       </c>
       <c r="H18" t="n">
-        <v>136568.25</v>
+        <v>80540.25</v>
       </c>
       <c r="I18" t="n">
-        <v>116.76585375</v>
+        <v>68.86191375</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -4470,21 +3560,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-28-2886-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4492,16 +3582,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="G19" t="n">
-        <v>39.8199</v>
+        <v>47.92395</v>
       </c>
       <c r="H19" t="n">
-        <v>517658.7</v>
+        <v>47923.95</v>
       </c>
       <c r="I19" t="n">
-        <v>442.5981885</v>
+        <v>40.97497725</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -4510,21 +3600,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-28-2892-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4532,16 +3622,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="G20" t="n">
-        <v>46.6233</v>
+        <v>34.31715</v>
       </c>
       <c r="H20" t="n">
-        <v>512856.3</v>
+        <v>68634.3</v>
       </c>
       <c r="I20" t="n">
-        <v>438.4921365</v>
+        <v>58.6823265</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -4550,21 +3640,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-28-5880-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4572,16 +3662,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="G21" t="n">
-        <v>33.51674999999999</v>
+        <v>25.262625</v>
       </c>
       <c r="H21" t="n">
-        <v>536267.9999999999</v>
+        <v>75787.875</v>
       </c>
       <c r="I21" t="n">
-        <v>458.5091399999999</v>
+        <v>64.79863312499999</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -4590,21 +3680,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26-3045-BUY</t>
+          <t>2026-08-31-2880-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3045</v>
+        <v>2880</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4612,16 +3702,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G22" t="n">
-        <v>116.058</v>
+        <v>40.82039999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>116058</v>
+        <v>81640.79999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>99.22959</v>
+        <v>69.80288399999999</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -4630,21 +3720,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26-4904-BUY</t>
+          <t>2026-08-31-2886-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4904</v>
+        <v>2886</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4652,16 +3742,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G23" t="n">
-        <v>101.0505</v>
+        <v>48.2241</v>
       </c>
       <c r="H23" t="n">
-        <v>202101</v>
+        <v>48224.1</v>
       </c>
       <c r="I23" t="n">
-        <v>172.796355</v>
+        <v>41.2316055</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -4670,21 +3760,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-31-2892-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4692,16 +3782,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="G24" t="n">
-        <v>25.0125</v>
+        <v>35.067525</v>
       </c>
       <c r="H24" t="n">
-        <v>525262.5</v>
+        <v>70135.04999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>449.0994375</v>
+        <v>59.96546774999999</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -4710,21 +3800,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-27-0050-BUY</t>
+          <t>2026-08-31-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4732,16 +3822,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G25" t="n">
-        <v>107.15355</v>
+        <v>25.362675</v>
       </c>
       <c r="H25" t="n">
-        <v>107153.55</v>
+        <v>76088.02499999999</v>
       </c>
       <c r="I25" t="n">
-        <v>91.61628525</v>
+        <v>65.05526137499999</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -4750,21 +3840,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27-2412-BUY</t>
+          <t>2026-09-01-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2412</v>
+        <v>50</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4775,13 +3865,13 @@
         <v>1000</v>
       </c>
       <c r="G26" t="n">
-        <v>136.068</v>
+        <v>107.55375</v>
       </c>
       <c r="H26" t="n">
-        <v>136068</v>
+        <v>107553.75</v>
       </c>
       <c r="I26" t="n">
-        <v>116.33814</v>
+        <v>91.95845625</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -4790,17 +3880,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-09-01-2880-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -4812,16 +3902,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
       <c r="G27" t="n">
-        <v>39.369675</v>
+        <v>41.970975</v>
       </c>
       <c r="H27" t="n">
-        <v>551175.4500000001</v>
+        <v>41970.97500000001</v>
       </c>
       <c r="I27" t="n">
-        <v>471.2550097500001</v>
+        <v>35.885183625</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -4830,17 +3920,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-09-01-2886-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4852,16 +3942,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="G28" t="n">
-        <v>46.92345</v>
+        <v>48.274125</v>
       </c>
       <c r="H28" t="n">
-        <v>563081.3999999999</v>
+        <v>48274.125</v>
       </c>
       <c r="I28" t="n">
-        <v>481.4345969999999</v>
+        <v>41.274376875</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -4870,17 +3960,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-09-01-2892-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4892,16 +3982,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="G29" t="n">
-        <v>33.51674999999999</v>
+        <v>35.567775</v>
       </c>
       <c r="H29" t="n">
-        <v>569784.7499999999</v>
+        <v>71135.54999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>487.1659612499999</v>
+        <v>60.82089524999999</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -4910,21 +4000,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27-3045-BUY</t>
+          <t>2026-09-01-5880-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3045</v>
+        <v>5880</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4932,16 +4022,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G30" t="n">
-        <v>115.55775</v>
+        <v>25.6128</v>
       </c>
       <c r="H30" t="n">
-        <v>115557.75</v>
+        <v>76838.39999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>98.80187625000001</v>
+        <v>65.69683199999999</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -4950,21 +4040,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27-4904-BUY</t>
+          <t>2026-09-02-2880-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4904</v>
+        <v>2880</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4975,13 +4065,13 @@
         <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>101.55075</v>
+        <v>42.92144999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>101550.75</v>
+        <v>42921.44999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>86.82589125</v>
+        <v>36.69783974999999</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -4990,21 +4080,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-09-02-2886-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5012,16 +4102,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>23000</v>
+        <v>1000</v>
       </c>
       <c r="G32" t="n">
-        <v>25.11255</v>
+        <v>49.0245</v>
       </c>
       <c r="H32" t="n">
-        <v>577588.65</v>
+        <v>49024.49999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>493.83829575</v>
+        <v>41.9159475</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
@@ -5030,21 +4120,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28-0050-BUY</t>
+          <t>2026-09-02-2892-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>2892</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5052,16 +4142,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G33" t="n">
-        <v>105.6528</v>
+        <v>36.268125</v>
       </c>
       <c r="H33" t="n">
-        <v>316958.4</v>
+        <v>72536.25</v>
       </c>
       <c r="I33" t="n">
-        <v>270.999432</v>
+        <v>62.01849375</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -5070,21 +4160,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-09-02-5880-BUY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2880</v>
+        <v>5880</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5092,16 +4182,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>15000</v>
+        <v>3000</v>
       </c>
       <c r="G34" t="n">
-        <v>40.270125</v>
+        <v>26.31315</v>
       </c>
       <c r="H34" t="n">
-        <v>604051.875</v>
+        <v>78939.45</v>
       </c>
       <c r="I34" t="n">
-        <v>516.464353125</v>
+        <v>67.49322975</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -5110,21 +4200,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-09-03-2880-BUY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5132,16 +4222,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="G35" t="n">
-        <v>47.92395</v>
+        <v>43.771875</v>
       </c>
       <c r="H35" t="n">
-        <v>575087.4</v>
+        <v>43771.87499999999</v>
       </c>
       <c r="I35" t="n">
-        <v>491.699727</v>
+        <v>37.424953125</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -5150,21 +4240,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-09-03-2886-BUY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5172,16 +4262,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>18000</v>
+        <v>1000</v>
       </c>
       <c r="G36" t="n">
-        <v>34.31715</v>
+        <v>50.8254</v>
       </c>
       <c r="H36" t="n">
-        <v>617708.7</v>
+        <v>50825.4</v>
       </c>
       <c r="I36" t="n">
-        <v>528.1409384999999</v>
+        <v>43.45571699999999</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -5190,21 +4280,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-09-03-2892-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5212,16 +4302,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>24000</v>
+        <v>1000</v>
       </c>
       <c r="G37" t="n">
-        <v>25.262625</v>
+        <v>36.968475</v>
       </c>
       <c r="H37" t="n">
-        <v>606303</v>
+        <v>36968.475</v>
       </c>
       <c r="I37" t="n">
-        <v>518.389065</v>
+        <v>31.608046125</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -5230,21 +4320,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31-0050-BUY</t>
+          <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>5880</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5255,1255 +4345,15 @@
         <v>2000</v>
       </c>
       <c r="G38" t="n">
-        <v>106.55325</v>
+        <v>26.71335</v>
       </c>
       <c r="H38" t="n">
-        <v>213106.5</v>
+        <v>53426.7</v>
       </c>
       <c r="I38" t="n">
-        <v>182.2060575</v>
+        <v>45.67982849999999</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-08-31-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G39" t="n">
-        <v>40.82039999999999</v>
-      </c>
-      <c r="H39" t="n">
-        <v>204102</v>
-      </c>
-      <c r="I39" t="n">
-        <v>174.50721</v>
-      </c>
-      <c r="J39" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-08-31-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G40" t="n">
-        <v>48.2241</v>
-      </c>
-      <c r="H40" t="n">
-        <v>241120.5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>206.1580275</v>
-      </c>
-      <c r="J40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-08-31-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G41" t="n">
-        <v>35.067525</v>
-      </c>
-      <c r="H41" t="n">
-        <v>210405.15</v>
-      </c>
-      <c r="I41" t="n">
-        <v>179.89640325</v>
-      </c>
-      <c r="J41" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-31-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G42" t="n">
-        <v>25.362675</v>
-      </c>
-      <c r="H42" t="n">
-        <v>228264.075</v>
-      </c>
-      <c r="I42" t="n">
-        <v>195.165784125</v>
-      </c>
-      <c r="J42" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-09-01-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G43" t="n">
-        <v>136.43175</v>
-      </c>
-      <c r="H43" t="n">
-        <v>136431.75</v>
-      </c>
-      <c r="I43" t="n">
-        <v>525.94439625</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-09-01-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G44" t="n">
-        <v>115.44225</v>
-      </c>
-      <c r="H44" t="n">
-        <v>115442.25</v>
-      </c>
-      <c r="I44" t="n">
-        <v>445.02987375</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-09-01-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G45" t="n">
-        <v>100.44975</v>
-      </c>
-      <c r="H45" t="n">
-        <v>100449.75</v>
-      </c>
-      <c r="I45" t="n">
-        <v>387.23378625</v>
-      </c>
-      <c r="J45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-09-01-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>50</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G46" t="n">
-        <v>107.55375</v>
-      </c>
-      <c r="H46" t="n">
-        <v>215107.5</v>
-      </c>
-      <c r="I46" t="n">
-        <v>183.9169125</v>
-      </c>
-      <c r="J46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-09-01-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G47" t="n">
-        <v>41.970975</v>
-      </c>
-      <c r="H47" t="n">
-        <v>83941.95000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>71.77036725000001</v>
-      </c>
-      <c r="J47" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-09-01-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G48" t="n">
-        <v>48.274125</v>
-      </c>
-      <c r="H48" t="n">
-        <v>96548.25</v>
-      </c>
-      <c r="I48" t="n">
-        <v>82.54875375</v>
-      </c>
-      <c r="J48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-09-01-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G49" t="n">
-        <v>35.567775</v>
-      </c>
-      <c r="H49" t="n">
-        <v>106703.325</v>
-      </c>
-      <c r="I49" t="n">
-        <v>91.231342875</v>
-      </c>
-      <c r="J49" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-01-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G50" t="n">
-        <v>25.6128</v>
-      </c>
-      <c r="H50" t="n">
-        <v>102451.2</v>
-      </c>
-      <c r="I50" t="n">
-        <v>87.595776</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-09-02-2412-SELL</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>2412</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G51" t="n">
-        <v>137.43125</v>
-      </c>
-      <c r="H51" t="n">
-        <v>137431.25</v>
-      </c>
-      <c r="I51" t="n">
-        <v>529.79746875</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-09-02-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G52" t="n">
-        <v>115.942</v>
-      </c>
-      <c r="H52" t="n">
-        <v>115942</v>
-      </c>
-      <c r="I52" t="n">
-        <v>446.95641</v>
-      </c>
-      <c r="J52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-09-02-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G53" t="n">
-        <v>102.44875</v>
-      </c>
-      <c r="H53" t="n">
-        <v>102448.75</v>
-      </c>
-      <c r="I53" t="n">
-        <v>394.93993125</v>
-      </c>
-      <c r="J53" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-09-02-0050-BUY</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>50</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G54" t="n">
-        <v>106.95345</v>
-      </c>
-      <c r="H54" t="n">
-        <v>106953.45</v>
-      </c>
-      <c r="I54" t="n">
-        <v>91.44519975</v>
-      </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-09-02-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G55" t="n">
-        <v>42.92144999999999</v>
-      </c>
-      <c r="H55" t="n">
-        <v>85842.89999999998</v>
-      </c>
-      <c r="I55" t="n">
-        <v>73.39567949999999</v>
-      </c>
-      <c r="J55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-02-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G56" t="n">
-        <v>49.0245</v>
-      </c>
-      <c r="H56" t="n">
-        <v>49024.49999999999</v>
-      </c>
-      <c r="I56" t="n">
-        <v>41.9159475</v>
-      </c>
-      <c r="J56" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-02-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G57" t="n">
-        <v>36.268125</v>
-      </c>
-      <c r="H57" t="n">
-        <v>72536.25</v>
-      </c>
-      <c r="I57" t="n">
-        <v>62.01849375</v>
-      </c>
-      <c r="J57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-02-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G58" t="n">
-        <v>26.31315</v>
-      </c>
-      <c r="H58" t="n">
-        <v>78939.45</v>
-      </c>
-      <c r="I58" t="n">
-        <v>67.49322975</v>
-      </c>
-      <c r="J58" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-03-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G59" t="n">
-        <v>117.44125</v>
-      </c>
-      <c r="H59" t="n">
-        <v>117441.25</v>
-      </c>
-      <c r="I59" t="n">
-        <v>452.73601875</v>
-      </c>
-      <c r="J59" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-09-03-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G60" t="n">
-        <v>102.9485</v>
-      </c>
-      <c r="H60" t="n">
-        <v>102948.5</v>
-      </c>
-      <c r="I60" t="n">
-        <v>396.8664675000001</v>
-      </c>
-      <c r="J60" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-03-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G61" t="n">
-        <v>43.771875</v>
-      </c>
-      <c r="H61" t="n">
-        <v>87543.74999999999</v>
-      </c>
-      <c r="I61" t="n">
-        <v>74.84990624999999</v>
-      </c>
-      <c r="J61" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-03-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G62" t="n">
-        <v>50.8254</v>
-      </c>
-      <c r="H62" t="n">
-        <v>101650.8</v>
-      </c>
-      <c r="I62" t="n">
-        <v>86.91143399999999</v>
-      </c>
-      <c r="J62" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-03-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G63" t="n">
-        <v>26.71335</v>
-      </c>
-      <c r="H63" t="n">
-        <v>26713.35</v>
-      </c>
-      <c r="I63" t="n">
-        <v>22.83991425</v>
-      </c>
-      <c r="J63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-04-3045-SELL</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>3045</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G64" t="n">
-        <v>117.941</v>
-      </c>
-      <c r="H64" t="n">
-        <v>117941</v>
-      </c>
-      <c r="I64" t="n">
-        <v>454.662555</v>
-      </c>
-      <c r="J64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-04-4904-SELL</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4904</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G65" t="n">
-        <v>104.44775</v>
-      </c>
-      <c r="H65" t="n">
-        <v>104447.75</v>
-      </c>
-      <c r="I65" t="n">
-        <v>402.64607625</v>
-      </c>
-      <c r="J65" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-04-2880-BUY</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G66" t="n">
-        <v>44.72235</v>
-      </c>
-      <c r="H66" t="n">
-        <v>44722.35</v>
-      </c>
-      <c r="I66" t="n">
-        <v>38.23760925</v>
-      </c>
-      <c r="J66" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-04-2886-BUY</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>2886</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G67" t="n">
-        <v>50.4252</v>
-      </c>
-      <c r="H67" t="n">
-        <v>50425.2</v>
-      </c>
-      <c r="I67" t="n">
-        <v>43.11354599999999</v>
-      </c>
-      <c r="J67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-04-2892-BUY</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2892</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G68" t="n">
-        <v>38.019</v>
-      </c>
-      <c r="H68" t="n">
-        <v>76038</v>
-      </c>
-      <c r="I68" t="n">
-        <v>65.01249</v>
-      </c>
-      <c r="J68" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-04-5880-BUY</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G69" t="n">
-        <v>26.763375</v>
-      </c>
-      <c r="H69" t="n">
-        <v>53526.75</v>
-      </c>
-      <c r="I69" t="n">
-        <v>45.76537125</v>
-      </c>
-      <c r="J69" t="n">
         <v>5</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:54.587142+00:00</t>
+          <t>2026-09-08T01:32:12.982564+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:55.260389+00:00</t>
+          <t>2026-09-08T01:32:13.665083+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:55.953983+00:00</t>
+          <t>2026-09-08T01:32:14.348158+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:56.625361+00:00</t>
+          <t>2026-09-08T01:32:15.031539+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:57.302543+00:00</t>
+          <t>2026-09-08T01:32:15.728178+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:57.984715+00:00</t>
+          <t>2026-09-08T01:32:16.430427+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:58.675569+00:00</t>
+          <t>2026-09-08T01:32:17.123871+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:59.360649+00:00</t>
+          <t>2026-09-08T01:32:17.817754+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-08T00:52:00.028473+00:00</t>
+          <t>2026-09-08T01:32:18.532358+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-08T00:52:00.693783+00:00</t>
+          <t>2026-09-08T01:32:19.230458+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08T00:52:01.341982+00:00</t>
+          <t>2026-09-08T01:32:19.916463+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3000000</v>
+        <v>500000000</v>
       </c>
       <c r="C2" t="n">
-        <v>3000000</v>
+        <v>500000000</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1330,28 +1330,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3001924.395765</v>
+        <v>500718253.7125438</v>
       </c>
       <c r="C3" t="n">
-        <v>2685574.395765</v>
+        <v>400157353.7125438</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1053824008513653</v>
+        <v>0.1322462273125257</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0619150585586557</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0066720156000502</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8946175991486346</v>
+        <v>0.7991666985287681</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1378,28 +1378,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2998911.005652251</v>
+        <v>499186054.3534285</v>
       </c>
       <c r="C4" t="n">
-        <v>2417111.005652251</v>
+        <v>300423254.3534285</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1940037563313623</v>
+        <v>0.2627982069128871</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1217982743503347</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.0135773023723162</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8059962436686375</v>
+        <v>0.6018262163644618</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1426,28 +1426,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2994284.317075251</v>
+        <v>498503926.5436805</v>
       </c>
       <c r="C5" t="n">
-        <v>2101884.317075251</v>
+        <v>200372626.5436805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2980344902155704</v>
+        <v>0.4103444107617794</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.1664339949641902</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0212736538978309</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7019655097844294</v>
+        <v>0.4019479403761992</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1474,28 +1474,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3024257.628498252</v>
+        <v>504731959.0571287</v>
       </c>
       <c r="C6" t="n">
-        <v>1786657.628498251</v>
+        <v>100218809.0571287</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4092243955468014</v>
+        <v>0.5861769691633743</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.1851755140978128</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0300890397912787</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5907756044531984</v>
+        <v>0.2264652293991205</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1522,28 +1522,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3051687.935647626</v>
+        <v>511808481.8633183</v>
       </c>
       <c r="C7" t="n">
-        <v>1513537.935647627</v>
+        <v>22734881.86331829</v>
       </c>
       <c r="D7" t="n">
-        <v>0.504032532957396</v>
+        <v>0.7269356862658615</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.1781975157347164</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.0504461159103945</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4959674670426039</v>
+        <v>0.1286820150038017</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1570,28 +1570,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3068713.905429002</v>
+        <v>515760364.341664</v>
       </c>
       <c r="C8" t="n">
-        <v>1237213.905429002</v>
+        <v>5817614.341664043</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5968298304901639</v>
+        <v>0.7782465031262099</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.1454997421055953</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0649740699690538</v>
       </c>
       <c r="G8" t="n">
-        <v>0.403170169509836</v>
+        <v>0.0831788950943374</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1618,28 +1618,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3106745.469685002</v>
+        <v>523485930.2158344</v>
       </c>
       <c r="C9" t="n">
-        <v>891145.4696850018</v>
+        <v>1500930.21583442</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6787810654516911</v>
+        <v>0.8044181814521335</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.1186564841855249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0343768104088773</v>
+        <v>0.07405815087334949</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2868421241394314</v>
+        <v>0.0608549464230463</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1666,28 +1666,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3146815.694174252</v>
+        <v>531259770.5317957</v>
       </c>
       <c r="C10" t="n">
-        <v>647515.6941742518</v>
+        <v>504220.5317956712</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7604830509871878</v>
+        <v>0.8238535539061771</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.0964358734498488</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0337484016609583</v>
+        <v>0.0787614690984694</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2057685473518539</v>
+        <v>0.0534983576191357</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1714,28 +1714,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3151865.075629502</v>
+        <v>532722538.1812888</v>
       </c>
       <c r="C11" t="n">
-        <v>462365.0756295018</v>
+        <v>48588.18128879648</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8190705940940044</v>
+        <v>0.8431466998438631</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.081213008459719</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0342336989087167</v>
+        <v>0.0755490844021767</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1466957069972788</v>
+        <v>0.0338344925790966</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1762,28 +1762,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3163015.075629502</v>
+        <v>534431224.1685917</v>
       </c>
       <c r="C12" t="n">
-        <v>462365.0756295018</v>
+        <v>21074.16859167116</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8190760834373798</v>
+        <v>0.8548416135504104</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.06718170341909829</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0347453291787196</v>
+        <v>0.0779372501387763</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1461785873839004</v>
+        <v>0.0071076379499846</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1814,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,7 +1852,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="F2" t="n">
-        <v>39.25</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1895,16 +1895,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F3" t="n">
-        <v>46.85</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2000</v>
+        <v>419000</v>
       </c>
       <c r="F4" t="n">
-        <v>33.55</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1947,25 +1947,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3000</v>
+        <v>351000</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1973,25 +1973,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2000</v>
+        <v>490000</v>
       </c>
       <c r="F6" t="n">
-        <v>39.8</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2002,22 +2002,22 @@
         <v>1000</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2000</v>
+        <v>300000</v>
       </c>
       <c r="F8" t="n">
-        <v>33.8</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3000</v>
+        <v>658000</v>
       </c>
       <c r="F9" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2077,25 +2077,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="F10" t="n">
-        <v>39.6</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2103,25 +2103,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F11" t="n">
-        <v>46.6</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2129,25 +2129,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2000</v>
+        <v>414000</v>
       </c>
       <c r="F12" t="n">
-        <v>33.4</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3000</v>
+        <v>350000</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2000</v>
+        <v>487000</v>
       </c>
       <c r="F14" t="n">
-        <v>39.35</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F15" t="n">
-        <v>46.15</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2000</v>
+        <v>297000</v>
       </c>
       <c r="F16" t="n">
-        <v>33.35</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3000</v>
+        <v>658000</v>
       </c>
       <c r="F17" t="n">
         <v>25.05</v>
@@ -2268,16 +2268,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2000</v>
+        <v>36000</v>
       </c>
       <c r="F18" t="n">
-        <v>40.25</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2314,22 +2314,22 @@
         <v>1000</v>
       </c>
       <c r="F19" t="n">
-        <v>48.2</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2337,25 +2337,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2000</v>
+        <v>468000</v>
       </c>
       <c r="F20" t="n">
-        <v>34.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3000</v>
+        <v>398000</v>
       </c>
       <c r="F21" t="n">
-        <v>25.25</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2389,25 +2389,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2000</v>
+        <v>555000</v>
       </c>
       <c r="F22" t="n">
-        <v>41.35</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2418,22 +2418,22 @@
         <v>1000</v>
       </c>
       <c r="F23" t="n">
-        <v>48.55</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2000</v>
+        <v>213000</v>
       </c>
       <c r="F24" t="n">
-        <v>35.3</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2467,21 +2467,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3000</v>
+        <v>742000</v>
       </c>
       <c r="F25" t="n">
-        <v>25.55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2493,25 +2493,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1000</v>
+        <v>42000</v>
       </c>
       <c r="F26" t="n">
-        <v>108.45</v>
+        <v>106.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2522,22 +2522,22 @@
         <v>1000</v>
       </c>
       <c r="F27" t="n">
-        <v>41.95</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1000</v>
+        <v>531000</v>
       </c>
       <c r="F28" t="n">
-        <v>48.5</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2571,25 +2571,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2000</v>
+        <v>453000</v>
       </c>
       <c r="F29" t="n">
-        <v>35.9</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2597,25 +2597,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3000</v>
+        <v>627000</v>
       </c>
       <c r="F30" t="n">
-        <v>25.6</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2626,22 +2626,22 @@
         <v>1000</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2649,25 +2649,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1000</v>
+        <v>110000</v>
       </c>
       <c r="F32" t="n">
-        <v>49</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2675,103 +2675,103 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2000</v>
+        <v>835000</v>
       </c>
       <c r="F33" t="n">
-        <v>36.25</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-08-28-2412-SELL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5880</v>
+        <v>2412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F34" t="n">
-        <v>26.3</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-08-28-3045-SELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="F35" t="n">
-        <v>43.45</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-08-28-4904-SELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1000</v>
+        <v>17000</v>
       </c>
       <c r="F36" t="n">
-        <v>50.4</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2892</v>
+        <v>50</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2779,36 +2779,894 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1000</v>
+        <v>101000</v>
       </c>
       <c r="F37" t="n">
-        <v>36.85</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2026-08-28-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>432000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-28-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>361000</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-28-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>505000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-28-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>689000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>160000</v>
+      </c>
+      <c r="F42" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>50</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>106.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>41.35</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>134000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>48.55</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>185000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>255000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>137000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>50</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>54000</v>
+      </c>
+      <c r="F49" t="n">
+        <v>108.45</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>73000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>41.95</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>63000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F52" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F53" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>111000</v>
+      </c>
+      <c r="F54" t="n">
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>50</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>31000</v>
+      </c>
+      <c r="F55" t="n">
+        <v>106.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>46000</v>
+      </c>
+      <c r="F57" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F58" t="n">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>86000</v>
+      </c>
+      <c r="F59" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-03-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>50</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>79000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>103.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F62" t="n">
+        <v>43.45</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>53000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-03-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>73000</v>
+      </c>
+      <c r="F64" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C65" t="n">
         <v>5880</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F38" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>101000</v>
+      </c>
+      <c r="F65" t="n">
         <v>26.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>64000</v>
+      </c>
+      <c r="F66" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-04-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>50</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F67" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F68" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F69" t="n">
+        <v>49.55</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F70" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F71" t="n">
+        <v>26.65</v>
       </c>
     </row>
   </sheetData>
@@ -2822,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,7 +3738,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2894,7 +3752,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2902,16 +3760,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="G2" t="n">
-        <v>39.169575</v>
+        <v>102.95145</v>
       </c>
       <c r="H2" t="n">
-        <v>78339.14999999999</v>
+        <v>3294446.4</v>
       </c>
       <c r="I2" t="n">
-        <v>66.97997324999999</v>
+        <v>2816.751672</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -2920,7 +3778,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2934,7 +3792,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2942,16 +3800,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G3" t="n">
-        <v>46.873425</v>
+        <v>136.56825</v>
       </c>
       <c r="H3" t="n">
-        <v>93746.85000000001</v>
+        <v>136568.25</v>
       </c>
       <c r="I3" t="n">
-        <v>80.15355674999999</v>
+        <v>116.76585375</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -2960,7 +3818,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2974,7 +3832,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2982,16 +3840,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000</v>
+        <v>419000</v>
       </c>
       <c r="G4" t="n">
-        <v>33.51674999999999</v>
+        <v>39.169575</v>
       </c>
       <c r="H4" t="n">
-        <v>67033.49999999999</v>
+        <v>16412051.925</v>
       </c>
       <c r="I4" t="n">
-        <v>57.31364249999999</v>
+        <v>14032.304395875</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -3000,7 +3858,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3014,7 +3872,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3022,16 +3880,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3000</v>
+        <v>351000</v>
       </c>
       <c r="G5" t="n">
-        <v>25.0125</v>
+        <v>46.873425</v>
       </c>
       <c r="H5" t="n">
-        <v>75037.5</v>
+        <v>16452572.175</v>
       </c>
       <c r="I5" t="n">
-        <v>64.15706249999999</v>
+        <v>14066.949209625</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -3040,21 +3898,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D6" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3062,16 +3920,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>490000</v>
       </c>
       <c r="G6" t="n">
-        <v>39.6198</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>79239.59999999999</v>
+        <v>16423207.5</v>
       </c>
       <c r="I6" t="n">
-        <v>67.74985799999999</v>
+        <v>14041.8424125</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -3080,21 +3938,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D7" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3105,13 +3963,13 @@
         <v>1000</v>
       </c>
       <c r="G7" t="n">
-        <v>46.92345</v>
+        <v>115.0575</v>
       </c>
       <c r="H7" t="n">
-        <v>46923.45</v>
+        <v>115057.5</v>
       </c>
       <c r="I7" t="n">
-        <v>40.11954975</v>
+        <v>98.37416249999998</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -3120,21 +3978,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D8" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3142,16 +4000,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000</v>
+        <v>300000</v>
       </c>
       <c r="G8" t="n">
-        <v>33.51674999999999</v>
+        <v>101.55075</v>
       </c>
       <c r="H8" t="n">
-        <v>67033.49999999999</v>
+        <v>30465225</v>
       </c>
       <c r="I8" t="n">
-        <v>57.31364249999999</v>
+        <v>26047.767375</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -3160,17 +4018,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3182,16 +4040,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3000</v>
+        <v>658000</v>
       </c>
       <c r="G9" t="n">
         <v>25.0125</v>
       </c>
       <c r="H9" t="n">
-        <v>75037.5</v>
+        <v>16458225</v>
       </c>
       <c r="I9" t="n">
-        <v>64.15706249999999</v>
+        <v>14071.782375</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -3200,21 +4058,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D10" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3222,16 +4080,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="G10" t="n">
-        <v>39.8199</v>
+        <v>104.15205</v>
       </c>
       <c r="H10" t="n">
-        <v>79639.79999999999</v>
+        <v>3332865.6</v>
       </c>
       <c r="I10" t="n">
-        <v>68.09202899999998</v>
+        <v>2849.600088</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -3240,21 +4098,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D11" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3262,16 +4120,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G11" t="n">
-        <v>46.6233</v>
+        <v>136.56825</v>
       </c>
       <c r="H11" t="n">
-        <v>93246.60000000001</v>
+        <v>136568.25</v>
       </c>
       <c r="I11" t="n">
-        <v>79.725843</v>
+        <v>116.76585375</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -3280,21 +4138,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D12" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3302,16 +4160,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000</v>
+        <v>414000</v>
       </c>
       <c r="G12" t="n">
-        <v>33.51674999999999</v>
+        <v>39.6198</v>
       </c>
       <c r="H12" t="n">
-        <v>67033.49999999999</v>
+        <v>16402597.2</v>
       </c>
       <c r="I12" t="n">
-        <v>57.31364249999999</v>
+        <v>14024.220606</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -3320,21 +4178,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D13" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3342,16 +4200,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3000</v>
+        <v>350000</v>
       </c>
       <c r="G13" t="n">
-        <v>25.0125</v>
+        <v>46.92345</v>
       </c>
       <c r="H13" t="n">
-        <v>75037.5</v>
+        <v>16423207.5</v>
       </c>
       <c r="I13" t="n">
-        <v>64.15706249999999</v>
+        <v>14041.8424125</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -3360,21 +4218,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3382,16 +4240,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000</v>
+        <v>487000</v>
       </c>
       <c r="G14" t="n">
-        <v>39.369675</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>78739.35000000001</v>
+        <v>16322657.25</v>
       </c>
       <c r="I14" t="n">
-        <v>67.32214425000001</v>
+        <v>13955.87194875</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -3400,21 +4258,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3422,16 +4280,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G15" t="n">
-        <v>46.92345</v>
+        <v>115.0575</v>
       </c>
       <c r="H15" t="n">
-        <v>93846.89999999999</v>
+        <v>115057.5</v>
       </c>
       <c r="I15" t="n">
-        <v>80.23909949999999</v>
+        <v>98.37416249999998</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -3440,21 +4298,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3462,16 +4320,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000</v>
+        <v>297000</v>
       </c>
       <c r="G16" t="n">
-        <v>33.51674999999999</v>
+        <v>102.55125</v>
       </c>
       <c r="H16" t="n">
-        <v>67033.49999999999</v>
+        <v>30457721.25</v>
       </c>
       <c r="I16" t="n">
-        <v>57.31364249999999</v>
+        <v>26041.35166875</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -3480,17 +4338,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3502,16 +4360,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3000</v>
+        <v>658000</v>
       </c>
       <c r="G17" t="n">
-        <v>25.11255</v>
+        <v>25.0125</v>
       </c>
       <c r="H17" t="n">
-        <v>75337.64999999999</v>
+        <v>16458225</v>
       </c>
       <c r="I17" t="n">
-        <v>64.41369074999999</v>
+        <v>14071.782375</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -3520,21 +4378,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3542,16 +4400,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000</v>
+        <v>36000</v>
       </c>
       <c r="G18" t="n">
-        <v>40.270125</v>
+        <v>106.55325</v>
       </c>
       <c r="H18" t="n">
-        <v>80540.25</v>
+        <v>3835917</v>
       </c>
       <c r="I18" t="n">
-        <v>68.86191375</v>
+        <v>3279.709034999999</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -3560,21 +4418,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3585,13 +4443,13 @@
         <v>1000</v>
       </c>
       <c r="G19" t="n">
-        <v>47.92395</v>
+        <v>136.56825</v>
       </c>
       <c r="H19" t="n">
-        <v>47923.95</v>
+        <v>136568.25</v>
       </c>
       <c r="I19" t="n">
-        <v>40.97497725</v>
+        <v>116.76585375</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -3600,21 +4458,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3622,16 +4480,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2000</v>
+        <v>468000</v>
       </c>
       <c r="G20" t="n">
-        <v>34.31715</v>
+        <v>39.8199</v>
       </c>
       <c r="H20" t="n">
-        <v>68634.3</v>
+        <v>18635713.2</v>
       </c>
       <c r="I20" t="n">
-        <v>58.6823265</v>
+        <v>15933.534786</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -3640,21 +4498,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3662,16 +4520,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3000</v>
+        <v>398000</v>
       </c>
       <c r="G21" t="n">
-        <v>25.262625</v>
+        <v>46.6233</v>
       </c>
       <c r="H21" t="n">
-        <v>75787.875</v>
+        <v>18556073.4</v>
       </c>
       <c r="I21" t="n">
-        <v>64.79863312499999</v>
+        <v>15865.442757</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -3680,21 +4538,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3702,16 +4560,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2000</v>
+        <v>555000</v>
       </c>
       <c r="G22" t="n">
-        <v>40.82039999999999</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>81640.79999999999</v>
+        <v>18601796.25</v>
       </c>
       <c r="I22" t="n">
-        <v>69.80288399999999</v>
+        <v>15904.53579375</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -3720,21 +4578,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3745,13 +4603,13 @@
         <v>1000</v>
       </c>
       <c r="G23" t="n">
-        <v>48.2241</v>
+        <v>116.058</v>
       </c>
       <c r="H23" t="n">
-        <v>48224.1</v>
+        <v>116058</v>
       </c>
       <c r="I23" t="n">
-        <v>41.2316055</v>
+        <v>99.22959</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -3760,21 +4618,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3782,16 +4640,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000</v>
+        <v>213000</v>
       </c>
       <c r="G24" t="n">
-        <v>35.067525</v>
+        <v>101.0505</v>
       </c>
       <c r="H24" t="n">
-        <v>70135.04999999999</v>
+        <v>21523756.5</v>
       </c>
       <c r="I24" t="n">
-        <v>59.96546774999999</v>
+        <v>18402.8118075</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -3800,17 +4658,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3822,16 +4680,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3000</v>
+        <v>742000</v>
       </c>
       <c r="G25" t="n">
-        <v>25.362675</v>
+        <v>25.0125</v>
       </c>
       <c r="H25" t="n">
-        <v>76088.02499999999</v>
+        <v>18559275</v>
       </c>
       <c r="I25" t="n">
-        <v>65.05526137499999</v>
+        <v>15868.180125</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -3840,17 +4698,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3862,16 +4720,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1000</v>
+        <v>42000</v>
       </c>
       <c r="G26" t="n">
-        <v>107.55375</v>
+        <v>107.15355</v>
       </c>
       <c r="H26" t="n">
-        <v>107553.75</v>
+        <v>4500449.1</v>
       </c>
       <c r="I26" t="n">
-        <v>91.95845625</v>
+        <v>3847.883980499999</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -3880,21 +4738,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -3905,13 +4763,13 @@
         <v>1000</v>
       </c>
       <c r="G27" t="n">
-        <v>41.970975</v>
+        <v>136.068</v>
       </c>
       <c r="H27" t="n">
-        <v>41970.97500000001</v>
+        <v>136068</v>
       </c>
       <c r="I27" t="n">
-        <v>35.885183625</v>
+        <v>116.33814</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -3920,21 +4778,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3942,16 +4800,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1000</v>
+        <v>531000</v>
       </c>
       <c r="G28" t="n">
-        <v>48.274125</v>
+        <v>39.369675</v>
       </c>
       <c r="H28" t="n">
-        <v>48274.125</v>
+        <v>20905297.425</v>
       </c>
       <c r="I28" t="n">
-        <v>41.274376875</v>
+        <v>17874.029298375</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -3960,21 +4818,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3982,16 +4840,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2000</v>
+        <v>453000</v>
       </c>
       <c r="G29" t="n">
-        <v>35.567775</v>
+        <v>46.92345</v>
       </c>
       <c r="H29" t="n">
-        <v>71135.54999999999</v>
+        <v>21256322.85</v>
       </c>
       <c r="I29" t="n">
-        <v>60.82089524999999</v>
+        <v>18174.15603675</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -4000,21 +4858,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4022,16 +4880,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3000</v>
+        <v>627000</v>
       </c>
       <c r="G30" t="n">
-        <v>25.6128</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>76838.39999999999</v>
+        <v>21015002.25</v>
       </c>
       <c r="I30" t="n">
-        <v>65.69683199999999</v>
+        <v>17967.82692375</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -4040,21 +4898,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4065,13 +4923,13 @@
         <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>42.92144999999999</v>
+        <v>115.55775</v>
       </c>
       <c r="H31" t="n">
-        <v>42921.44999999999</v>
+        <v>115557.75</v>
       </c>
       <c r="I31" t="n">
-        <v>36.69783974999999</v>
+        <v>98.80187625000001</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -4080,21 +4938,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4102,16 +4960,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1000</v>
+        <v>110000</v>
       </c>
       <c r="G32" t="n">
-        <v>49.0245</v>
+        <v>101.55075</v>
       </c>
       <c r="H32" t="n">
-        <v>49024.49999999999</v>
+        <v>11170582.5</v>
       </c>
       <c r="I32" t="n">
-        <v>41.9159475</v>
+        <v>9550.8480375</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
@@ -4120,21 +4978,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -4142,16 +5000,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000</v>
+        <v>835000</v>
       </c>
       <c r="G33" t="n">
-        <v>36.268125</v>
+        <v>25.11255</v>
       </c>
       <c r="H33" t="n">
-        <v>72536.25</v>
+        <v>20968979.25</v>
       </c>
       <c r="I33" t="n">
-        <v>62.01849375</v>
+        <v>17928.47725875</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -4160,38 +5018,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-08-28-2412-SELL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5880</v>
+        <v>2412</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G34" t="n">
-        <v>26.31315</v>
+        <v>135.932</v>
       </c>
       <c r="H34" t="n">
-        <v>78939.45</v>
+        <v>543728.0000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>67.49322975</v>
+        <v>2096.071440000001</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -4200,38 +5058,38 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-08-28-3045-SELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="G35" t="n">
-        <v>43.771875</v>
+        <v>114.9425</v>
       </c>
       <c r="H35" t="n">
-        <v>43771.87499999999</v>
+        <v>459770.0000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>37.424953125</v>
+        <v>1772.41335</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -4240,38 +5098,38 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-08-28-4904-SELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1000</v>
+        <v>17000</v>
       </c>
       <c r="G36" t="n">
-        <v>50.8254</v>
+        <v>99.7501</v>
       </c>
       <c r="H36" t="n">
-        <v>50825.4</v>
+        <v>1695751.7</v>
       </c>
       <c r="I36" t="n">
-        <v>43.45571699999999</v>
+        <v>6537.1228035</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -4280,21 +5138,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2892</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -4302,16 +5160,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1000</v>
+        <v>101000</v>
       </c>
       <c r="G37" t="n">
-        <v>36.968475</v>
+        <v>105.6528</v>
       </c>
       <c r="H37" t="n">
-        <v>36968.475</v>
+        <v>10670932.8</v>
       </c>
       <c r="I37" t="n">
-        <v>31.608046125</v>
+        <v>9123.647543999999</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -4320,40 +5178,1360 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2026-08-28-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>432000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>40.270125</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17396694</v>
+      </c>
+      <c r="I38" t="n">
+        <v>14874.17337</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-28-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>361000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>47.92395</v>
+      </c>
+      <c r="H39" t="n">
+        <v>17300545.95</v>
+      </c>
+      <c r="I39" t="n">
+        <v>14791.96678725</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-28-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>505000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.31715</v>
+      </c>
+      <c r="H40" t="n">
+        <v>17330160.75</v>
+      </c>
+      <c r="I40" t="n">
+        <v>14817.28744125</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-28-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>689000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>25.262625</v>
+      </c>
+      <c r="H41" t="n">
+        <v>17405948.625</v>
+      </c>
+      <c r="I41" t="n">
+        <v>14882.086074375</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100.44975</v>
+      </c>
+      <c r="H42" t="n">
+        <v>16071960</v>
+      </c>
+      <c r="I42" t="n">
+        <v>61957.40580000001</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>106.55325</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7032514.499999999</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6012.799897499999</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>158000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>40.82039999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6449623.199999998</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5514.427835999998</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>134000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>48.2241</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6462029.4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5525.035137</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>185000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.067525</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6487492.124999999</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5546.805766874999</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>255000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>25.362675</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6467482.125</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5529.697216875</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>137000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>100.44975</v>
+      </c>
+      <c r="H48" t="n">
+        <v>13761615.75</v>
+      </c>
+      <c r="I48" t="n">
+        <v>53051.02871625</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>50</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>54000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>107.55375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>5807902.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4965.7566375</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>73000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>41.970975</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3063881.175</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2619.618404625</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>48.274125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3041269.875</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2600.285743125</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>35.567775</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3023260.875</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2584.888048125</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>25.6128</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3073536</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2627.87328</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>111000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>102.44875</v>
+      </c>
+      <c r="H54" t="n">
+        <v>11371811.25</v>
+      </c>
+      <c r="I54" t="n">
+        <v>43838.33236875</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>50</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>31000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>106.95345</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3315556.95</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2834.80119225</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>52000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>42.92144999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2231915.399999999</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1908.287667</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>49.0245</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2255127</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1928.133585</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>62000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>36.268125</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2248623.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1922.57330625</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>86000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>26.31315</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2262930.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1934.8059195</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-03-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>50</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>107.64615</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2260569.15</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4193.355773249999</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>79000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>102.9485</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8132931.500000001</v>
+      </c>
+      <c r="I61" t="n">
+        <v>31352.4509325</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>62000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>43.771875</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2713856.25</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2320.34709375</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>53000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>50.8254</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2693746.2</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2303.153001</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-03-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>73000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>36.968475</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2698698.675</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2307.387367125</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D65" t="n">
         <v>5880</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>101000</v>
+      </c>
+      <c r="G65" t="n">
         <v>26.71335</v>
       </c>
-      <c r="H38" t="n">
-        <v>53426.7</v>
-      </c>
-      <c r="I38" t="n">
-        <v>45.67982849999999</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="H65" t="n">
+        <v>2698048.35</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2306.831339249999</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>64000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>104.44775</v>
+      </c>
+      <c r="H66" t="n">
+        <v>6684656</v>
+      </c>
+      <c r="I66" t="n">
+        <v>25769.34888</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-04-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>50</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>109.104525</v>
+      </c>
+      <c r="H67" t="n">
+        <v>654627.15</v>
+      </c>
+      <c r="I67" t="n">
+        <v>559.70621325</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>44.72235</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1520559.9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1300.0787145</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>50.4252</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1512756</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1293.40638</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>38.019</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1520760</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1300.2498</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>55000</v>
+      </c>
+      <c r="G71" t="n">
+        <v>26.763375</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1471985.625</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1258.547709375</v>
+      </c>
+      <c r="J71" t="n">
         <v>5</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,91 +416,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>generated_at_utc</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>data_max_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>score_financial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>score_telecom</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>score_0050</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>e19_points</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>e19_alert</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>e20_confirmations</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>e20_streak</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>e16_financial</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>e16_telecom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>e16_0050</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>e20_financial</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>e20_telecom</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>e20_0050</t>
         </is>
@@ -1187,6 +1175,67 @@
       </c>
       <c r="Q12" t="n">
         <v>0.0772434852114485</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-08T13:00:39.776410+00:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7963471471660826</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.3763286375716355</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.420018509594447</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8721280402820835</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0557560243629684</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0721159353549481</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.8721280402820835</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0557560243629684</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0721159353549481</v>
       </c>
     </row>
   </sheetData>
@@ -1200,76 +1249,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nav_e16_e18</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pre_financial</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pre_telecom</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pre_0050</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>target_l1_gap</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>orders_created</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fills_processed</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>exact_t1_ok</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>same_bar_fills</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>e22_version</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>e22_cash_credit</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>e22_stock_shares_added</t>
         </is>
@@ -1800,6 +1849,54 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3198015.075629502</v>
+      </c>
+      <c r="C13" t="n">
+        <v>462365.0756295018</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8211343404887154</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0342868927778323</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1445787667334523</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1814,36 +1911,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>reference_close</t>
         </is>
@@ -2809,6 +2906,32 @@
       </c>
       <c r="F38" t="n">
         <v>26.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-08-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F39" t="n">
+        <v>26.85</v>
       </c>
     </row>
   </sheetData>
@@ -2826,52 +2949,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fill_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>fill_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>fill_price</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gross</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fees_tax</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>slippage_bp</t>
         </is>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,87 +432,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>generated_at_utc</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>data_max_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>score_financial</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>score_telecom</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>score_0050</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>e19_points</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>e19_alert</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>e20_confirmations</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>e20_streak</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>e16_financial</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>e16_telecom</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>e16_0050</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>e20_financial</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>e20_telecom</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>e20_0050</t>
         </is>
@@ -514,7 +526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:54.587142+00:00</t>
+          <t>2026-09-09T02:21:35.887932+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -575,7 +587,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:55.260389+00:00</t>
+          <t>2026-09-09T02:21:36.569289+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -636,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:55.953983+00:00</t>
+          <t>2026-09-09T02:21:37.253559+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -697,7 +709,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:56.625361+00:00</t>
+          <t>2026-09-09T02:21:37.951411+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -758,7 +770,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:57.302543+00:00</t>
+          <t>2026-09-09T02:21:38.635659+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,7 +831,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:57.984715+00:00</t>
+          <t>2026-09-09T02:21:39.311862+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -880,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:58.675569+00:00</t>
+          <t>2026-09-09T02:21:39.987562+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -941,7 +953,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:59.360649+00:00</t>
+          <t>2026-09-09T02:21:40.665829+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1002,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-08T00:52:00.028473+00:00</t>
+          <t>2026-09-09T02:21:41.343588+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1063,7 +1075,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-08T00:52:00.693783+00:00</t>
+          <t>2026-09-09T02:21:42.026071+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1124,7 +1136,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08T00:52:01.341982+00:00</t>
+          <t>2026-09-09T02:21:42.691710+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1185,7 +1197,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-08T13:00:39.776410+00:00</t>
+          <t>2026-09-09T02:21:43.354388+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1253,72 +1265,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>nav_e16_e18</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pre_financial</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pre_telecom</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pre_0050</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>target_l1_gap</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>orders_created</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fills_processed</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>exact_t1_ok</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>same_bar_fills</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>e22_version</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>e22_cash_credit</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>e22_stock_shares_added</t>
         </is>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3000000</v>
+        <v>500000000</v>
       </c>
       <c r="C2" t="n">
-        <v>3000000</v>
+        <v>500000000</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1349,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1379,28 +1391,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3001924.395765</v>
+        <v>500562360.7913163</v>
       </c>
       <c r="C3" t="n">
-        <v>2685574.395765</v>
+        <v>400236460.7913163</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1053824008513653</v>
+        <v>0.1322874134909361</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.06146486913511</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0066740935029926</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8946175991486346</v>
+        <v>0.7995736238709611</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1427,28 +1439,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2998911.005652251</v>
+        <v>499595312.5623673</v>
       </c>
       <c r="C4" t="n">
-        <v>2417111.005652251</v>
+        <v>300614012.5623673</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1940037563313623</v>
+        <v>0.262532887523092</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1221858941928715</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.0135661801253467</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8059962436686375</v>
+        <v>0.6017150381586895</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1475,28 +1487,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2994284.317075251</v>
+        <v>498486679.2259161</v>
       </c>
       <c r="C5" t="n">
-        <v>2101884.317075251</v>
+        <v>200633179.2259161</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2980344902155704</v>
+        <v>0.4105044498235437</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.1657366253563566</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0212743899525422</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7019655097844294</v>
+        <v>0.4024845348675572</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1523,28 +1535,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3024257.628498252</v>
+        <v>505311026.7473876</v>
       </c>
       <c r="C6" t="n">
-        <v>1786657.628498251</v>
+        <v>100564326.7473876</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4092243955468014</v>
+        <v>0.5853598760825561</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.185570856435867</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0300545588679428</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5907756044531984</v>
+        <v>0.2277121457413287</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1571,28 +1583,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3051687.935647626</v>
+        <v>512312614.9859537</v>
       </c>
       <c r="C7" t="n">
-        <v>1513537.935647627</v>
+        <v>25277214.98595371</v>
       </c>
       <c r="D7" t="n">
-        <v>0.504032532957396</v>
+        <v>0.7268328733427916</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.1734312164115577</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.0503964752082239</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4959674670426039</v>
+        <v>0.1240681693058834</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1619,28 +1631,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3068713.905429002</v>
+        <v>516183738.0785156</v>
       </c>
       <c r="C8" t="n">
-        <v>1237213.905429002</v>
+        <v>6412988.0785156</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5968298304901639</v>
+        <v>0.7783656678058427</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.1442897063693839</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.06492077825764959</v>
       </c>
       <c r="G8" t="n">
-        <v>0.403170169509836</v>
+        <v>0.0819029863898975</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1667,28 +1679,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3106745.469685002</v>
+        <v>523687820.0889247</v>
       </c>
       <c r="C9" t="n">
-        <v>891145.4696850018</v>
+        <v>1509370.088924725</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6787810654516911</v>
+        <v>0.8048679649040288</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.1182202404277558</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0343768104088773</v>
+        <v>0.0740296002939631</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2868421241394314</v>
+        <v>0.0599974697927682</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -1715,28 +1727,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3146815.694174252</v>
+        <v>531489800.2564741</v>
       </c>
       <c r="C10" t="n">
-        <v>647515.6941742518</v>
+        <v>431800.2564741019</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7604830509871878</v>
+        <v>0.8239127068641539</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.0965474783810302</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0337484016609583</v>
+        <v>0.0787273809954743</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2057685473518539</v>
+        <v>0.0535167214893452</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -1763,28 +1775,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3151865.075629502</v>
+        <v>532778468.8269692</v>
       </c>
       <c r="C11" t="n">
-        <v>462365.0756295018</v>
+        <v>2168.826969227754</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8190705940940044</v>
+        <v>0.8429736302760771</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.0812786224175731</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0342336989087167</v>
+        <v>0.07574367652065531</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1466957069972788</v>
+        <v>0.0338785839862582</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1811,28 +1823,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3163015.075629502</v>
+        <v>534895521.781057</v>
       </c>
       <c r="C12" t="n">
-        <v>462365.0756295018</v>
+        <v>22371.78105697828</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8190760834373798</v>
+        <v>0.8540678158584251</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.06802076016424879</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0347453291787196</v>
+        <v>0.07786959939636399</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1461785873839004</v>
+        <v>0.008652841644708</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1859,25 +1871,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3198015.075629502</v>
+        <v>541417221.781057</v>
       </c>
       <c r="C13" t="n">
-        <v>462365.0756295018</v>
+        <v>22371.78105697828</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8211343404887154</v>
+        <v>0.8552119906286296</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.0679900795894629</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0342868927778323</v>
+        <v>0.0767566090034818</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1445787667334523</v>
+        <v>0.033790778528482</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1911,36 +1923,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>reference_close</t>
         </is>
@@ -1949,7 +1961,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1958,7 +1970,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1966,16 +1978,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="F2" t="n">
-        <v>39.25</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1984,7 +1996,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1992,16 +2004,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2000</v>
+        <v>75000</v>
       </c>
       <c r="F3" t="n">
-        <v>46.85</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2010,7 +2022,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2018,16 +2030,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2000</v>
+        <v>419000</v>
       </c>
       <c r="F4" t="n">
-        <v>33.55</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2036,7 +2048,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2044,25 +2056,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3000</v>
+        <v>351000</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2070,25 +2082,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2000</v>
+        <v>490000</v>
       </c>
       <c r="F6" t="n">
-        <v>39.8</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2096,25 +2108,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1000</v>
+        <v>89000</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2122,21 +2134,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2000</v>
+        <v>100000</v>
       </c>
       <c r="F8" t="n">
-        <v>33.8</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2148,25 +2160,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3000</v>
+        <v>658000</v>
       </c>
       <c r="F9" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2174,25 +2186,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="F10" t="n">
-        <v>39.6</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2200,25 +2212,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2000</v>
+        <v>75000</v>
       </c>
       <c r="F11" t="n">
-        <v>46.6</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2226,25 +2238,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2000</v>
+        <v>414000</v>
       </c>
       <c r="F12" t="n">
-        <v>33.4</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2252,25 +2264,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3000</v>
+        <v>350000</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2278,25 +2290,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2000</v>
+        <v>487000</v>
       </c>
       <c r="F14" t="n">
-        <v>39.35</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,25 +2316,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2000</v>
+        <v>88000</v>
       </c>
       <c r="F15" t="n">
-        <v>46.15</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,21 +2342,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2000</v>
+        <v>100000</v>
       </c>
       <c r="F16" t="n">
-        <v>33.35</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2356,7 +2368,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3000</v>
+        <v>657000</v>
       </c>
       <c r="F17" t="n">
         <v>25.05</v>
@@ -2365,16 +2377,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,25 +2394,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2000</v>
+        <v>36000</v>
       </c>
       <c r="F18" t="n">
-        <v>40.25</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,25 +2420,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1000</v>
+        <v>53000</v>
       </c>
       <c r="F19" t="n">
-        <v>48.2</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2434,25 +2446,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2000</v>
+        <v>469000</v>
       </c>
       <c r="F20" t="n">
-        <v>34.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2460,25 +2472,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3000</v>
+        <v>398000</v>
       </c>
       <c r="F21" t="n">
-        <v>25.25</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2486,25 +2498,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2000</v>
+        <v>556000</v>
       </c>
       <c r="F22" t="n">
-        <v>41.35</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2512,25 +2524,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1000</v>
+        <v>62000</v>
       </c>
       <c r="F23" t="n">
-        <v>48.55</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2538,21 +2550,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2000</v>
+        <v>71000</v>
       </c>
       <c r="F24" t="n">
-        <v>35.3</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2564,21 +2576,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3000</v>
+        <v>743000</v>
       </c>
       <c r="F25" t="n">
-        <v>25.55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2590,25 +2602,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1000</v>
+        <v>42000</v>
       </c>
       <c r="F26" t="n">
-        <v>108.45</v>
+        <v>106.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2616,25 +2628,25 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1000</v>
+        <v>28000</v>
       </c>
       <c r="F27" t="n">
-        <v>41.95</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2642,25 +2654,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1000</v>
+        <v>530000</v>
       </c>
       <c r="F28" t="n">
-        <v>48.5</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2668,25 +2680,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2000</v>
+        <v>452000</v>
       </c>
       <c r="F29" t="n">
-        <v>35.9</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2694,25 +2706,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3000</v>
+        <v>626000</v>
       </c>
       <c r="F30" t="n">
-        <v>25.6</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2720,25 +2732,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1000</v>
+        <v>33000</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2746,25 +2758,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1000</v>
+        <v>38000</v>
       </c>
       <c r="F32" t="n">
-        <v>49</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2772,103 +2784,103 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2000</v>
+        <v>834000</v>
       </c>
       <c r="F33" t="n">
-        <v>36.25</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-08-28-2412-SELL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5880</v>
+        <v>2412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3000</v>
+        <v>13000</v>
       </c>
       <c r="F34" t="n">
-        <v>26.3</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-08-28-3045-SELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="F35" t="n">
-        <v>43.45</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-08-28-4904-SELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="F36" t="n">
-        <v>50.4</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2892</v>
+        <v>50</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2876,25 +2888,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1000</v>
+        <v>101000</v>
       </c>
       <c r="F37" t="n">
-        <v>36.85</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-03-5880-BUY</t>
+          <t>2026-08-28-2880-BUY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5880</v>
+        <v>2880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2902,35 +2914,1335 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2000</v>
+        <v>434000</v>
       </c>
       <c r="F38" t="n">
-        <v>26.7</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026-08-28-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>363000</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-28-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>508000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-28-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>693000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F42" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>47000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>106.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>41.35</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>48.55</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>185000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>256000</v>
+      </c>
+      <c r="F49" t="n">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-01-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>44000</v>
+      </c>
+      <c r="F52" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>50</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>54000</v>
+      </c>
+      <c r="F53" t="n">
+        <v>108.45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>73000</v>
+      </c>
+      <c r="F54" t="n">
+        <v>41.95</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>63000</v>
+      </c>
+      <c r="F55" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F57" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F58" t="n">
+        <v>137.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-02-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F59" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>36000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>50</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>31000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>106.8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>51000</v>
+      </c>
+      <c r="F62" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F63" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>61000</v>
+      </c>
+      <c r="F64" t="n">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>84000</v>
+      </c>
+      <c r="F65" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-03-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>50</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F66" t="n">
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-03-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F67" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-03-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F68" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F69" t="n">
+        <v>103.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F70" t="n">
+        <v>43.45</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>53000</v>
+      </c>
+      <c r="F71" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-03-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>73000</v>
+      </c>
+      <c r="F72" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-03-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>101000</v>
+      </c>
+      <c r="F73" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-04-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F74" t="n">
+        <v>137.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-04-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F75" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F76" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-04-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>50</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F77" t="n">
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F78" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>31000</v>
+      </c>
+      <c r="F79" t="n">
+        <v>49.55</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F80" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F81" t="n">
+        <v>26.65</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-08-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>50</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F82" t="n">
+        <v>109.65</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-08-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F83" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-08-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F84" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-08-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F85" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-08-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F86" t="n">
+        <v>45.15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-08-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F87" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-08-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F88" t="n">
+        <v>37.85</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>2026-09-08-5880-BUY</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C89" t="n">
         <v>5880</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>63000</v>
+      </c>
+      <c r="F89" t="n">
         <v>26.85</v>
       </c>
     </row>
@@ -2945,56 +4257,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fill_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>fill_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>fill_price</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gross</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fees_tax</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>slippage_bp</t>
         </is>
@@ -3003,7 +4315,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24-2880-BUY</t>
+          <t>2026-08-24-0050-BUY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3017,7 +4329,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3025,16 +4337,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="G2" t="n">
-        <v>39.169575</v>
+        <v>102.95145</v>
       </c>
       <c r="H2" t="n">
-        <v>78339.14999999999</v>
+        <v>3294446.4</v>
       </c>
       <c r="I2" t="n">
-        <v>66.97997324999999</v>
+        <v>2816.751672</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -3043,7 +4355,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24-2886-BUY</t>
+          <t>2026-08-24-2412-BUY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3057,7 +4369,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3065,16 +4377,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000</v>
+        <v>75000</v>
       </c>
       <c r="G3" t="n">
-        <v>46.873425</v>
+        <v>136.56825</v>
       </c>
       <c r="H3" t="n">
-        <v>93746.85000000001</v>
+        <v>10242618.75</v>
       </c>
       <c r="I3" t="n">
-        <v>80.15355674999999</v>
+        <v>8757.43903125</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -3083,7 +4395,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24-2892-BUY</t>
+          <t>2026-08-24-2880-BUY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3097,7 +4409,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3105,16 +4417,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000</v>
+        <v>419000</v>
       </c>
       <c r="G4" t="n">
-        <v>33.51674999999999</v>
+        <v>39.169575</v>
       </c>
       <c r="H4" t="n">
-        <v>67033.49999999999</v>
+        <v>16412051.925</v>
       </c>
       <c r="I4" t="n">
-        <v>57.31364249999999</v>
+        <v>14032.304395875</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -3123,7 +4435,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24-5880-BUY</t>
+          <t>2026-08-24-2886-BUY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3137,7 +4449,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3145,16 +4457,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3000</v>
+        <v>351000</v>
       </c>
       <c r="G5" t="n">
-        <v>25.0125</v>
+        <v>46.873425</v>
       </c>
       <c r="H5" t="n">
-        <v>75037.5</v>
+        <v>16452572.175</v>
       </c>
       <c r="I5" t="n">
-        <v>64.15706249999999</v>
+        <v>14066.949209625</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -3163,21 +4475,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25-2880-BUY</t>
+          <t>2026-08-24-2892-BUY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D6" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3185,16 +4497,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>490000</v>
       </c>
       <c r="G6" t="n">
-        <v>39.6198</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>79239.59999999999</v>
+        <v>16423207.5</v>
       </c>
       <c r="I6" t="n">
-        <v>67.74985799999999</v>
+        <v>14041.8424125</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -3203,21 +4515,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25-2886-BUY</t>
+          <t>2026-08-24-3045-BUY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D7" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3225,16 +4537,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1000</v>
+        <v>89000</v>
       </c>
       <c r="G7" t="n">
-        <v>46.92345</v>
+        <v>115.0575</v>
       </c>
       <c r="H7" t="n">
-        <v>46923.45</v>
+        <v>10240117.5</v>
       </c>
       <c r="I7" t="n">
-        <v>40.11954975</v>
+        <v>8755.300462499999</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -3243,21 +4555,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25-2892-BUY</t>
+          <t>2026-08-24-4904-BUY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="D8" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3265,16 +4577,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000</v>
+        <v>100000</v>
       </c>
       <c r="G8" t="n">
-        <v>33.51674999999999</v>
+        <v>101.55075</v>
       </c>
       <c r="H8" t="n">
-        <v>67033.49999999999</v>
+        <v>10155075</v>
       </c>
       <c r="I8" t="n">
-        <v>57.31364249999999</v>
+        <v>8682.589125</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -3283,17 +4595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25-5880-BUY</t>
+          <t>2026-08-24-5880-BUY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3305,16 +4617,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3000</v>
+        <v>658000</v>
       </c>
       <c r="G9" t="n">
         <v>25.0125</v>
       </c>
       <c r="H9" t="n">
-        <v>75037.5</v>
+        <v>16458225</v>
       </c>
       <c r="I9" t="n">
-        <v>64.15706249999999</v>
+        <v>14071.782375</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -3323,21 +4635,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26-2880-BUY</t>
+          <t>2026-08-25-0050-BUY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D10" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3345,16 +4657,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000</v>
+        <v>32000</v>
       </c>
       <c r="G10" t="n">
-        <v>39.8199</v>
+        <v>104.15205</v>
       </c>
       <c r="H10" t="n">
-        <v>79639.79999999999</v>
+        <v>3332865.6</v>
       </c>
       <c r="I10" t="n">
-        <v>68.09202899999998</v>
+        <v>2849.600088</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -3363,21 +4675,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26-2886-BUY</t>
+          <t>2026-08-25-2412-BUY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D11" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3385,16 +4697,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000</v>
+        <v>75000</v>
       </c>
       <c r="G11" t="n">
-        <v>46.6233</v>
+        <v>136.56825</v>
       </c>
       <c r="H11" t="n">
-        <v>93246.60000000001</v>
+        <v>10242618.75</v>
       </c>
       <c r="I11" t="n">
-        <v>79.725843</v>
+        <v>8757.43903125</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -3403,21 +4715,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26-2892-BUY</t>
+          <t>2026-08-25-2880-BUY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D12" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3425,16 +4737,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000</v>
+        <v>414000</v>
       </c>
       <c r="G12" t="n">
-        <v>33.51674999999999</v>
+        <v>39.6198</v>
       </c>
       <c r="H12" t="n">
-        <v>67033.49999999999</v>
+        <v>16402597.2</v>
       </c>
       <c r="I12" t="n">
-        <v>57.31364249999999</v>
+        <v>14024.220606</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -3443,21 +4755,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26-5880-BUY</t>
+          <t>2026-08-25-2886-BUY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="D13" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3465,16 +4777,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3000</v>
+        <v>350000</v>
       </c>
       <c r="G13" t="n">
-        <v>25.0125</v>
+        <v>46.92345</v>
       </c>
       <c r="H13" t="n">
-        <v>75037.5</v>
+        <v>16423207.5</v>
       </c>
       <c r="I13" t="n">
-        <v>64.15706249999999</v>
+        <v>14041.8424125</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
@@ -3483,21 +4795,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27-2880-BUY</t>
+          <t>2026-08-25-2892-BUY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3505,16 +4817,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000</v>
+        <v>487000</v>
       </c>
       <c r="G14" t="n">
-        <v>39.369675</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>78739.35000000001</v>
+        <v>16322657.25</v>
       </c>
       <c r="I14" t="n">
-        <v>67.32214425000001</v>
+        <v>13955.87194875</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -3523,21 +4835,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27-2886-BUY</t>
+          <t>2026-08-25-3045-BUY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3545,16 +4857,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000</v>
+        <v>88000</v>
       </c>
       <c r="G15" t="n">
-        <v>46.92345</v>
+        <v>115.0575</v>
       </c>
       <c r="H15" t="n">
-        <v>93846.89999999999</v>
+        <v>10125060</v>
       </c>
       <c r="I15" t="n">
-        <v>80.23909949999999</v>
+        <v>8656.926299999999</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -3563,21 +4875,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27-2892-BUY</t>
+          <t>2026-08-25-4904-BUY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3585,16 +4897,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000</v>
+        <v>100000</v>
       </c>
       <c r="G16" t="n">
-        <v>33.51674999999999</v>
+        <v>102.55125</v>
       </c>
       <c r="H16" t="n">
-        <v>67033.49999999999</v>
+        <v>10255125</v>
       </c>
       <c r="I16" t="n">
-        <v>57.31364249999999</v>
+        <v>8768.131874999999</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -3603,17 +4915,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27-5880-BUY</t>
+          <t>2026-08-25-5880-BUY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3625,16 +4937,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3000</v>
+        <v>657000</v>
       </c>
       <c r="G17" t="n">
-        <v>25.11255</v>
+        <v>25.0125</v>
       </c>
       <c r="H17" t="n">
-        <v>75337.64999999999</v>
+        <v>16433212.5</v>
       </c>
       <c r="I17" t="n">
-        <v>64.41369074999999</v>
+        <v>14050.3966875</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
@@ -3643,21 +4955,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28-2880-BUY</t>
+          <t>2026-08-26-0050-BUY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2880</v>
+        <v>50</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3665,16 +4977,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000</v>
+        <v>36000</v>
       </c>
       <c r="G18" t="n">
-        <v>40.270125</v>
+        <v>106.55325</v>
       </c>
       <c r="H18" t="n">
-        <v>80540.25</v>
+        <v>3835917</v>
       </c>
       <c r="I18" t="n">
-        <v>68.86191375</v>
+        <v>3279.709034999999</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
@@ -3683,21 +4995,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28-2886-BUY</t>
+          <t>2026-08-26-2412-BUY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2886</v>
+        <v>2412</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3705,16 +5017,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1000</v>
+        <v>53000</v>
       </c>
       <c r="G19" t="n">
-        <v>47.92395</v>
+        <v>136.56825</v>
       </c>
       <c r="H19" t="n">
-        <v>47923.95</v>
+        <v>7238117.25</v>
       </c>
       <c r="I19" t="n">
-        <v>40.97497725</v>
+        <v>6188.59024875</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
@@ -3723,21 +5035,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28-2892-BUY</t>
+          <t>2026-08-26-2880-BUY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2892</v>
+        <v>2880</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3745,16 +5057,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2000</v>
+        <v>469000</v>
       </c>
       <c r="G20" t="n">
-        <v>34.31715</v>
+        <v>39.8199</v>
       </c>
       <c r="H20" t="n">
-        <v>68634.3</v>
+        <v>18675533.1</v>
       </c>
       <c r="I20" t="n">
-        <v>58.6823265</v>
+        <v>15967.5808005</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
@@ -3763,21 +5075,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28-5880-BUY</t>
+          <t>2026-08-26-2886-BUY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5880</v>
+        <v>2886</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3785,16 +5097,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3000</v>
+        <v>398000</v>
       </c>
       <c r="G21" t="n">
-        <v>25.262625</v>
+        <v>46.6233</v>
       </c>
       <c r="H21" t="n">
-        <v>75787.875</v>
+        <v>18556073.4</v>
       </c>
       <c r="I21" t="n">
-        <v>64.79863312499999</v>
+        <v>15865.442757</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -3803,21 +5115,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31-2880-BUY</t>
+          <t>2026-08-26-2892-BUY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2880</v>
+        <v>2892</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3825,16 +5137,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2000</v>
+        <v>556000</v>
       </c>
       <c r="G22" t="n">
-        <v>40.82039999999999</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>81640.79999999999</v>
+        <v>18635313</v>
       </c>
       <c r="I22" t="n">
-        <v>69.80288399999999</v>
+        <v>15933.192615</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -3843,21 +5155,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31-2886-BUY</t>
+          <t>2026-08-26-3045-BUY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2886</v>
+        <v>3045</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3865,16 +5177,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1000</v>
+        <v>62000</v>
       </c>
       <c r="G23" t="n">
-        <v>48.2241</v>
+        <v>116.058</v>
       </c>
       <c r="H23" t="n">
-        <v>48224.1</v>
+        <v>7195596</v>
       </c>
       <c r="I23" t="n">
-        <v>41.2316055</v>
+        <v>6152.234579999999</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
@@ -3883,21 +5195,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31-2892-BUY</t>
+          <t>2026-08-26-4904-BUY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2892</v>
+        <v>4904</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3905,16 +5217,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000</v>
+        <v>71000</v>
       </c>
       <c r="G24" t="n">
-        <v>35.067525</v>
+        <v>101.0505</v>
       </c>
       <c r="H24" t="n">
-        <v>70135.04999999999</v>
+        <v>7174585.5</v>
       </c>
       <c r="I24" t="n">
-        <v>59.96546774999999</v>
+        <v>6134.2706025</v>
       </c>
       <c r="J24" t="n">
         <v>5</v>
@@ -3923,17 +5235,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31-5880-BUY</t>
+          <t>2026-08-26-5880-BUY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3945,16 +5257,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3000</v>
+        <v>743000</v>
       </c>
       <c r="G25" t="n">
-        <v>25.362675</v>
+        <v>25.0125</v>
       </c>
       <c r="H25" t="n">
-        <v>76088.02499999999</v>
+        <v>18584287.5</v>
       </c>
       <c r="I25" t="n">
-        <v>65.05526137499999</v>
+        <v>15889.5658125</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -3963,17 +5275,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01-0050-BUY</t>
+          <t>2026-08-27-0050-BUY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3985,16 +5297,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1000</v>
+        <v>42000</v>
       </c>
       <c r="G26" t="n">
-        <v>107.55375</v>
+        <v>107.15355</v>
       </c>
       <c r="H26" t="n">
-        <v>107553.75</v>
+        <v>4500449.1</v>
       </c>
       <c r="I26" t="n">
-        <v>91.95845625</v>
+        <v>3847.883980499999</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -4003,21 +5315,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01-2880-BUY</t>
+          <t>2026-08-27-2412-BUY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2880</v>
+        <v>2412</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4025,16 +5337,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1000</v>
+        <v>28000</v>
       </c>
       <c r="G27" t="n">
-        <v>41.970975</v>
+        <v>136.068</v>
       </c>
       <c r="H27" t="n">
-        <v>41970.97500000001</v>
+        <v>3809904</v>
       </c>
       <c r="I27" t="n">
-        <v>35.885183625</v>
+        <v>3257.46792</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
@@ -4043,21 +5355,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01-2886-BUY</t>
+          <t>2026-08-27-2880-BUY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2886</v>
+        <v>2880</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4065,16 +5377,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1000</v>
+        <v>530000</v>
       </c>
       <c r="G28" t="n">
-        <v>48.274125</v>
+        <v>39.369675</v>
       </c>
       <c r="H28" t="n">
-        <v>48274.125</v>
+        <v>20865927.75</v>
       </c>
       <c r="I28" t="n">
-        <v>41.274376875</v>
+        <v>17840.36822625</v>
       </c>
       <c r="J28" t="n">
         <v>5</v>
@@ -4083,21 +5395,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01-2892-BUY</t>
+          <t>2026-08-27-2886-BUY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4105,16 +5417,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2000</v>
+        <v>452000</v>
       </c>
       <c r="G29" t="n">
-        <v>35.567775</v>
+        <v>46.92345</v>
       </c>
       <c r="H29" t="n">
-        <v>71135.54999999999</v>
+        <v>21209399.4</v>
       </c>
       <c r="I29" t="n">
-        <v>60.82089524999999</v>
+        <v>18134.036487</v>
       </c>
       <c r="J29" t="n">
         <v>5</v>
@@ -4123,21 +5435,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01-5880-BUY</t>
+          <t>2026-08-27-2892-BUY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5880</v>
+        <v>2892</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4145,16 +5457,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3000</v>
+        <v>626000</v>
       </c>
       <c r="G30" t="n">
-        <v>25.6128</v>
+        <v>33.51674999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>76838.39999999999</v>
+        <v>20981485.5</v>
       </c>
       <c r="I30" t="n">
-        <v>65.69683199999999</v>
+        <v>17939.1701025</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -4163,21 +5475,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02-2880-BUY</t>
+          <t>2026-08-27-3045-BUY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4185,16 +5497,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1000</v>
+        <v>33000</v>
       </c>
       <c r="G31" t="n">
-        <v>42.92144999999999</v>
+        <v>115.55775</v>
       </c>
       <c r="H31" t="n">
-        <v>42921.44999999999</v>
+        <v>3813405.75</v>
       </c>
       <c r="I31" t="n">
-        <v>36.69783974999999</v>
+        <v>3260.46191625</v>
       </c>
       <c r="J31" t="n">
         <v>5</v>
@@ -4203,21 +5515,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02-2886-BUY</t>
+          <t>2026-08-27-4904-BUY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4225,16 +5537,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1000</v>
+        <v>38000</v>
       </c>
       <c r="G32" t="n">
-        <v>49.0245</v>
+        <v>101.55075</v>
       </c>
       <c r="H32" t="n">
-        <v>49024.49999999999</v>
+        <v>3858928.5</v>
       </c>
       <c r="I32" t="n">
-        <v>41.9159475</v>
+        <v>3299.3838675</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
@@ -4243,21 +5555,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02-2892-BUY</t>
+          <t>2026-08-27-5880-BUY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2892</v>
+        <v>5880</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -4265,16 +5577,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000</v>
+        <v>834000</v>
       </c>
       <c r="G33" t="n">
-        <v>36.268125</v>
+        <v>25.11255</v>
       </c>
       <c r="H33" t="n">
-        <v>72536.25</v>
+        <v>20943866.7</v>
       </c>
       <c r="I33" t="n">
-        <v>62.01849375</v>
+        <v>17907.0060285</v>
       </c>
       <c r="J33" t="n">
         <v>5</v>
@@ -4283,38 +5595,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02-5880-BUY</t>
+          <t>2026-08-28-2412-SELL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5880</v>
+        <v>2412</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3000</v>
+        <v>13000</v>
       </c>
       <c r="G34" t="n">
-        <v>26.31315</v>
+        <v>135.932</v>
       </c>
       <c r="H34" t="n">
-        <v>78939.45</v>
+        <v>1767116</v>
       </c>
       <c r="I34" t="n">
-        <v>67.49322975</v>
+        <v>6812.232180000001</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -4323,38 +5635,38 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03-2880-BUY</t>
+          <t>2026-08-28-3045-SELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2880</v>
+        <v>3045</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="G35" t="n">
-        <v>43.771875</v>
+        <v>114.9425</v>
       </c>
       <c r="H35" t="n">
-        <v>43771.87499999999</v>
+        <v>1724137.5</v>
       </c>
       <c r="I35" t="n">
-        <v>37.424953125</v>
+        <v>6646.5500625</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -4363,38 +5675,38 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03-2886-BUY</t>
+          <t>2026-08-28-4904-SELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2886</v>
+        <v>4904</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="G36" t="n">
-        <v>50.8254</v>
+        <v>99.7501</v>
       </c>
       <c r="H36" t="n">
-        <v>50825.4</v>
+        <v>1795501.8</v>
       </c>
       <c r="I36" t="n">
-        <v>43.45571699999999</v>
+        <v>6921.659439</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -4403,21 +5715,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03-2892-BUY</t>
+          <t>2026-08-28-0050-BUY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2892</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -4425,16 +5737,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1000</v>
+        <v>101000</v>
       </c>
       <c r="G37" t="n">
-        <v>36.968475</v>
+        <v>105.6528</v>
       </c>
       <c r="H37" t="n">
-        <v>36968.475</v>
+        <v>10670932.8</v>
       </c>
       <c r="I37" t="n">
-        <v>31.608046125</v>
+        <v>9123.647543999999</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -4443,40 +5755,1760 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2026-08-28-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>434000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>40.270125</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17477234.25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>14943.03528375</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-28-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>363000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>47.92395</v>
+      </c>
+      <c r="H39" t="n">
+        <v>17396393.85</v>
+      </c>
+      <c r="I39" t="n">
+        <v>14873.91674175</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-28-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>508000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.31715</v>
+      </c>
+      <c r="H40" t="n">
+        <v>17433112.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>14905.310931</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-28-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>693000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>25.262625</v>
+      </c>
+      <c r="H41" t="n">
+        <v>17506999.125</v>
+      </c>
+      <c r="I41" t="n">
+        <v>14968.484251875</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>135.932</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4757620.000000001</v>
+      </c>
+      <c r="I42" t="n">
+        <v>18340.6251</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>41000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>114.9425</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4712642.5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>18167.2368375</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>47000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>100.44975</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4721138.25</v>
+      </c>
+      <c r="I44" t="n">
+        <v>18199.98795375</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-31-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>50</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>106.55325</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7032514.499999999</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6012.799897499999</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-31-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>158000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>40.82039999999999</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6449623.199999998</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5514.427835999998</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-31-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>135000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>48.2241</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6510253.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5566.2667425</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-31-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>185000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.067525</v>
+      </c>
+      <c r="H48" t="n">
+        <v>6487492.124999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5546.805766874999</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-31-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>256000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>25.362675</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6492844.8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5551.382304</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-01-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>136.43175</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4365816</v>
+      </c>
+      <c r="I50" t="n">
+        <v>16830.22068</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-01-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>115.44225</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4386805.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>16911.1352025</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-01-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>44000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>100.44975</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4419789</v>
+      </c>
+      <c r="I52" t="n">
+        <v>17038.286595</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>50</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>54000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>107.55375</v>
+      </c>
+      <c r="H53" t="n">
+        <v>5807902.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4965.7566375</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-01-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>73000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>41.970975</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3063881.175</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2619.618404625</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-01-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>48.274125</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3041269.875</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2600.285743125</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-01-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>35.567775</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3023260.875</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2584.888048125</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-01-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>25.6128</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3073536</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2627.87328</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-02-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>27000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>137.43125</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3710643.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>14304.53165625</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-02-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>115.942</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3710144</v>
+      </c>
+      <c r="I59" t="n">
+        <v>14302.60512</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-02-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>102.44875</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3688155</v>
+      </c>
+      <c r="I60" t="n">
+        <v>14217.837525</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>50</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>31000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>106.95345</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3315556.95</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2834.80119225</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-02-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>51000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>42.92144999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2188993.95</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1871.58982725</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-02-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>49.0245</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2206102.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1886.2176375</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-02-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>61000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>36.268125</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2212355.625</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1891.564059375</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-02-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>84000</v>
+      </c>
+      <c r="G65" t="n">
+        <v>26.31315</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2210304.6</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1889.810433</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-03-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>107.64615</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2152923</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3993.672165</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-03-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>137.931</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2620689</v>
+      </c>
+      <c r="I67" t="n">
+        <v>10102.756095</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-03-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>23000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>117.44125</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2701148.75</v>
+      </c>
+      <c r="I68" t="n">
+        <v>10412.92843125</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-03-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>26000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>102.9485</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2676661</v>
+      </c>
+      <c r="I69" t="n">
+        <v>10318.528155</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-03-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>62000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>43.771875</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2713856.25</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2320.34709375</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-03-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>53000</v>
+      </c>
+      <c r="G71" t="n">
+        <v>50.8254</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2693746.2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2303.153001</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-03-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>73000</v>
+      </c>
+      <c r="G72" t="n">
+        <v>36.968475</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2698698.675</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2307.387367125</v>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>2026-09-03-5880-BUY</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D73" t="n">
         <v>5880</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>91000</v>
+      </c>
+      <c r="G73" t="n">
         <v>26.71335</v>
       </c>
-      <c r="H38" t="n">
-        <v>53426.7</v>
-      </c>
-      <c r="I38" t="n">
-        <v>45.67982849999999</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="H73" t="n">
+        <v>2430914.85</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2078.43219675</v>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-04-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G74" t="n">
+        <v>138.43075</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2214892</v>
+      </c>
+      <c r="I74" t="n">
+        <v>8538.408660000001</v>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-04-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G75" t="n">
+        <v>117.941</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2240879</v>
+      </c>
+      <c r="I75" t="n">
+        <v>8638.588545000001</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-04-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G76" t="n">
+        <v>104.44775</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2193402.75</v>
+      </c>
+      <c r="I76" t="n">
+        <v>8455.567601249999</v>
+      </c>
+      <c r="J76" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-04-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>50</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G77" t="n">
+        <v>109.104525</v>
+      </c>
+      <c r="H77" t="n">
+        <v>545522.625</v>
+      </c>
+      <c r="I77" t="n">
+        <v>466.421844375</v>
+      </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G78" t="n">
+        <v>44.72235</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1565282.25</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1338.31632375</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-04-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>31000</v>
+      </c>
+      <c r="G79" t="n">
+        <v>50.4252</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1563181.2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1336.519926</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-04-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>41000</v>
+      </c>
+      <c r="G80" t="n">
+        <v>38.019</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1558779</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1332.756045</v>
+      </c>
+      <c r="J80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-04-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>51000</v>
+      </c>
+      <c r="G81" t="n">
+        <v>26.763375</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1364932.125</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1167.016966875</v>
+      </c>
+      <c r="J81" t="n">
         <v>5</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,93 +416,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>generated_at_utc</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>data_max_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>score_financial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>score_telecom</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>score_0050</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>e19_points</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>e19_alert</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>e20_confirmations</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>e20_streak</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>e16_financial</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>e16_telecom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>e16_0050</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>e20_financial</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>e20_telecom</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>e20_0050</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>financial_alloc</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>kd_opt_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>e45_stitch</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>e45_book</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>e45_blend_alpha</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>e45_exposure</t>
         </is>
       </c>
     </row>
@@ -578,6 +596,12 @@
       <c r="Q2" t="n">
         <v>0.033862723023274</v>
       </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -639,6 +663,12 @@
       <c r="Q3" t="n">
         <v>0.033862723023274</v>
       </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -700,6 +730,12 @@
       <c r="Q4" t="n">
         <v>0.0366971605567614</v>
       </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -761,6 +797,12 @@
       <c r="Q5" t="n">
         <v>0.0393464527190748</v>
       </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -822,6 +864,12 @@
       <c r="Q6" t="n">
         <v>0.0586869499945679</v>
       </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -883,6 +931,12 @@
       <c r="Q7" t="n">
         <v>0.0688673280768098</v>
       </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -944,6 +998,12 @@
       <c r="Q8" t="n">
         <v>0.08029640544059249</v>
       </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1005,6 +1065,12 @@
       <c r="Q9" t="n">
         <v>0.0827062291187696</v>
       </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1066,6 +1132,12 @@
       <c r="Q10" t="n">
         <v>0.0731342277551144</v>
       </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1127,6 +1199,12 @@
       <c r="Q11" t="n">
         <v>0.0772434852114485</v>
       </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1188,6 +1266,12 @@
       <c r="Q12" t="n">
         <v>0.0772434852114485</v>
       </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1249,6 +1333,89 @@
       <c r="Q13" t="n">
         <v>0.0721159353549481</v>
       </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-09T13:06:29.474609+00:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6740874879855158</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.0882160699650812</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.5858714180204344</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8656548579770516</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0587160638372494</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0756290781856991</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8656548579770516</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0587160638372494</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0756290781856991</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1261,76 +1428,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nav_e16_e18</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pre_financial</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pre_telecom</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pre_0050</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>target_l1_gap</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>orders_created</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fills_processed</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>exact_t1_ok</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>same_bar_fills</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>e22_version</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>e22_cash_credit</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>e22_stock_shares_added</t>
         </is>
@@ -1909,6 +2076,54 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>538570722.172183</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1022.172182978364</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8664273433170694</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0598695745471501</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.07370118420085579</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0038538900347618</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1927,32 +2142,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>reference_close</t>
         </is>
@@ -4257,56 +4472,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fill_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>fill_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>side</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>fill_price</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gross</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fees_tax</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>slippage_bp</t>
         </is>
@@ -7509,6 +7724,326 @@
         <v>1167.016966875</v>
       </c>
       <c r="J81" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-08-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>50</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G82" t="n">
+        <v>109.895025</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1868215.425</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3465.539613375</v>
+      </c>
+      <c r="J82" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-08-2412-SELL</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G83" t="n">
+        <v>137.931</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1517241</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5848.964055</v>
+      </c>
+      <c r="J83" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-08-3045-SELL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G84" t="n">
+        <v>117.44125</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1644177.5</v>
+      </c>
+      <c r="I84" t="n">
+        <v>6338.304262500001</v>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-08-4904-SELL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G85" t="n">
+        <v>102.44875</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1536731.25</v>
+      </c>
+      <c r="I85" t="n">
+        <v>5924.09896875</v>
+      </c>
+      <c r="J85" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-08-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G86" t="n">
+        <v>44.872425</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1705152.15</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1457.90508825</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-08-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G87" t="n">
+        <v>50.025</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1650825</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1411.455375</v>
+      </c>
+      <c r="J87" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-08-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G88" t="n">
+        <v>37.968975</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1708603.875</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1460.856313125</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-08-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>56000</v>
+      </c>
+      <c r="G89" t="n">
+        <v>26.71335</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1495947.6</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1279.035198</v>
+      </c>
+      <c r="J89" t="n">
         <v>5</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1416,6 +1416,83 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-10T13:02:59.077955+00:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7314883351475182</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.005458661230077</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.7260296739174408</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8656548579770516</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0587160638372494</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0756290781856991</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.8656548579770516</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0587160638372494</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.0756290781856991</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1428,7 +1505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,6 +2201,54 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>539414872.172183</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1022.172182978364</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8667939541918169</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0599538530885684</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.07325029775483741</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.004755665896946</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1493,6 +1493,83 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-11T12:57:49.560650+00:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7302254234361545</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0818398508418032</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.8120652742779577</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8742411434827887</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0615768919658533</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.064181964551358</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.8742411434827887</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0615768919658533</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.064181964551358</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1505,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2249,6 +2326,54 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>550396672.172183</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1022.172182978364</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8699148708701048</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0592481779937042</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0708350939807343</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0133081160142092</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
